--- a/output/2025-07-17.xlsx
+++ b/output/2025-07-17.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.93</v>
+        <v>2.17</v>
       </c>
       <c r="F14" t="n">
-        <v>9.25</v>
+        <v>8.93</v>
       </c>
       <c r="G14" t="n">
-        <v>82</v>
+        <v>59.8</v>
       </c>
       <c r="H14" t="n">
-        <v>91.8</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>-58.71</v>
+        <v>-194.96</v>
       </c>
       <c r="K14" t="n">
-        <v>71.83</v>
+        <v>-6.68</v>
       </c>
       <c r="L14" t="n">
-        <v>92.77</v>
+        <v>195.08</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:56:16</t>
+          <t>04:55:56</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="F15" t="n">
-        <v>8.699999999999999</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>81.7</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>91.8</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-86.66</v>
+        <v>-25.32</v>
       </c>
       <c r="K15" t="n">
-        <v>-31.15</v>
+        <v>-69.66</v>
       </c>
       <c r="L15" t="n">
-        <v>92.09</v>
+        <v>74.12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:57:46</t>
+          <t>04:58:42</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="F16" t="n">
-        <v>8.75</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>70.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>92.90000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="I16" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>31.24</v>
+        <v>65.64</v>
       </c>
       <c r="K16" t="n">
-        <v>70.14</v>
+        <v>125.27</v>
       </c>
       <c r="L16" t="n">
-        <v>76.78</v>
+        <v>141.43</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:03:51</t>
+          <t>05:03:15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="F17" t="n">
-        <v>8.630000000000001</v>
+        <v>9.84</v>
       </c>
       <c r="G17" t="n">
-        <v>84.09999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>89.90000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>89.34</v>
+        <v>-21.99</v>
       </c>
       <c r="K17" t="n">
-        <v>166.99</v>
+        <v>-190.66</v>
       </c>
       <c r="L17" t="n">
-        <v>189.39</v>
+        <v>191.92</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:05:59</t>
+          <t>05:04:13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.63</v>
+        <v>2.16</v>
       </c>
       <c r="F18" t="n">
-        <v>8.960000000000001</v>
+        <v>8.16</v>
       </c>
       <c r="G18" t="n">
-        <v>79.5</v>
+        <v>88.3</v>
       </c>
       <c r="H18" t="n">
-        <v>90.40000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>-171.04</v>
+        <v>42.07</v>
       </c>
       <c r="K18" t="n">
-        <v>72.02</v>
+        <v>127.58</v>
       </c>
       <c r="L18" t="n">
-        <v>185.58</v>
+        <v>134.34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:08:04</t>
+          <t>05:05:18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.74</v>
+        <v>1.96</v>
       </c>
       <c r="F19" t="n">
-        <v>9.26</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>82.5</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>91.40000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>-208.82</v>
+        <v>56.78</v>
       </c>
       <c r="K19" t="n">
-        <v>-26.06</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>210.44</v>
+        <v>91.06999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:14:05</t>
+          <t>05:09:06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.97</v>
+        <v>1.79</v>
       </c>
       <c r="F20" t="n">
-        <v>7.47</v>
+        <v>8.94</v>
       </c>
       <c r="G20" t="n">
-        <v>83.8</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>84.7</v>
+        <v>84.2</v>
       </c>
       <c r="I20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>230.92</v>
+        <v>119.48</v>
       </c>
       <c r="K20" t="n">
-        <v>-67.34</v>
+        <v>-146.32</v>
       </c>
       <c r="L20" t="n">
-        <v>240.53</v>
+        <v>188.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:15:35</t>
+          <t>05:10:25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.74</v>
+        <v>2.18</v>
       </c>
       <c r="F21" t="n">
-        <v>8.58</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>71.7</v>
+        <v>66.8</v>
       </c>
       <c r="H21" t="n">
-        <v>86.3</v>
+        <v>88.7</v>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>-156.65</v>
+        <v>-4.87</v>
       </c>
       <c r="K21" t="n">
-        <v>-181.59</v>
+        <v>-80.70999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>239.82</v>
+        <v>80.84999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:17:39</t>
+          <t>05:12:08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.58</v>
+        <v>1.66</v>
       </c>
       <c r="F22" t="n">
-        <v>9.109999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>74.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>91.59999999999999</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-136.55</v>
+        <v>-113.16</v>
       </c>
       <c r="K22" t="n">
-        <v>-204.15</v>
+        <v>32.49</v>
       </c>
       <c r="L22" t="n">
-        <v>245.61</v>
+        <v>117.73</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:21:39</t>
+          <t>05:18:21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.39</v>
+        <v>1.99</v>
       </c>
       <c r="F23" t="n">
-        <v>8.35</v>
+        <v>8.44</v>
       </c>
       <c r="G23" t="n">
-        <v>69.90000000000001</v>
+        <v>86</v>
       </c>
       <c r="H23" t="n">
-        <v>84.2</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>523.78</v>
+        <v>-281.79</v>
       </c>
       <c r="K23" t="n">
-        <v>173.76</v>
+        <v>17.74</v>
       </c>
       <c r="L23" t="n">
-        <v>551.85</v>
+        <v>282.35</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:23:15</t>
+          <t>05:20:29</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.2</v>
+        <v>1.38</v>
       </c>
       <c r="F24" t="n">
-        <v>8</v>
+        <v>9.57</v>
       </c>
       <c r="G24" t="n">
-        <v>80.90000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>81.2</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J24" t="n">
-        <v>-127.28</v>
+        <v>230.86</v>
       </c>
       <c r="K24" t="n">
-        <v>-292.68</v>
+        <v>17.03</v>
       </c>
       <c r="L24" t="n">
-        <v>319.16</v>
+        <v>231.49</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:25:18</t>
+          <t>05:21:55</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.67</v>
+        <v>2.12</v>
       </c>
       <c r="F25" t="n">
-        <v>9.119999999999999</v>
+        <v>9.19</v>
       </c>
       <c r="G25" t="n">
-        <v>74.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>81.7</v>
+        <v>93.2</v>
       </c>
       <c r="I25" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>176.37</v>
+        <v>118.24</v>
       </c>
       <c r="K25" t="n">
-        <v>72</v>
+        <v>228.02</v>
       </c>
       <c r="L25" t="n">
-        <v>190.5</v>
+        <v>256.85</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:29:59</t>
+          <t>05:26:33</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.48</v>
+        <v>2.01</v>
       </c>
       <c r="F26" t="n">
-        <v>8.800000000000001</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>64.40000000000001</v>
+        <v>61.6</v>
       </c>
       <c r="H26" t="n">
-        <v>88.8</v>
+        <v>83.2</v>
       </c>
       <c r="I26" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-306.91</v>
+        <v>-46.74</v>
       </c>
       <c r="K26" t="n">
-        <v>-365.09</v>
+        <v>455.46</v>
       </c>
       <c r="L26" t="n">
-        <v>476.95</v>
+        <v>457.85</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:32:24</t>
+          <t>05:28:16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="F27" t="n">
-        <v>8.01</v>
+        <v>8.83</v>
       </c>
       <c r="G27" t="n">
-        <v>73</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>92.40000000000001</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>-194.84</v>
+        <v>-564.14</v>
       </c>
       <c r="K27" t="n">
-        <v>-53.83</v>
+        <v>-51.45</v>
       </c>
       <c r="L27" t="n">
-        <v>202.14</v>
+        <v>566.48</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:33:42</t>
+          <t>05:29:55</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.62</v>
+        <v>2.04</v>
       </c>
       <c r="F28" t="n">
         <v>9.08</v>
       </c>
       <c r="G28" t="n">
-        <v>73.90000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>85.3</v>
+        <v>90</v>
       </c>
       <c r="I28" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>257.16</v>
+        <v>-120.76</v>
       </c>
       <c r="K28" t="n">
-        <v>-344.45</v>
+        <v>186.58</v>
       </c>
       <c r="L28" t="n">
-        <v>429.86</v>
+        <v>222.25</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:43:27</t>
+          <t>05:37:37</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="F29" t="n">
-        <v>8.869999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>73.8</v>
+        <v>63.5</v>
       </c>
       <c r="H29" t="n">
-        <v>90.90000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="I29" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>40.49</v>
+        <v>-38.01</v>
       </c>
       <c r="K29" t="n">
-        <v>-109.03</v>
+        <v>-29.77</v>
       </c>
       <c r="L29" t="n">
-        <v>116.3</v>
+        <v>48.28</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:44:14</t>
+          <t>05:39:01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.81</v>
+        <v>2.25</v>
       </c>
       <c r="F30" t="n">
-        <v>9.16</v>
+        <v>8.08</v>
       </c>
       <c r="G30" t="n">
-        <v>65.59999999999999</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>92.2</v>
+        <v>88</v>
       </c>
       <c r="I30" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-43.22</v>
+        <v>-90.42</v>
       </c>
       <c r="K30" t="n">
-        <v>-73.63</v>
+        <v>30.74</v>
       </c>
       <c r="L30" t="n">
-        <v>85.38</v>
+        <v>95.51000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:45:42</t>
+          <t>05:40:05</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.23</v>
+        <v>2.01</v>
       </c>
       <c r="F31" t="n">
-        <v>8.82</v>
+        <v>9.34</v>
       </c>
       <c r="G31" t="n">
-        <v>100.5</v>
+        <v>52.8</v>
       </c>
       <c r="H31" t="n">
-        <v>89.5</v>
+        <v>88.3</v>
       </c>
       <c r="I31" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>69.18000000000001</v>
+        <v>-24.25</v>
       </c>
       <c r="K31" t="n">
-        <v>0.15</v>
+        <v>38.79</v>
       </c>
       <c r="L31" t="n">
-        <v>69.18000000000001</v>
+        <v>45.75</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:49:33</t>
+          <t>05:43:30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="F32" t="n">
-        <v>9.33</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>90.2</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>92.5</v>
+        <v>97.3</v>
       </c>
       <c r="I32" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>-90.92</v>
+        <v>125.28</v>
       </c>
       <c r="K32" t="n">
-        <v>-17.24</v>
+        <v>-148.82</v>
       </c>
       <c r="L32" t="n">
-        <v>92.55</v>
+        <v>194.53</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:51:57</t>
+          <t>05:45:15</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="F33" t="n">
-        <v>8.960000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="G33" t="n">
-        <v>68</v>
+        <v>75.5</v>
       </c>
       <c r="H33" t="n">
-        <v>90.3</v>
+        <v>92.2</v>
       </c>
       <c r="I33" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>47.75</v>
+        <v>44.39</v>
       </c>
       <c r="K33" t="n">
-        <v>-51.29</v>
+        <v>201.1</v>
       </c>
       <c r="L33" t="n">
-        <v>70.08</v>
+        <v>205.94</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:53:37</t>
+          <t>05:47:01</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="F34" t="n">
-        <v>9.07</v>
+        <v>8.85</v>
       </c>
       <c r="G34" t="n">
-        <v>71.8</v>
+        <v>63.9</v>
       </c>
       <c r="H34" t="n">
-        <v>84.59999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-6.47</v>
+        <v>-224.53</v>
       </c>
       <c r="K34" t="n">
-        <v>-213.05</v>
+        <v>85.51000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>213.15</v>
+        <v>240.26</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:56:51</t>
+          <t>05:51:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="F35" t="n">
-        <v>8.15</v>
+        <v>9.67</v>
       </c>
       <c r="G35" t="n">
-        <v>80.90000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>82</v>
+        <v>96.8</v>
       </c>
       <c r="I35" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>52.47</v>
+        <v>-2.21</v>
       </c>
       <c r="K35" t="n">
-        <v>-151.77</v>
+        <v>301.85</v>
       </c>
       <c r="L35" t="n">
-        <v>160.58</v>
+        <v>301.86</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:57:30</t>
+          <t>05:52:51</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.22</v>
+        <v>1.81</v>
       </c>
       <c r="F36" t="n">
-        <v>8.98</v>
+        <v>8.92</v>
       </c>
       <c r="G36" t="n">
-        <v>66.59999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="H36" t="n">
-        <v>73.40000000000001</v>
+        <v>90.8</v>
       </c>
       <c r="I36" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>-154.06</v>
+        <v>149.51</v>
       </c>
       <c r="K36" t="n">
-        <v>137.53</v>
+        <v>31.48</v>
       </c>
       <c r="L36" t="n">
-        <v>206.52</v>
+        <v>152.79</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:59:54</t>
+          <t>05:54:55</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="F37" t="n">
-        <v>8.779999999999999</v>
+        <v>9.34</v>
       </c>
       <c r="G37" t="n">
-        <v>70.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="H37" t="n">
-        <v>89.90000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>111.24</v>
+        <v>-226.01</v>
       </c>
       <c r="K37" t="n">
-        <v>17.12</v>
+        <v>-52.05</v>
       </c>
       <c r="L37" t="n">
-        <v>112.55</v>
+        <v>231.93</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:03:52</t>
+          <t>06:00:45</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="F38" t="n">
-        <v>8.970000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="G38" t="n">
-        <v>78</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="H38" t="n">
-        <v>92.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="I38" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>-114.43</v>
+        <v>75.77</v>
       </c>
       <c r="K38" t="n">
-        <v>294.78</v>
+        <v>232.85</v>
       </c>
       <c r="L38" t="n">
-        <v>316.21</v>
+        <v>244.87</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:05:50</t>
+          <t>06:02:23</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="F39" t="n">
-        <v>9.01</v>
+        <v>8.82</v>
       </c>
       <c r="G39" t="n">
-        <v>65.8</v>
+        <v>79.5</v>
       </c>
       <c r="H39" t="n">
-        <v>83.40000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="I39" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>52.21</v>
+        <v>389.98</v>
       </c>
       <c r="K39" t="n">
-        <v>88.55</v>
+        <v>-178.96</v>
       </c>
       <c r="L39" t="n">
-        <v>102.79</v>
+        <v>429.08</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:08:24</t>
+          <t>06:03:08</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.57</v>
+        <v>2.69</v>
       </c>
       <c r="F40" t="n">
-        <v>8.949999999999999</v>
+        <v>8.81</v>
       </c>
       <c r="G40" t="n">
-        <v>76.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="H40" t="n">
-        <v>88.2</v>
+        <v>96</v>
       </c>
       <c r="I40" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>441.97</v>
+        <v>-177.86</v>
       </c>
       <c r="K40" t="n">
-        <v>15.37</v>
+        <v>386.18</v>
       </c>
       <c r="L40" t="n">
-        <v>442.23</v>
+        <v>425.17</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:11:42</t>
+          <t>06:06:56</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.13</v>
+        <v>1.9</v>
       </c>
       <c r="F41" t="n">
-        <v>8.24</v>
+        <v>8.59</v>
       </c>
       <c r="G41" t="n">
-        <v>73.59999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="H41" t="n">
-        <v>84.8</v>
+        <v>85.7</v>
       </c>
       <c r="I41" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>65.36</v>
+        <v>-305.03</v>
       </c>
       <c r="K41" t="n">
-        <v>-99.89</v>
+        <v>483.59</v>
       </c>
       <c r="L41" t="n">
-        <v>119.38</v>
+        <v>571.75</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:12:23</t>
+          <t>06:08:16</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,13 +1801,13 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.53</v>
+        <v>2.06</v>
       </c>
       <c r="F42" t="n">
-        <v>8.75</v>
+        <v>9.26</v>
       </c>
       <c r="G42" t="n">
-        <v>82.8</v>
+        <v>89.3</v>
       </c>
       <c r="H42" t="n">
         <v>92</v>
@@ -1816,19 +1816,19 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>25.58</v>
+        <v>-343.29</v>
       </c>
       <c r="K42" t="n">
-        <v>-46.58</v>
+        <v>119.93</v>
       </c>
       <c r="L42" t="n">
-        <v>53.14</v>
+        <v>363.64</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:14:49</t>
+          <t>06:09:27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="F43" t="n">
-        <v>8.390000000000001</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="G43" t="n">
-        <v>68.40000000000001</v>
+        <v>58.1</v>
       </c>
       <c r="H43" t="n">
-        <v>92.2</v>
+        <v>89.5</v>
       </c>
       <c r="I43" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>-362.52</v>
+        <v>18.27</v>
       </c>
       <c r="K43" t="n">
-        <v>-37.35</v>
+        <v>396.6</v>
       </c>
       <c r="L43" t="n">
-        <v>364.44</v>
+        <v>397.02</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:25:40</t>
+          <t>06:17:12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.21</v>
+        <v>2.45</v>
       </c>
       <c r="F44" t="n">
-        <v>9.369999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="G44" t="n">
-        <v>71.90000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="H44" t="n">
-        <v>85.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-56.81</v>
+        <v>-110.05</v>
       </c>
       <c r="K44" t="n">
-        <v>-34.55</v>
+        <v>15.11</v>
       </c>
       <c r="L44" t="n">
-        <v>66.48999999999999</v>
+        <v>111.09</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:27:57</t>
+          <t>06:18:38</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="F45" t="n">
-        <v>9.779999999999999</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G45" t="n">
-        <v>83.59999999999999</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>80.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="I45" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>19.4</v>
+        <v>-54.3</v>
       </c>
       <c r="K45" t="n">
-        <v>-38.1</v>
+        <v>-44</v>
       </c>
       <c r="L45" t="n">
-        <v>42.75</v>
+        <v>69.89</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:29:35</t>
+          <t>06:20:56</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.86</v>
+        <v>2.09</v>
       </c>
       <c r="F46" t="n">
-        <v>9.01</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="G46" t="n">
-        <v>80.3</v>
+        <v>71.2</v>
       </c>
       <c r="H46" t="n">
-        <v>89.40000000000001</v>
+        <v>91</v>
       </c>
       <c r="I46" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>-15.76</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>133.66</v>
+        <v>-50.06</v>
       </c>
       <c r="L46" t="n">
-        <v>134.58</v>
+        <v>107.51</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:34:22</t>
+          <t>06:25:47</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="F47" t="n">
-        <v>9.02</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G47" t="n">
-        <v>79.09999999999999</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>92.8</v>
+        <v>94</v>
       </c>
       <c r="I47" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-161.58</v>
+        <v>-43.57</v>
       </c>
       <c r="K47" t="n">
-        <v>64.2</v>
+        <v>61.32</v>
       </c>
       <c r="L47" t="n">
-        <v>173.86</v>
+        <v>75.22</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:35:57</t>
+          <t>06:28:11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="F48" t="n">
-        <v>9.460000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="G48" t="n">
-        <v>65.5</v>
+        <v>78.3</v>
       </c>
       <c r="H48" t="n">
-        <v>87.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>10.91</v>
+        <v>-40.68</v>
       </c>
       <c r="K48" t="n">
-        <v>-59.27</v>
+        <v>23.61</v>
       </c>
       <c r="L48" t="n">
-        <v>60.27</v>
+        <v>47.04</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:36:54</t>
+          <t>06:29:49</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.57</v>
+        <v>1.48</v>
       </c>
       <c r="F49" t="n">
-        <v>8.48</v>
+        <v>8.35</v>
       </c>
       <c r="G49" t="n">
-        <v>76.5</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>85.2</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>35.09</v>
+        <v>127.87</v>
       </c>
       <c r="K49" t="n">
-        <v>-47.54</v>
+        <v>-52.87</v>
       </c>
       <c r="L49" t="n">
-        <v>59.09</v>
+        <v>138.37</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:40:13</t>
+          <t>06:35:47</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="F50" t="n">
-        <v>8.5</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>74.59999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H50" t="n">
-        <v>91.40000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="I50" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J50" t="n">
-        <v>-69.36</v>
+        <v>270.01</v>
       </c>
       <c r="K50" t="n">
-        <v>81.37</v>
+        <v>350.91</v>
       </c>
       <c r="L50" t="n">
-        <v>106.92</v>
+        <v>442.76</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:42:14</t>
+          <t>06:37:10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.47</v>
+        <v>2.22</v>
       </c>
       <c r="F51" t="n">
-        <v>9.07</v>
+        <v>8.31</v>
       </c>
       <c r="G51" t="n">
-        <v>83.5</v>
+        <v>84.7</v>
       </c>
       <c r="H51" t="n">
-        <v>93.3</v>
+        <v>83</v>
       </c>
       <c r="I51" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>158.98</v>
+        <v>35.89</v>
       </c>
       <c r="K51" t="n">
-        <v>-44.55</v>
+        <v>-444.33</v>
       </c>
       <c r="L51" t="n">
-        <v>165.11</v>
+        <v>445.77</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:44:11</t>
+          <t>06:38:38</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.31</v>
+        <v>1.8</v>
       </c>
       <c r="F52" t="n">
-        <v>8.369999999999999</v>
+        <v>9.31</v>
       </c>
       <c r="G52" t="n">
-        <v>67.5</v>
+        <v>75.2</v>
       </c>
       <c r="H52" t="n">
-        <v>86.2</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>-199.71</v>
+        <v>-72.92</v>
       </c>
       <c r="K52" t="n">
-        <v>-114.74</v>
+        <v>-18.85</v>
       </c>
       <c r="L52" t="n">
-        <v>230.33</v>
+        <v>75.31</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:50:00</t>
+          <t>06:43:33</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="F53" t="n">
-        <v>8.56</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="G53" t="n">
-        <v>62.6</v>
+        <v>78.2</v>
       </c>
       <c r="H53" t="n">
-        <v>83.09999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="I53" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>-52.42</v>
+        <v>251.14</v>
       </c>
       <c r="K53" t="n">
-        <v>504.66</v>
+        <v>-356.02</v>
       </c>
       <c r="L53" t="n">
-        <v>507.37</v>
+        <v>435.69</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:51:52</t>
+          <t>06:45:30</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.01</v>
+        <v>1.81</v>
       </c>
       <c r="F54" t="n">
-        <v>8.869999999999999</v>
+        <v>9.24</v>
       </c>
       <c r="G54" t="n">
-        <v>81.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H54" t="n">
-        <v>86.7</v>
+        <v>79.3</v>
       </c>
       <c r="I54" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-453.04</v>
+        <v>38.64</v>
       </c>
       <c r="K54" t="n">
-        <v>-417.97</v>
+        <v>-57.39</v>
       </c>
       <c r="L54" t="n">
-        <v>616.4</v>
+        <v>69.18000000000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:53:55</t>
+          <t>06:47:38</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="F55" t="n">
-        <v>9.15</v>
+        <v>8.6</v>
       </c>
       <c r="G55" t="n">
-        <v>71.5</v>
+        <v>84.8</v>
       </c>
       <c r="H55" t="n">
-        <v>93.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>-1.33</v>
+        <v>31.43</v>
       </c>
       <c r="K55" t="n">
-        <v>95.61</v>
+        <v>-231.46</v>
       </c>
       <c r="L55" t="n">
-        <v>95.62</v>
+        <v>233.59</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:57:16</t>
+          <t>06:50:41</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.36</v>
+        <v>2.55</v>
       </c>
       <c r="F56" t="n">
-        <v>8.74</v>
+        <v>8.98</v>
       </c>
       <c r="G56" t="n">
-        <v>81.2</v>
+        <v>72.5</v>
       </c>
       <c r="H56" t="n">
-        <v>81.8</v>
+        <v>82.3</v>
       </c>
       <c r="I56" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J56" t="n">
-        <v>-142.06</v>
+        <v>-696.0599999999999</v>
       </c>
       <c r="K56" t="n">
-        <v>-201.05</v>
+        <v>-276.89</v>
       </c>
       <c r="L56" t="n">
-        <v>246.17</v>
+        <v>749.11</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:59:00</t>
+          <t>06:51:46</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.38</v>
+        <v>1.81</v>
       </c>
       <c r="F57" t="n">
-        <v>9.300000000000001</v>
+        <v>9.35</v>
       </c>
       <c r="G57" t="n">
-        <v>72.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="H57" t="n">
-        <v>93</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>85.58</v>
+        <v>258.92</v>
       </c>
       <c r="K57" t="n">
-        <v>75.16</v>
+        <v>-488.45</v>
       </c>
       <c r="L57" t="n">
-        <v>113.9</v>
+        <v>552.83</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:00:39</t>
+          <t>06:53:43</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="F58" t="n">
-        <v>9.039999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>68.5</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>96.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>332.84</v>
+        <v>-61.81</v>
       </c>
       <c r="K58" t="n">
-        <v>-270.26</v>
+        <v>658.42</v>
       </c>
       <c r="L58" t="n">
-        <v>428.75</v>
+        <v>661.3200000000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:12:29</t>
+          <t>07:05:12</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.43</v>
+        <v>2.29</v>
       </c>
       <c r="F59" t="n">
-        <v>8.949999999999999</v>
+        <v>9.35</v>
       </c>
       <c r="G59" t="n">
-        <v>75</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>83.2</v>
+        <v>83.7</v>
       </c>
       <c r="I59" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>28.94</v>
+        <v>-15.16</v>
       </c>
       <c r="K59" t="n">
-        <v>-94.37</v>
+        <v>-79.84</v>
       </c>
       <c r="L59" t="n">
-        <v>98.70999999999999</v>
+        <v>81.27</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:13:39</t>
+          <t>07:07:05</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.32</v>
+        <v>1.71</v>
       </c>
       <c r="F60" t="n">
-        <v>9.279999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="G60" t="n">
-        <v>82.8</v>
+        <v>76.7</v>
       </c>
       <c r="H60" t="n">
-        <v>86.90000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>-124.33</v>
+        <v>17.41</v>
       </c>
       <c r="K60" t="n">
-        <v>125.78</v>
+        <v>-94.34</v>
       </c>
       <c r="L60" t="n">
-        <v>176.86</v>
+        <v>95.94</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:14:48</t>
+          <t>07:09:29</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="F61" t="n">
-        <v>9.31</v>
+        <v>8.73</v>
       </c>
       <c r="G61" t="n">
-        <v>56.1</v>
+        <v>62.5</v>
       </c>
       <c r="H61" t="n">
-        <v>94</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>10.1</v>
+        <v>-239.39</v>
       </c>
       <c r="K61" t="n">
-        <v>60.6</v>
+        <v>75.98</v>
       </c>
       <c r="L61" t="n">
-        <v>61.43</v>
+        <v>251.15</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:19:34</t>
+          <t>07:14:55</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="F62" t="n">
-        <v>9.970000000000001</v>
+        <v>8.41</v>
       </c>
       <c r="G62" t="n">
-        <v>78.5</v>
+        <v>67.2</v>
       </c>
       <c r="H62" t="n">
-        <v>88.2</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I62" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-53.49</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>-123.31</v>
+        <v>-63.78</v>
       </c>
       <c r="L62" t="n">
-        <v>134.41</v>
+        <v>108.42</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:20:47</t>
+          <t>07:16:03</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.8</v>
+        <v>2.11</v>
       </c>
       <c r="F63" t="n">
-        <v>8.869999999999999</v>
+        <v>9.49</v>
       </c>
       <c r="G63" t="n">
-        <v>66.09999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="H63" t="n">
-        <v>89</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-52.5</v>
+        <v>-89.43000000000001</v>
       </c>
       <c r="K63" t="n">
-        <v>-71.59999999999999</v>
+        <v>-156.33</v>
       </c>
       <c r="L63" t="n">
-        <v>88.78</v>
+        <v>180.1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:23:10</t>
+          <t>07:18:04</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.09</v>
+        <v>1.97</v>
       </c>
       <c r="F64" t="n">
-        <v>9.19</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="G64" t="n">
-        <v>60.2</v>
+        <v>67</v>
       </c>
       <c r="H64" t="n">
-        <v>89.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="I64" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>3.93</v>
+        <v>-48.16</v>
       </c>
       <c r="K64" t="n">
-        <v>58.09</v>
+        <v>201.61</v>
       </c>
       <c r="L64" t="n">
-        <v>58.23</v>
+        <v>207.29</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:27:07</t>
+          <t>07:23:12</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="F65" t="n">
-        <v>9.27</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="G65" t="n">
-        <v>80.90000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="H65" t="n">
-        <v>86</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>35.47</v>
+        <v>148.33</v>
       </c>
       <c r="K65" t="n">
-        <v>-9.15</v>
+        <v>94.83</v>
       </c>
       <c r="L65" t="n">
-        <v>36.63</v>
+        <v>176.05</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:29:28</t>
+          <t>07:24:43</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.6</v>
+        <v>1.73</v>
       </c>
       <c r="F66" t="n">
-        <v>8.57</v>
+        <v>9.08</v>
       </c>
       <c r="G66" t="n">
-        <v>56.5</v>
+        <v>68.7</v>
       </c>
       <c r="H66" t="n">
-        <v>91.09999999999999</v>
+        <v>86</v>
       </c>
       <c r="I66" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>295.88</v>
+        <v>-29.38</v>
       </c>
       <c r="K66" t="n">
-        <v>159.32</v>
+        <v>303.64</v>
       </c>
       <c r="L66" t="n">
-        <v>336.05</v>
+        <v>305.06</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:30:22</t>
+          <t>07:26:51</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="F67" t="n">
-        <v>9.289999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="G67" t="n">
-        <v>79.5</v>
+        <v>84.2</v>
       </c>
       <c r="H67" t="n">
-        <v>88.09999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I67" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>-244.6</v>
+        <v>-30.59</v>
       </c>
       <c r="K67" t="n">
-        <v>119.03</v>
+        <v>-121.07</v>
       </c>
       <c r="L67" t="n">
-        <v>272.03</v>
+        <v>124.88</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:34:45</t>
+          <t>07:32:04</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.41</v>
+        <v>1.87</v>
       </c>
       <c r="F68" t="n">
-        <v>8.779999999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="G68" t="n">
-        <v>76.5</v>
+        <v>69.3</v>
       </c>
       <c r="H68" t="n">
-        <v>88.5</v>
+        <v>93.2</v>
       </c>
       <c r="I68" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>-135.83</v>
+        <v>-80.52</v>
       </c>
       <c r="K68" t="n">
-        <v>84.64</v>
+        <v>276.24</v>
       </c>
       <c r="L68" t="n">
-        <v>160.04</v>
+        <v>287.74</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:35:25</t>
+          <t>07:34:06</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.48</v>
+        <v>2.08</v>
       </c>
       <c r="F69" t="n">
-        <v>8.56</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="G69" t="n">
-        <v>77.09999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H69" t="n">
-        <v>86.59999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="I69" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>-177.3</v>
+        <v>-72.76000000000001</v>
       </c>
       <c r="K69" t="n">
-        <v>63.34</v>
+        <v>-211.53</v>
       </c>
       <c r="L69" t="n">
-        <v>188.27</v>
+        <v>223.69</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:37:22</t>
+          <t>07:35:27</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>1.88</v>
+        <v>2.53</v>
       </c>
       <c r="F70" t="n">
-        <v>8.85</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="G70" t="n">
-        <v>69.5</v>
+        <v>77.3</v>
       </c>
       <c r="H70" t="n">
-        <v>87.40000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="I70" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>-712.8099999999999</v>
+        <v>8.5</v>
       </c>
       <c r="K70" t="n">
-        <v>335.62</v>
+        <v>419.53</v>
       </c>
       <c r="L70" t="n">
-        <v>787.86</v>
+        <v>419.62</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:43:15</t>
+          <t>07:41:06</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.07</v>
+        <v>2.45</v>
       </c>
       <c r="F71" t="n">
-        <v>8.289999999999999</v>
+        <v>8.77</v>
       </c>
       <c r="G71" t="n">
-        <v>72.8</v>
+        <v>75.2</v>
       </c>
       <c r="H71" t="n">
-        <v>94.5</v>
+        <v>92</v>
       </c>
       <c r="I71" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>-143.43</v>
+        <v>-381.89</v>
       </c>
       <c r="K71" t="n">
-        <v>-522.48</v>
+        <v>84.19</v>
       </c>
       <c r="L71" t="n">
-        <v>541.8099999999999</v>
+        <v>391.06</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:45:31</t>
+          <t>07:43:10</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="F72" t="n">
-        <v>9.01</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="G72" t="n">
-        <v>57.4</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="H72" t="n">
-        <v>83.59999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I72" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-668.83</v>
+        <v>28.16</v>
       </c>
       <c r="K72" t="n">
-        <v>34.01</v>
+        <v>383.76</v>
       </c>
       <c r="L72" t="n">
-        <v>669.6900000000001</v>
+        <v>384.79</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:46:25</t>
+          <t>07:45:09</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="F73" t="n">
-        <v>8.27</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="G73" t="n">
-        <v>69.5</v>
+        <v>76.2</v>
       </c>
       <c r="H73" t="n">
-        <v>86</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>352.13</v>
+        <v>-221.05</v>
       </c>
       <c r="K73" t="n">
-        <v>-197.1</v>
+        <v>220.24</v>
       </c>
       <c r="L73" t="n">
-        <v>403.54</v>
+        <v>312.04</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:55:54</t>
+          <t>07:56:23</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.71</v>
+        <v>2.25</v>
       </c>
       <c r="F74" t="n">
-        <v>8.94</v>
+        <v>7.99</v>
       </c>
       <c r="G74" t="n">
-        <v>65.7</v>
+        <v>90.7</v>
       </c>
       <c r="H74" t="n">
-        <v>84.8</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-38.79</v>
+        <v>-88.73</v>
       </c>
       <c r="K74" t="n">
-        <v>-5.7</v>
+        <v>122.9</v>
       </c>
       <c r="L74" t="n">
-        <v>39.2</v>
+        <v>151.59</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:57:33</t>
+          <t>07:59:06</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="F75" t="n">
-        <v>9.109999999999999</v>
+        <v>8.66</v>
       </c>
       <c r="G75" t="n">
-        <v>63.4</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="H75" t="n">
-        <v>90.40000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>-89.7</v>
+        <v>-62.44</v>
       </c>
       <c r="K75" t="n">
-        <v>-9.890000000000001</v>
+        <v>2.21</v>
       </c>
       <c r="L75" t="n">
-        <v>90.23999999999999</v>
+        <v>62.47</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:58:56</t>
+          <t>08:00:02</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.64</v>
+        <v>1.76</v>
       </c>
       <c r="F76" t="n">
-        <v>9.16</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="G76" t="n">
-        <v>52.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H76" t="n">
-        <v>89.3</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J76" t="n">
-        <v>152.23</v>
+        <v>-53.71</v>
       </c>
       <c r="K76" t="n">
-        <v>4.11</v>
+        <v>-34.34</v>
       </c>
       <c r="L76" t="n">
-        <v>152.28</v>
+        <v>63.75</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:01:49</t>
+          <t>08:04:35</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="F77" t="n">
-        <v>9.26</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="G77" t="n">
-        <v>69.8</v>
+        <v>64.5</v>
       </c>
       <c r="H77" t="n">
-        <v>84.40000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="I77" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-219.94</v>
+        <v>-47.58</v>
       </c>
       <c r="K77" t="n">
-        <v>189.79</v>
+        <v>-6.62</v>
       </c>
       <c r="L77" t="n">
-        <v>290.5</v>
+        <v>48.04</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:02:50</t>
+          <t>08:06:36</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.48</v>
+        <v>1.92</v>
       </c>
       <c r="F78" t="n">
-        <v>8.35</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="G78" t="n">
-        <v>77.7</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="H78" t="n">
-        <v>86.90000000000001</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I78" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>-74.08</v>
+        <v>23.1</v>
       </c>
       <c r="K78" t="n">
-        <v>149.38</v>
+        <v>189.18</v>
       </c>
       <c r="L78" t="n">
-        <v>166.74</v>
+        <v>190.59</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:05:11</t>
+          <t>08:08:40</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.57</v>
+        <v>2.24</v>
       </c>
       <c r="F79" t="n">
-        <v>8.85</v>
+        <v>8.73</v>
       </c>
       <c r="G79" t="n">
-        <v>74.8</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="H79" t="n">
-        <v>93.3</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>196.46</v>
+        <v>-2.49</v>
       </c>
       <c r="K79" t="n">
-        <v>-254.46</v>
+        <v>155.76</v>
       </c>
       <c r="L79" t="n">
-        <v>321.48</v>
+        <v>155.78</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:08:56</t>
+          <t>08:14:14</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="F80" t="n">
-        <v>8.34</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G80" t="n">
-        <v>78.7</v>
+        <v>69.3</v>
       </c>
       <c r="H80" t="n">
-        <v>88.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="I80" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J80" t="n">
-        <v>-29.38</v>
+        <v>-218.85</v>
       </c>
       <c r="K80" t="n">
-        <v>-98.54000000000001</v>
+        <v>-135.55</v>
       </c>
       <c r="L80" t="n">
-        <v>102.83</v>
+        <v>257.42</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:10:25</t>
+          <t>08:15:15</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.41</v>
+        <v>2.15</v>
       </c>
       <c r="F81" t="n">
-        <v>8.83</v>
+        <v>8.65</v>
       </c>
       <c r="G81" t="n">
-        <v>73.59999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="H81" t="n">
-        <v>87.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>75.15000000000001</v>
+        <v>82.69</v>
       </c>
       <c r="K81" t="n">
-        <v>-180.46</v>
+        <v>274.64</v>
       </c>
       <c r="L81" t="n">
-        <v>195.48</v>
+        <v>286.82</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:12:37</t>
+          <t>08:16:38</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.87</v>
+        <v>2.05</v>
       </c>
       <c r="F82" t="n">
-        <v>8.32</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="G82" t="n">
-        <v>71.2</v>
+        <v>79.8</v>
       </c>
       <c r="H82" t="n">
-        <v>83.5</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>228.37</v>
+        <v>-80.33</v>
       </c>
       <c r="K82" t="n">
-        <v>-7.36</v>
+        <v>109.93</v>
       </c>
       <c r="L82" t="n">
-        <v>228.49</v>
+        <v>136.15</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:17:41</t>
+          <t>08:20:38</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.48</v>
+        <v>2.24</v>
       </c>
       <c r="F83" t="n">
-        <v>8.460000000000001</v>
+        <v>9.01</v>
       </c>
       <c r="G83" t="n">
-        <v>85.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="H83" t="n">
-        <v>86.2</v>
+        <v>88.5</v>
       </c>
       <c r="I83" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>-87.45999999999999</v>
+        <v>122.98</v>
       </c>
       <c r="K83" t="n">
-        <v>-226.29</v>
+        <v>-137.39</v>
       </c>
       <c r="L83" t="n">
-        <v>242.6</v>
+        <v>184.39</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:19:21</t>
+          <t>08:22:27</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="F84" t="n">
-        <v>8.470000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="G84" t="n">
         <v>71.7</v>
       </c>
       <c r="H84" t="n">
-        <v>80.2</v>
+        <v>91.2</v>
       </c>
       <c r="I84" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>-174.79</v>
+        <v>-198.63</v>
       </c>
       <c r="K84" t="n">
-        <v>-450.48</v>
+        <v>51.82</v>
       </c>
       <c r="L84" t="n">
-        <v>483.2</v>
+        <v>205.28</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:21:36</t>
+          <t>08:23:52</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.88</v>
+        <v>2.11</v>
       </c>
       <c r="F85" t="n">
-        <v>8.699999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="G85" t="n">
-        <v>64.2</v>
+        <v>67.3</v>
       </c>
       <c r="H85" t="n">
-        <v>91.2</v>
+        <v>93.8</v>
       </c>
       <c r="I85" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>519.25</v>
+        <v>-197.39</v>
       </c>
       <c r="K85" t="n">
-        <v>-267.71</v>
+        <v>-152.17</v>
       </c>
       <c r="L85" t="n">
-        <v>584.2</v>
+        <v>249.24</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:26:55</t>
+          <t>08:29:05</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.59</v>
+        <v>2.85</v>
       </c>
       <c r="F86" t="n">
-        <v>9.279999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="G86" t="n">
-        <v>89.09999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="H86" t="n">
-        <v>91.5</v>
+        <v>86.2</v>
       </c>
       <c r="I86" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>505.55</v>
+        <v>-364.71</v>
       </c>
       <c r="K86" t="n">
-        <v>-255</v>
+        <v>58.41</v>
       </c>
       <c r="L86" t="n">
-        <v>566.22</v>
+        <v>369.36</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:28:54</t>
+          <t>08:31:14</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>1.35</v>
+        <v>2.65</v>
       </c>
       <c r="F87" t="n">
-        <v>8.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G87" t="n">
-        <v>68.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="H87" t="n">
-        <v>90.8</v>
+        <v>86.7</v>
       </c>
       <c r="I87" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>-190.3</v>
+        <v>762.86</v>
       </c>
       <c r="K87" t="n">
-        <v>244.51</v>
+        <v>346.3</v>
       </c>
       <c r="L87" t="n">
-        <v>309.84</v>
+        <v>837.78</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:30:46</t>
+          <t>08:32:09</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.73</v>
+        <v>3.82</v>
       </c>
       <c r="F88" t="n">
-        <v>8.199999999999999</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="G88" t="n">
-        <v>61.7</v>
+        <v>69.3</v>
       </c>
       <c r="H88" t="n">
-        <v>89.5</v>
+        <v>87.2</v>
       </c>
       <c r="I88" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>707.72</v>
+        <v>73.42</v>
       </c>
       <c r="K88" t="n">
-        <v>-242.4</v>
+        <v>113.33</v>
       </c>
       <c r="L88" t="n">
-        <v>748.09</v>
+        <v>135.03</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-17.xlsx
+++ b/output/2025-07-17.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>-194.96</v>
+        <v>-133.99</v>
       </c>
       <c r="K14" t="n">
-        <v>-6.68</v>
+        <v>-4.59</v>
       </c>
       <c r="L14" t="n">
-        <v>195.08</v>
+        <v>134.07</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-25.32</v>
+        <v>-24.7</v>
       </c>
       <c r="K15" t="n">
-        <v>-69.66</v>
+        <v>-67.95999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>74.12</v>
+        <v>72.31</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>65.64</v>
+        <v>50.6</v>
       </c>
       <c r="K16" t="n">
-        <v>125.27</v>
+        <v>96.56999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>141.43</v>
+        <v>109.02</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>-21.99</v>
+        <v>-19.44</v>
       </c>
       <c r="K17" t="n">
-        <v>-190.66</v>
+        <v>-168.55</v>
       </c>
       <c r="L17" t="n">
-        <v>191.92</v>
+        <v>169.67</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>42.07</v>
+        <v>41.46</v>
       </c>
       <c r="K18" t="n">
-        <v>127.58</v>
+        <v>125.74</v>
       </c>
       <c r="L18" t="n">
-        <v>134.34</v>
+        <v>132.4</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>56.78</v>
+        <v>61.15</v>
       </c>
       <c r="K19" t="n">
-        <v>71.20999999999999</v>
+        <v>76.69</v>
       </c>
       <c r="L19" t="n">
-        <v>91.06999999999999</v>
+        <v>98.09</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>119.48</v>
+        <v>114.69</v>
       </c>
       <c r="K20" t="n">
-        <v>-146.32</v>
+        <v>-140.46</v>
       </c>
       <c r="L20" t="n">
-        <v>188.9</v>
+        <v>181.33</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>-4.87</v>
+        <v>-8.08</v>
       </c>
       <c r="K21" t="n">
-        <v>-80.70999999999999</v>
+        <v>-133.97</v>
       </c>
       <c r="L21" t="n">
-        <v>80.84999999999999</v>
+        <v>134.21</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-113.16</v>
+        <v>-127.25</v>
       </c>
       <c r="K22" t="n">
-        <v>32.49</v>
+        <v>36.54</v>
       </c>
       <c r="L22" t="n">
-        <v>117.73</v>
+        <v>132.4</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-281.79</v>
+        <v>-281.5</v>
       </c>
       <c r="K23" t="n">
-        <v>17.74</v>
+        <v>17.72</v>
       </c>
       <c r="L23" t="n">
-        <v>282.35</v>
+        <v>282.06</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>18</v>
       </c>
       <c r="J24" t="n">
-        <v>230.86</v>
+        <v>308.37</v>
       </c>
       <c r="K24" t="n">
-        <v>17.03</v>
+        <v>22.74</v>
       </c>
       <c r="L24" t="n">
-        <v>231.49</v>
+        <v>309.21</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>118.24</v>
+        <v>127</v>
       </c>
       <c r="K25" t="n">
-        <v>228.02</v>
+        <v>244.93</v>
       </c>
       <c r="L25" t="n">
-        <v>256.85</v>
+        <v>275.9</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-46.74</v>
+        <v>-48.13</v>
       </c>
       <c r="K26" t="n">
-        <v>455.46</v>
+        <v>468.96</v>
       </c>
       <c r="L26" t="n">
-        <v>457.85</v>
+        <v>471.43</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>-564.14</v>
+        <v>-631.63</v>
       </c>
       <c r="K27" t="n">
-        <v>-51.45</v>
+        <v>-57.61</v>
       </c>
       <c r="L27" t="n">
-        <v>566.48</v>
+        <v>634.25</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>-120.76</v>
+        <v>-182.32</v>
       </c>
       <c r="K28" t="n">
-        <v>186.58</v>
+        <v>281.7</v>
       </c>
       <c r="L28" t="n">
-        <v>222.25</v>
+        <v>335.55</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-38.01</v>
+        <v>-48.65</v>
       </c>
       <c r="K29" t="n">
-        <v>-29.77</v>
+        <v>-38.1</v>
       </c>
       <c r="L29" t="n">
-        <v>48.28</v>
+        <v>61.79</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-90.42</v>
+        <v>-79.3</v>
       </c>
       <c r="K30" t="n">
-        <v>30.74</v>
+        <v>26.96</v>
       </c>
       <c r="L30" t="n">
-        <v>95.51000000000001</v>
+        <v>83.76000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>-24.25</v>
+        <v>-29.31</v>
       </c>
       <c r="K31" t="n">
-        <v>38.79</v>
+        <v>46.87</v>
       </c>
       <c r="L31" t="n">
-        <v>45.75</v>
+        <v>55.28</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>125.28</v>
+        <v>105.11</v>
       </c>
       <c r="K32" t="n">
-        <v>-148.82</v>
+        <v>-124.86</v>
       </c>
       <c r="L32" t="n">
-        <v>194.53</v>
+        <v>163.21</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>44.39</v>
+        <v>34.75</v>
       </c>
       <c r="K33" t="n">
-        <v>201.1</v>
+        <v>157.39</v>
       </c>
       <c r="L33" t="n">
-        <v>205.94</v>
+        <v>161.18</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-224.53</v>
+        <v>-168.21</v>
       </c>
       <c r="K34" t="n">
-        <v>85.51000000000001</v>
+        <v>64.06</v>
       </c>
       <c r="L34" t="n">
-        <v>240.26</v>
+        <v>180</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-2.21</v>
+        <v>-2.05</v>
       </c>
       <c r="K35" t="n">
-        <v>301.85</v>
+        <v>279.57</v>
       </c>
       <c r="L35" t="n">
-        <v>301.86</v>
+        <v>279.57</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>149.51</v>
+        <v>174.61</v>
       </c>
       <c r="K36" t="n">
-        <v>31.48</v>
+        <v>36.76</v>
       </c>
       <c r="L36" t="n">
-        <v>152.79</v>
+        <v>178.43</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>-226.01</v>
+        <v>-208.83</v>
       </c>
       <c r="K37" t="n">
-        <v>-52.05</v>
+        <v>-48.09</v>
       </c>
       <c r="L37" t="n">
-        <v>231.93</v>
+        <v>214.3</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>75.77</v>
+        <v>88.36</v>
       </c>
       <c r="K38" t="n">
-        <v>232.85</v>
+        <v>271.53</v>
       </c>
       <c r="L38" t="n">
-        <v>244.87</v>
+        <v>285.54</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>389.98</v>
+        <v>362</v>
       </c>
       <c r="K39" t="n">
-        <v>-178.96</v>
+        <v>-166.12</v>
       </c>
       <c r="L39" t="n">
-        <v>429.08</v>
+        <v>398.3</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>-177.86</v>
+        <v>-192.24</v>
       </c>
       <c r="K40" t="n">
-        <v>386.18</v>
+        <v>417.4</v>
       </c>
       <c r="L40" t="n">
-        <v>425.17</v>
+        <v>459.54</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-305.03</v>
+        <v>-324.67</v>
       </c>
       <c r="K41" t="n">
-        <v>483.59</v>
+        <v>514.73</v>
       </c>
       <c r="L41" t="n">
-        <v>571.75</v>
+        <v>608.5700000000001</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-343.29</v>
+        <v>-452.98</v>
       </c>
       <c r="K42" t="n">
-        <v>119.93</v>
+        <v>158.25</v>
       </c>
       <c r="L42" t="n">
-        <v>363.64</v>
+        <v>479.83</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>18.27</v>
+        <v>21.58</v>
       </c>
       <c r="K43" t="n">
-        <v>396.6</v>
+        <v>468.52</v>
       </c>
       <c r="L43" t="n">
-        <v>397.02</v>
+        <v>469.01</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-110.05</v>
+        <v>-108.99</v>
       </c>
       <c r="K44" t="n">
-        <v>15.11</v>
+        <v>14.96</v>
       </c>
       <c r="L44" t="n">
-        <v>111.09</v>
+        <v>110.01</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-54.3</v>
+        <v>-56.07</v>
       </c>
       <c r="K45" t="n">
-        <v>-44</v>
+        <v>-45.44</v>
       </c>
       <c r="L45" t="n">
-        <v>69.89</v>
+        <v>72.17</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>95.15000000000001</v>
+        <v>71.78</v>
       </c>
       <c r="K46" t="n">
-        <v>-50.06</v>
+        <v>-37.76</v>
       </c>
       <c r="L46" t="n">
-        <v>107.51</v>
+        <v>81.09999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-43.57</v>
+        <v>-55.12</v>
       </c>
       <c r="K47" t="n">
-        <v>61.32</v>
+        <v>77.58</v>
       </c>
       <c r="L47" t="n">
-        <v>75.22</v>
+        <v>95.17</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>-40.68</v>
+        <v>-61.93</v>
       </c>
       <c r="K48" t="n">
-        <v>23.61</v>
+        <v>35.95</v>
       </c>
       <c r="L48" t="n">
-        <v>47.04</v>
+        <v>71.61</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>127.87</v>
+        <v>106.79</v>
       </c>
       <c r="K49" t="n">
-        <v>-52.87</v>
+        <v>-44.15</v>
       </c>
       <c r="L49" t="n">
-        <v>138.37</v>
+        <v>115.55</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>18</v>
       </c>
       <c r="J50" t="n">
-        <v>270.01</v>
+        <v>246.68</v>
       </c>
       <c r="K50" t="n">
-        <v>350.91</v>
+        <v>320.59</v>
       </c>
       <c r="L50" t="n">
-        <v>442.76</v>
+        <v>404.52</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>35.89</v>
+        <v>31.13</v>
       </c>
       <c r="K51" t="n">
-        <v>-444.33</v>
+        <v>-385.38</v>
       </c>
       <c r="L51" t="n">
-        <v>445.77</v>
+        <v>386.63</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>-72.92</v>
+        <v>-105.19</v>
       </c>
       <c r="K52" t="n">
-        <v>-18.85</v>
+        <v>-27.19</v>
       </c>
       <c r="L52" t="n">
-        <v>75.31</v>
+        <v>108.64</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>251.14</v>
+        <v>248.29</v>
       </c>
       <c r="K53" t="n">
-        <v>-356.02</v>
+        <v>-351.99</v>
       </c>
       <c r="L53" t="n">
-        <v>435.69</v>
+        <v>430.75</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>38.64</v>
+        <v>77.39</v>
       </c>
       <c r="K54" t="n">
-        <v>-57.39</v>
+        <v>-114.95</v>
       </c>
       <c r="L54" t="n">
-        <v>69.18000000000001</v>
+        <v>138.58</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>31.43</v>
+        <v>33.07</v>
       </c>
       <c r="K55" t="n">
-        <v>-231.46</v>
+        <v>-243.5</v>
       </c>
       <c r="L55" t="n">
-        <v>233.59</v>
+        <v>245.74</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>19</v>
       </c>
       <c r="J56" t="n">
-        <v>-696.0599999999999</v>
+        <v>-777.51</v>
       </c>
       <c r="K56" t="n">
-        <v>-276.89</v>
+        <v>-309.29</v>
       </c>
       <c r="L56" t="n">
-        <v>749.11</v>
+        <v>836.77</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>258.92</v>
+        <v>294.18</v>
       </c>
       <c r="K57" t="n">
-        <v>-488.45</v>
+        <v>-554.96</v>
       </c>
       <c r="L57" t="n">
-        <v>552.83</v>
+        <v>628.11</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>-61.81</v>
+        <v>-64.31</v>
       </c>
       <c r="K58" t="n">
-        <v>658.42</v>
+        <v>685.09</v>
       </c>
       <c r="L58" t="n">
-        <v>661.3200000000001</v>
+        <v>688.11</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>-15.16</v>
+        <v>-15.11</v>
       </c>
       <c r="K59" t="n">
-        <v>-79.84</v>
+        <v>-79.56999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>81.27</v>
+        <v>80.98999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>17.41</v>
+        <v>14.88</v>
       </c>
       <c r="K60" t="n">
-        <v>-94.34</v>
+        <v>-80.64</v>
       </c>
       <c r="L60" t="n">
-        <v>95.94</v>
+        <v>82</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-239.39</v>
+        <v>-150.49</v>
       </c>
       <c r="K61" t="n">
-        <v>75.98</v>
+        <v>47.77</v>
       </c>
       <c r="L61" t="n">
-        <v>251.15</v>
+        <v>157.89</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>87.68000000000001</v>
+        <v>81.17</v>
       </c>
       <c r="K62" t="n">
-        <v>-63.78</v>
+        <v>-59.04</v>
       </c>
       <c r="L62" t="n">
-        <v>108.42</v>
+        <v>100.37</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-89.43000000000001</v>
+        <v>-68.3</v>
       </c>
       <c r="K63" t="n">
-        <v>-156.33</v>
+        <v>-119.4</v>
       </c>
       <c r="L63" t="n">
-        <v>180.1</v>
+        <v>137.56</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-48.16</v>
+        <v>-41.72</v>
       </c>
       <c r="K64" t="n">
-        <v>201.61</v>
+        <v>174.65</v>
       </c>
       <c r="L64" t="n">
-        <v>207.29</v>
+        <v>179.57</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>148.33</v>
+        <v>148.32</v>
       </c>
       <c r="K65" t="n">
         <v>94.83</v>
       </c>
       <c r="L65" t="n">
-        <v>176.05</v>
+        <v>176.04</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-29.38</v>
+        <v>-27.41</v>
       </c>
       <c r="K66" t="n">
-        <v>303.64</v>
+        <v>283.32</v>
       </c>
       <c r="L66" t="n">
-        <v>305.06</v>
+        <v>284.64</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>-30.59</v>
+        <v>-39.24</v>
       </c>
       <c r="K67" t="n">
-        <v>-121.07</v>
+        <v>-155.27</v>
       </c>
       <c r="L67" t="n">
-        <v>124.88</v>
+        <v>160.15</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>-80.52</v>
+        <v>-95.34999999999999</v>
       </c>
       <c r="K68" t="n">
-        <v>276.24</v>
+        <v>327.13</v>
       </c>
       <c r="L68" t="n">
-        <v>287.74</v>
+        <v>340.75</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>-72.76000000000001</v>
+        <v>-90.45999999999999</v>
       </c>
       <c r="K69" t="n">
-        <v>-211.53</v>
+        <v>-263</v>
       </c>
       <c r="L69" t="n">
-        <v>223.69</v>
+        <v>278.12</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>8.5</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="K70" t="n">
-        <v>419.53</v>
+        <v>413.42</v>
       </c>
       <c r="L70" t="n">
-        <v>419.62</v>
+        <v>413.51</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>-381.89</v>
+        <v>-531.5700000000001</v>
       </c>
       <c r="K71" t="n">
-        <v>84.19</v>
+        <v>117.18</v>
       </c>
       <c r="L71" t="n">
-        <v>391.06</v>
+        <v>544.34</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>28.16</v>
+        <v>33.63</v>
       </c>
       <c r="K72" t="n">
-        <v>383.76</v>
+        <v>458.29</v>
       </c>
       <c r="L72" t="n">
-        <v>384.79</v>
+        <v>459.53</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-221.05</v>
+        <v>-287.1</v>
       </c>
       <c r="K73" t="n">
-        <v>220.24</v>
+        <v>286.04</v>
       </c>
       <c r="L73" t="n">
-        <v>312.04</v>
+        <v>405.27</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-88.73</v>
+        <v>-64.36</v>
       </c>
       <c r="K74" t="n">
-        <v>122.9</v>
+        <v>89.13</v>
       </c>
       <c r="L74" t="n">
-        <v>151.59</v>
+        <v>109.94</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>-62.44</v>
+        <v>-87.56999999999999</v>
       </c>
       <c r="K75" t="n">
-        <v>2.21</v>
+        <v>3.1</v>
       </c>
       <c r="L75" t="n">
-        <v>62.47</v>
+        <v>87.63</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>18</v>
       </c>
       <c r="J76" t="n">
-        <v>-53.71</v>
+        <v>-61.81</v>
       </c>
       <c r="K76" t="n">
-        <v>-34.34</v>
+        <v>-39.51</v>
       </c>
       <c r="L76" t="n">
-        <v>63.75</v>
+        <v>73.36</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-47.58</v>
+        <v>-71.13</v>
       </c>
       <c r="K77" t="n">
-        <v>-6.62</v>
+        <v>-9.9</v>
       </c>
       <c r="L77" t="n">
-        <v>48.04</v>
+        <v>71.81999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>23.1</v>
+        <v>17.98</v>
       </c>
       <c r="K78" t="n">
-        <v>189.18</v>
+        <v>147.22</v>
       </c>
       <c r="L78" t="n">
-        <v>190.59</v>
+        <v>148.31</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>-2.49</v>
+        <v>-2.33</v>
       </c>
       <c r="K79" t="n">
-        <v>155.76</v>
+        <v>145.65</v>
       </c>
       <c r="L79" t="n">
-        <v>155.78</v>
+        <v>145.67</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>18</v>
       </c>
       <c r="J80" t="n">
-        <v>-218.85</v>
+        <v>-213.15</v>
       </c>
       <c r="K80" t="n">
-        <v>-135.55</v>
+        <v>-132.02</v>
       </c>
       <c r="L80" t="n">
-        <v>257.42</v>
+        <v>250.73</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>82.69</v>
+        <v>74.87</v>
       </c>
       <c r="K81" t="n">
-        <v>274.64</v>
+        <v>248.66</v>
       </c>
       <c r="L81" t="n">
-        <v>286.82</v>
+        <v>259.69</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-80.33</v>
+        <v>-89.7</v>
       </c>
       <c r="K82" t="n">
-        <v>109.93</v>
+        <v>122.75</v>
       </c>
       <c r="L82" t="n">
-        <v>136.15</v>
+        <v>152.03</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>122.98</v>
+        <v>153.53</v>
       </c>
       <c r="K83" t="n">
-        <v>-137.39</v>
+        <v>-171.52</v>
       </c>
       <c r="L83" t="n">
-        <v>184.39</v>
+        <v>230.2</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>-198.63</v>
+        <v>-269.54</v>
       </c>
       <c r="K84" t="n">
-        <v>51.82</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="L84" t="n">
-        <v>205.28</v>
+        <v>278.56</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>-197.39</v>
+        <v>-208.53</v>
       </c>
       <c r="K85" t="n">
-        <v>-152.17</v>
+        <v>-160.76</v>
       </c>
       <c r="L85" t="n">
-        <v>249.24</v>
+        <v>263.31</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-364.71</v>
+        <v>-534.54</v>
       </c>
       <c r="K86" t="n">
-        <v>58.41</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="L86" t="n">
-        <v>369.36</v>
+        <v>541.36</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>762.86</v>
+        <v>740.97</v>
       </c>
       <c r="K87" t="n">
-        <v>346.3</v>
+        <v>336.36</v>
       </c>
       <c r="L87" t="n">
-        <v>837.78</v>
+        <v>813.74</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>73.42</v>
+        <v>204.24</v>
       </c>
       <c r="K88" t="n">
-        <v>113.33</v>
+        <v>315.25</v>
       </c>
       <c r="L88" t="n">
-        <v>135.03</v>
+        <v>375.63</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-17.xlsx
+++ b/output/2025-07-17.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>-133.99</v>
+        <v>-114.69</v>
       </c>
       <c r="K14" t="n">
-        <v>-4.59</v>
+        <v>-3.93</v>
       </c>
       <c r="L14" t="n">
-        <v>134.07</v>
+        <v>114.75</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-24.7</v>
+        <v>-19.09</v>
       </c>
       <c r="K15" t="n">
-        <v>-67.95999999999999</v>
+        <v>-52.51</v>
       </c>
       <c r="L15" t="n">
-        <v>72.31</v>
+        <v>55.87</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>50.6</v>
+        <v>38.26</v>
       </c>
       <c r="K16" t="n">
-        <v>96.56999999999999</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>109.02</v>
+        <v>82.42</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>-19.44</v>
+        <v>-13.49</v>
       </c>
       <c r="K17" t="n">
-        <v>-168.55</v>
+        <v>-116.94</v>
       </c>
       <c r="L17" t="n">
-        <v>169.67</v>
+        <v>117.72</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>41.46</v>
+        <v>30.34</v>
       </c>
       <c r="K18" t="n">
-        <v>125.74</v>
+        <v>92</v>
       </c>
       <c r="L18" t="n">
-        <v>132.4</v>
+        <v>96.88</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>61.15</v>
+        <v>45.87</v>
       </c>
       <c r="K19" t="n">
-        <v>76.69</v>
+        <v>57.53</v>
       </c>
       <c r="L19" t="n">
-        <v>98.09</v>
+        <v>73.58</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>114.69</v>
+        <v>76.55</v>
       </c>
       <c r="K20" t="n">
-        <v>-140.46</v>
+        <v>-93.75</v>
       </c>
       <c r="L20" t="n">
-        <v>181.33</v>
+        <v>121.03</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>-8.08</v>
+        <v>-5.14</v>
       </c>
       <c r="K21" t="n">
-        <v>-133.97</v>
+        <v>-85.25</v>
       </c>
       <c r="L21" t="n">
-        <v>134.21</v>
+        <v>85.40000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-127.25</v>
+        <v>-88.31</v>
       </c>
       <c r="K22" t="n">
-        <v>36.54</v>
+        <v>25.35</v>
       </c>
       <c r="L22" t="n">
-        <v>132.4</v>
+        <v>91.87</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-281.5</v>
+        <v>-169.58</v>
       </c>
       <c r="K23" t="n">
-        <v>17.72</v>
+        <v>10.67</v>
       </c>
       <c r="L23" t="n">
-        <v>282.06</v>
+        <v>169.92</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>18</v>
       </c>
       <c r="J24" t="n">
-        <v>308.37</v>
+        <v>152.75</v>
       </c>
       <c r="K24" t="n">
-        <v>22.74</v>
+        <v>11.27</v>
       </c>
       <c r="L24" t="n">
-        <v>309.21</v>
+        <v>153.17</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>127</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>244.93</v>
+        <v>145.68</v>
       </c>
       <c r="L25" t="n">
-        <v>275.9</v>
+        <v>164.1</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-48.13</v>
+        <v>-27.15</v>
       </c>
       <c r="K26" t="n">
-        <v>468.96</v>
+        <v>264.55</v>
       </c>
       <c r="L26" t="n">
-        <v>471.43</v>
+        <v>265.94</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>-631.63</v>
+        <v>-304.14</v>
       </c>
       <c r="K27" t="n">
-        <v>-57.61</v>
+        <v>-27.74</v>
       </c>
       <c r="L27" t="n">
-        <v>634.25</v>
+        <v>305.4</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>-182.32</v>
+        <v>-94.09</v>
       </c>
       <c r="K28" t="n">
-        <v>281.7</v>
+        <v>145.38</v>
       </c>
       <c r="L28" t="n">
-        <v>335.55</v>
+        <v>173.17</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-48.65</v>
+        <v>-39.41</v>
       </c>
       <c r="K29" t="n">
-        <v>-38.1</v>
+        <v>-30.86</v>
       </c>
       <c r="L29" t="n">
-        <v>61.79</v>
+        <v>50.05</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-79.3</v>
+        <v>-68.54000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>26.96</v>
+        <v>23.3</v>
       </c>
       <c r="L30" t="n">
-        <v>83.76000000000001</v>
+        <v>72.39</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>-29.31</v>
+        <v>-24</v>
       </c>
       <c r="K31" t="n">
-        <v>46.87</v>
+        <v>38.39</v>
       </c>
       <c r="L31" t="n">
-        <v>55.28</v>
+        <v>45.28</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>105.11</v>
+        <v>76.65000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>-124.86</v>
+        <v>-91.05</v>
       </c>
       <c r="L32" t="n">
-        <v>163.21</v>
+        <v>119.02</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>34.75</v>
+        <v>26.98</v>
       </c>
       <c r="K33" t="n">
-        <v>157.39</v>
+        <v>122.24</v>
       </c>
       <c r="L33" t="n">
-        <v>161.18</v>
+        <v>125.18</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-168.21</v>
+        <v>-134.49</v>
       </c>
       <c r="K34" t="n">
-        <v>64.06</v>
+        <v>51.22</v>
       </c>
       <c r="L34" t="n">
-        <v>180</v>
+        <v>143.92</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-2.05</v>
+        <v>-1.25</v>
       </c>
       <c r="K35" t="n">
-        <v>279.57</v>
+        <v>170.45</v>
       </c>
       <c r="L35" t="n">
-        <v>279.57</v>
+        <v>170.45</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>174.61</v>
+        <v>103.61</v>
       </c>
       <c r="K36" t="n">
-        <v>36.76</v>
+        <v>21.81</v>
       </c>
       <c r="L36" t="n">
-        <v>178.43</v>
+        <v>105.88</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>-208.83</v>
+        <v>-150.59</v>
       </c>
       <c r="K37" t="n">
-        <v>-48.09</v>
+        <v>-34.68</v>
       </c>
       <c r="L37" t="n">
-        <v>214.3</v>
+        <v>154.53</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>88.36</v>
+        <v>46.56</v>
       </c>
       <c r="K38" t="n">
-        <v>271.53</v>
+        <v>143.07</v>
       </c>
       <c r="L38" t="n">
-        <v>285.54</v>
+        <v>150.46</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>362</v>
+        <v>208.97</v>
       </c>
       <c r="K39" t="n">
-        <v>-166.12</v>
+        <v>-95.90000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>398.3</v>
+        <v>229.93</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>-192.24</v>
+        <v>-106.77</v>
       </c>
       <c r="K40" t="n">
-        <v>417.4</v>
+        <v>231.82</v>
       </c>
       <c r="L40" t="n">
-        <v>459.54</v>
+        <v>255.22</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-324.67</v>
+        <v>-162.28</v>
       </c>
       <c r="K41" t="n">
-        <v>514.73</v>
+        <v>257.27</v>
       </c>
       <c r="L41" t="n">
-        <v>608.5700000000001</v>
+        <v>304.17</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-452.98</v>
+        <v>-216.66</v>
       </c>
       <c r="K42" t="n">
-        <v>158.25</v>
+        <v>75.69</v>
       </c>
       <c r="L42" t="n">
-        <v>479.83</v>
+        <v>229.51</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>21.58</v>
+        <v>11.76</v>
       </c>
       <c r="K43" t="n">
-        <v>468.52</v>
+        <v>255.34</v>
       </c>
       <c r="L43" t="n">
-        <v>469.01</v>
+        <v>255.61</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-108.99</v>
+        <v>-82.95</v>
       </c>
       <c r="K44" t="n">
-        <v>14.96</v>
+        <v>11.39</v>
       </c>
       <c r="L44" t="n">
-        <v>110.01</v>
+        <v>83.73</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-56.07</v>
+        <v>-47.8</v>
       </c>
       <c r="K45" t="n">
-        <v>-45.44</v>
+        <v>-38.74</v>
       </c>
       <c r="L45" t="n">
-        <v>72.17</v>
+        <v>61.53</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>71.78</v>
+        <v>65.22</v>
       </c>
       <c r="K46" t="n">
-        <v>-37.76</v>
+        <v>-34.31</v>
       </c>
       <c r="L46" t="n">
-        <v>81.09999999999999</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-55.12</v>
+        <v>-40.39</v>
       </c>
       <c r="K47" t="n">
-        <v>77.58</v>
+        <v>56.85</v>
       </c>
       <c r="L47" t="n">
-        <v>95.17</v>
+        <v>69.73999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>-61.93</v>
+        <v>-44.65</v>
       </c>
       <c r="K48" t="n">
-        <v>35.95</v>
+        <v>25.92</v>
       </c>
       <c r="L48" t="n">
-        <v>71.61</v>
+        <v>51.63</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>106.79</v>
+        <v>87.38</v>
       </c>
       <c r="K49" t="n">
-        <v>-44.15</v>
+        <v>-36.13</v>
       </c>
       <c r="L49" t="n">
-        <v>115.55</v>
+        <v>94.56</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>18</v>
       </c>
       <c r="J50" t="n">
-        <v>246.68</v>
+        <v>148.54</v>
       </c>
       <c r="K50" t="n">
-        <v>320.59</v>
+        <v>193.04</v>
       </c>
       <c r="L50" t="n">
-        <v>404.52</v>
+        <v>243.57</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>31.13</v>
+        <v>19.19</v>
       </c>
       <c r="K51" t="n">
-        <v>-385.38</v>
+        <v>-237.54</v>
       </c>
       <c r="L51" t="n">
-        <v>386.63</v>
+        <v>238.32</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>-105.19</v>
+        <v>-70.18000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>-27.19</v>
+        <v>-18.14</v>
       </c>
       <c r="L52" t="n">
-        <v>108.64</v>
+        <v>72.48999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>248.29</v>
+        <v>130.49</v>
       </c>
       <c r="K53" t="n">
-        <v>-351.99</v>
+        <v>-184.98</v>
       </c>
       <c r="L53" t="n">
-        <v>430.75</v>
+        <v>226.38</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>77.39</v>
+        <v>44.09</v>
       </c>
       <c r="K54" t="n">
-        <v>-114.95</v>
+        <v>-65.48999999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>138.58</v>
+        <v>78.95</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>33.07</v>
+        <v>20.39</v>
       </c>
       <c r="K55" t="n">
-        <v>-243.5</v>
+        <v>-150.1</v>
       </c>
       <c r="L55" t="n">
-        <v>245.74</v>
+        <v>151.48</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>19</v>
       </c>
       <c r="J56" t="n">
-        <v>-777.51</v>
+        <v>-372.56</v>
       </c>
       <c r="K56" t="n">
-        <v>-309.29</v>
+        <v>-148.2</v>
       </c>
       <c r="L56" t="n">
-        <v>836.77</v>
+        <v>400.95</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>294.18</v>
+        <v>137.6</v>
       </c>
       <c r="K57" t="n">
-        <v>-554.96</v>
+        <v>-259.58</v>
       </c>
       <c r="L57" t="n">
-        <v>628.11</v>
+        <v>293.8</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>-64.31</v>
+        <v>-31.97</v>
       </c>
       <c r="K58" t="n">
-        <v>685.09</v>
+        <v>340.62</v>
       </c>
       <c r="L58" t="n">
-        <v>688.11</v>
+        <v>342.12</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>-15.11</v>
+        <v>-12.55</v>
       </c>
       <c r="K59" t="n">
-        <v>-79.56999999999999</v>
+        <v>-66.12</v>
       </c>
       <c r="L59" t="n">
-        <v>80.98999999999999</v>
+        <v>67.31</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>14.88</v>
+        <v>11.86</v>
       </c>
       <c r="K60" t="n">
-        <v>-80.64</v>
+        <v>-64.27</v>
       </c>
       <c r="L60" t="n">
-        <v>82</v>
+        <v>65.34999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-150.49</v>
+        <v>-138.26</v>
       </c>
       <c r="K61" t="n">
-        <v>47.77</v>
+        <v>43.88</v>
       </c>
       <c r="L61" t="n">
-        <v>157.89</v>
+        <v>145.06</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>81.17</v>
+        <v>69.06</v>
       </c>
       <c r="K62" t="n">
-        <v>-59.04</v>
+        <v>-50.23</v>
       </c>
       <c r="L62" t="n">
-        <v>100.37</v>
+        <v>85.40000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-68.3</v>
+        <v>-58.32</v>
       </c>
       <c r="K63" t="n">
-        <v>-119.4</v>
+        <v>-101.95</v>
       </c>
       <c r="L63" t="n">
-        <v>137.56</v>
+        <v>117.46</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-41.72</v>
+        <v>-28.95</v>
       </c>
       <c r="K64" t="n">
-        <v>174.65</v>
+        <v>121.18</v>
       </c>
       <c r="L64" t="n">
-        <v>179.57</v>
+        <v>124.59</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>148.32</v>
+        <v>105.91</v>
       </c>
       <c r="K65" t="n">
-        <v>94.83</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>176.04</v>
+        <v>125.71</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-27.41</v>
+        <v>-16.31</v>
       </c>
       <c r="K66" t="n">
-        <v>283.32</v>
+        <v>168.62</v>
       </c>
       <c r="L66" t="n">
-        <v>284.64</v>
+        <v>169.41</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>-39.24</v>
+        <v>-23.85</v>
       </c>
       <c r="K67" t="n">
-        <v>-155.27</v>
+        <v>-94.37</v>
       </c>
       <c r="L67" t="n">
-        <v>160.15</v>
+        <v>97.33</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>-95.34999999999999</v>
+        <v>-48.72</v>
       </c>
       <c r="K68" t="n">
-        <v>327.13</v>
+        <v>167.13</v>
       </c>
       <c r="L68" t="n">
-        <v>340.75</v>
+        <v>174.09</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>-90.45999999999999</v>
+        <v>-48.91</v>
       </c>
       <c r="K69" t="n">
-        <v>-263</v>
+        <v>-142.21</v>
       </c>
       <c r="L69" t="n">
-        <v>278.12</v>
+        <v>150.39</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>8.380000000000001</v>
+        <v>5.03</v>
       </c>
       <c r="K70" t="n">
-        <v>413.42</v>
+        <v>248.26</v>
       </c>
       <c r="L70" t="n">
-        <v>413.51</v>
+        <v>248.31</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>-531.5700000000001</v>
+        <v>-250.26</v>
       </c>
       <c r="K71" t="n">
-        <v>117.18</v>
+        <v>55.17</v>
       </c>
       <c r="L71" t="n">
-        <v>544.34</v>
+        <v>256.27</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>33.63</v>
+        <v>17.55</v>
       </c>
       <c r="K72" t="n">
-        <v>458.29</v>
+        <v>239.14</v>
       </c>
       <c r="L72" t="n">
-        <v>459.53</v>
+        <v>239.78</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-287.1</v>
+        <v>-156.72</v>
       </c>
       <c r="K73" t="n">
-        <v>286.04</v>
+        <v>156.15</v>
       </c>
       <c r="L73" t="n">
-        <v>405.27</v>
+        <v>221.23</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-64.36</v>
+        <v>-57.42</v>
       </c>
       <c r="K74" t="n">
-        <v>89.13</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>109.94</v>
+        <v>98.09999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>-87.56999999999999</v>
+        <v>-64.06</v>
       </c>
       <c r="K75" t="n">
-        <v>3.1</v>
+        <v>2.27</v>
       </c>
       <c r="L75" t="n">
-        <v>87.63</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>18</v>
       </c>
       <c r="J76" t="n">
-        <v>-61.81</v>
+        <v>-42.68</v>
       </c>
       <c r="K76" t="n">
-        <v>-39.51</v>
+        <v>-27.28</v>
       </c>
       <c r="L76" t="n">
-        <v>73.36</v>
+        <v>50.65</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-71.13</v>
+        <v>-59.11</v>
       </c>
       <c r="K77" t="n">
-        <v>-9.9</v>
+        <v>-8.23</v>
       </c>
       <c r="L77" t="n">
-        <v>71.81999999999999</v>
+        <v>59.68</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>17.98</v>
+        <v>14.21</v>
       </c>
       <c r="K78" t="n">
-        <v>147.22</v>
+        <v>116.37</v>
       </c>
       <c r="L78" t="n">
-        <v>148.31</v>
+        <v>117.24</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>-2.33</v>
+        <v>-1.73</v>
       </c>
       <c r="K79" t="n">
-        <v>145.65</v>
+        <v>108.21</v>
       </c>
       <c r="L79" t="n">
-        <v>145.67</v>
+        <v>108.22</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>18</v>
       </c>
       <c r="J80" t="n">
-        <v>-213.15</v>
+        <v>-132.79</v>
       </c>
       <c r="K80" t="n">
-        <v>-132.02</v>
+        <v>-82.25</v>
       </c>
       <c r="L80" t="n">
-        <v>250.73</v>
+        <v>156.19</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>74.87</v>
+        <v>49.18</v>
       </c>
       <c r="K81" t="n">
-        <v>248.66</v>
+        <v>163.34</v>
       </c>
       <c r="L81" t="n">
-        <v>259.69</v>
+        <v>170.58</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-89.7</v>
+        <v>-61.52</v>
       </c>
       <c r="K82" t="n">
-        <v>122.75</v>
+        <v>84.19</v>
       </c>
       <c r="L82" t="n">
-        <v>152.03</v>
+        <v>104.28</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>153.53</v>
+        <v>92.52</v>
       </c>
       <c r="K83" t="n">
-        <v>-171.52</v>
+        <v>-103.35</v>
       </c>
       <c r="L83" t="n">
-        <v>230.2</v>
+        <v>138.71</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>-269.54</v>
+        <v>-144.65</v>
       </c>
       <c r="K84" t="n">
-        <v>70.31999999999999</v>
+        <v>37.74</v>
       </c>
       <c r="L84" t="n">
-        <v>278.56</v>
+        <v>149.49</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>-208.53</v>
+        <v>-127.34</v>
       </c>
       <c r="K85" t="n">
-        <v>-160.76</v>
+        <v>-98.16</v>
       </c>
       <c r="L85" t="n">
-        <v>263.31</v>
+        <v>160.78</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-534.54</v>
+        <v>-257.68</v>
       </c>
       <c r="K86" t="n">
-        <v>85.59999999999999</v>
+        <v>41.27</v>
       </c>
       <c r="L86" t="n">
-        <v>541.36</v>
+        <v>260.97</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>740.97</v>
+        <v>409.84</v>
       </c>
       <c r="K87" t="n">
-        <v>336.36</v>
+        <v>186.05</v>
       </c>
       <c r="L87" t="n">
-        <v>813.74</v>
+        <v>450.09</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>204.24</v>
+        <v>102.9</v>
       </c>
       <c r="K88" t="n">
-        <v>315.25</v>
+        <v>158.84</v>
       </c>
       <c r="L88" t="n">
-        <v>375.63</v>
+        <v>189.26</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-17.xlsx
+++ b/output/2025-07-17.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>-114.69</v>
+        <v>-119.4</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.93</v>
+        <v>-4.09</v>
       </c>
       <c r="L14" t="n">
-        <v>114.75</v>
+        <v>119.47</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-19.09</v>
+        <v>-19.83</v>
       </c>
       <c r="K15" t="n">
-        <v>-52.51</v>
+        <v>-54.56</v>
       </c>
       <c r="L15" t="n">
-        <v>55.87</v>
+        <v>58.06</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>38.26</v>
+        <v>40.29</v>
       </c>
       <c r="K16" t="n">
-        <v>73.01000000000001</v>
+        <v>76.89</v>
       </c>
       <c r="L16" t="n">
-        <v>82.42</v>
+        <v>86.81</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>-13.49</v>
+        <v>-14.77</v>
       </c>
       <c r="K17" t="n">
-        <v>-116.94</v>
+        <v>-128.05</v>
       </c>
       <c r="L17" t="n">
-        <v>117.72</v>
+        <v>128.9</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>30.34</v>
+        <v>32.9</v>
       </c>
       <c r="K18" t="n">
-        <v>92</v>
+        <v>99.76000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>96.88</v>
+        <v>105.05</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>45.87</v>
+        <v>49.73</v>
       </c>
       <c r="K19" t="n">
-        <v>57.53</v>
+        <v>62.36</v>
       </c>
       <c r="L19" t="n">
-        <v>73.58</v>
+        <v>79.76000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>76.55</v>
+        <v>85.45999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>-93.75</v>
+        <v>-104.66</v>
       </c>
       <c r="L20" t="n">
-        <v>121.03</v>
+        <v>135.12</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>-5.14</v>
+        <v>-5.88</v>
       </c>
       <c r="K21" t="n">
-        <v>-85.25</v>
+        <v>-97.48</v>
       </c>
       <c r="L21" t="n">
-        <v>85.40000000000001</v>
+        <v>97.66</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-88.31</v>
+        <v>-99.19</v>
       </c>
       <c r="K22" t="n">
-        <v>25.35</v>
+        <v>28.48</v>
       </c>
       <c r="L22" t="n">
-        <v>91.87</v>
+        <v>103.2</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-169.58</v>
+        <v>-198.94</v>
       </c>
       <c r="K23" t="n">
-        <v>10.67</v>
+        <v>12.52</v>
       </c>
       <c r="L23" t="n">
-        <v>169.92</v>
+        <v>199.34</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>18</v>
       </c>
       <c r="J24" t="n">
-        <v>152.75</v>
+        <v>181.52</v>
       </c>
       <c r="K24" t="n">
-        <v>11.27</v>
+        <v>13.39</v>
       </c>
       <c r="L24" t="n">
-        <v>153.17</v>
+        <v>182.02</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>75.54000000000001</v>
+        <v>88.91</v>
       </c>
       <c r="K25" t="n">
-        <v>145.68</v>
+        <v>171.47</v>
       </c>
       <c r="L25" t="n">
-        <v>164.1</v>
+        <v>193.15</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-27.15</v>
+        <v>-31.46</v>
       </c>
       <c r="K26" t="n">
-        <v>264.55</v>
+        <v>306.55</v>
       </c>
       <c r="L26" t="n">
-        <v>265.94</v>
+        <v>308.16</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>-304.14</v>
+        <v>-362.33</v>
       </c>
       <c r="K27" t="n">
-        <v>-27.74</v>
+        <v>-33.05</v>
       </c>
       <c r="L27" t="n">
-        <v>305.4</v>
+        <v>363.84</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>-94.09</v>
+        <v>-111.55</v>
       </c>
       <c r="K28" t="n">
-        <v>145.38</v>
+        <v>172.35</v>
       </c>
       <c r="L28" t="n">
-        <v>173.17</v>
+        <v>205.3</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-39.41</v>
+        <v>-41.92</v>
       </c>
       <c r="K29" t="n">
-        <v>-30.86</v>
+        <v>-32.83</v>
       </c>
       <c r="L29" t="n">
-        <v>50.05</v>
+        <v>53.25</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-68.54000000000001</v>
+        <v>-71.78</v>
       </c>
       <c r="K30" t="n">
-        <v>23.3</v>
+        <v>24.4</v>
       </c>
       <c r="L30" t="n">
-        <v>72.39</v>
+        <v>75.81999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>-24</v>
+        <v>-25.27</v>
       </c>
       <c r="K31" t="n">
-        <v>38.39</v>
+        <v>40.4</v>
       </c>
       <c r="L31" t="n">
-        <v>45.28</v>
+        <v>47.65</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>76.65000000000001</v>
+        <v>83.87</v>
       </c>
       <c r="K32" t="n">
-        <v>-91.05</v>
+        <v>-99.63</v>
       </c>
       <c r="L32" t="n">
-        <v>119.02</v>
+        <v>130.23</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>26.98</v>
+        <v>29.08</v>
       </c>
       <c r="K33" t="n">
-        <v>122.24</v>
+        <v>131.74</v>
       </c>
       <c r="L33" t="n">
-        <v>125.18</v>
+        <v>134.91</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-134.49</v>
+        <v>-145.27</v>
       </c>
       <c r="K34" t="n">
-        <v>51.22</v>
+        <v>55.33</v>
       </c>
       <c r="L34" t="n">
-        <v>143.92</v>
+        <v>155.45</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-1.25</v>
+        <v>-1.44</v>
       </c>
       <c r="K35" t="n">
-        <v>170.45</v>
+        <v>196.15</v>
       </c>
       <c r="L35" t="n">
-        <v>170.45</v>
+        <v>196.15</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>103.61</v>
+        <v>118.8</v>
       </c>
       <c r="K36" t="n">
-        <v>21.81</v>
+        <v>25.01</v>
       </c>
       <c r="L36" t="n">
-        <v>105.88</v>
+        <v>121.41</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>-150.59</v>
+        <v>-169.26</v>
       </c>
       <c r="K37" t="n">
-        <v>-34.68</v>
+        <v>-38.98</v>
       </c>
       <c r="L37" t="n">
-        <v>154.53</v>
+        <v>173.69</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>46.56</v>
+        <v>54.86</v>
       </c>
       <c r="K38" t="n">
-        <v>143.07</v>
+        <v>168.61</v>
       </c>
       <c r="L38" t="n">
-        <v>150.46</v>
+        <v>177.31</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>208.97</v>
+        <v>244.56</v>
       </c>
       <c r="K39" t="n">
-        <v>-95.90000000000001</v>
+        <v>-112.23</v>
       </c>
       <c r="L39" t="n">
-        <v>229.93</v>
+        <v>269.08</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>-106.77</v>
+        <v>-125.19</v>
       </c>
       <c r="K40" t="n">
-        <v>231.82</v>
+        <v>271.81</v>
       </c>
       <c r="L40" t="n">
-        <v>255.22</v>
+        <v>299.25</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-162.28</v>
+        <v>-191.65</v>
       </c>
       <c r="K41" t="n">
-        <v>257.27</v>
+        <v>303.84</v>
       </c>
       <c r="L41" t="n">
-        <v>304.17</v>
+        <v>359.24</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-216.66</v>
+        <v>-260.82</v>
       </c>
       <c r="K42" t="n">
-        <v>75.69</v>
+        <v>91.12</v>
       </c>
       <c r="L42" t="n">
-        <v>229.51</v>
+        <v>276.27</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>11.76</v>
+        <v>13.75</v>
       </c>
       <c r="K43" t="n">
-        <v>255.34</v>
+        <v>298.45</v>
       </c>
       <c r="L43" t="n">
-        <v>255.61</v>
+        <v>298.77</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-82.95</v>
+        <v>-88.31</v>
       </c>
       <c r="K44" t="n">
-        <v>11.39</v>
+        <v>12.13</v>
       </c>
       <c r="L44" t="n">
-        <v>83.73</v>
+        <v>89.14</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-47.8</v>
+        <v>-50.16</v>
       </c>
       <c r="K45" t="n">
-        <v>-38.74</v>
+        <v>-40.65</v>
       </c>
       <c r="L45" t="n">
-        <v>61.53</v>
+        <v>64.56</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>65.22</v>
+        <v>68.25</v>
       </c>
       <c r="K46" t="n">
-        <v>-34.31</v>
+        <v>-35.91</v>
       </c>
       <c r="L46" t="n">
-        <v>73.7</v>
+        <v>77.12</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-40.39</v>
+        <v>-44.41</v>
       </c>
       <c r="K47" t="n">
-        <v>56.85</v>
+        <v>62.5</v>
       </c>
       <c r="L47" t="n">
-        <v>69.73999999999999</v>
+        <v>76.67</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>-44.65</v>
+        <v>-48.12</v>
       </c>
       <c r="K48" t="n">
-        <v>25.92</v>
+        <v>27.93</v>
       </c>
       <c r="L48" t="n">
-        <v>51.63</v>
+        <v>55.64</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>87.38</v>
+        <v>92.25</v>
       </c>
       <c r="K49" t="n">
-        <v>-36.13</v>
+        <v>-38.14</v>
       </c>
       <c r="L49" t="n">
-        <v>94.56</v>
+        <v>99.83</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>18</v>
       </c>
       <c r="J50" t="n">
-        <v>148.54</v>
+        <v>170.52</v>
       </c>
       <c r="K50" t="n">
-        <v>193.04</v>
+        <v>221.61</v>
       </c>
       <c r="L50" t="n">
-        <v>243.57</v>
+        <v>279.62</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>19.19</v>
+        <v>21.87</v>
       </c>
       <c r="K51" t="n">
-        <v>-237.54</v>
+        <v>-270.72</v>
       </c>
       <c r="L51" t="n">
-        <v>238.32</v>
+        <v>271.6</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>-70.18000000000001</v>
+        <v>-78.53</v>
       </c>
       <c r="K52" t="n">
-        <v>-18.14</v>
+        <v>-20.3</v>
       </c>
       <c r="L52" t="n">
-        <v>72.48999999999999</v>
+        <v>81.11</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>130.49</v>
+        <v>152.26</v>
       </c>
       <c r="K53" t="n">
-        <v>-184.98</v>
+        <v>-215.86</v>
       </c>
       <c r="L53" t="n">
-        <v>226.38</v>
+        <v>264.16</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>44.09</v>
+        <v>50.73</v>
       </c>
       <c r="K54" t="n">
-        <v>-65.48999999999999</v>
+        <v>-75.34</v>
       </c>
       <c r="L54" t="n">
-        <v>78.95</v>
+        <v>90.83</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>20.39</v>
+        <v>23.46</v>
       </c>
       <c r="K55" t="n">
-        <v>-150.1</v>
+        <v>-172.76</v>
       </c>
       <c r="L55" t="n">
-        <v>151.48</v>
+        <v>174.35</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>19</v>
       </c>
       <c r="J56" t="n">
-        <v>-372.56</v>
+        <v>-438.54</v>
       </c>
       <c r="K56" t="n">
-        <v>-148.2</v>
+        <v>-174.45</v>
       </c>
       <c r="L56" t="n">
-        <v>400.95</v>
+        <v>471.96</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>137.6</v>
+        <v>164.62</v>
       </c>
       <c r="K57" t="n">
-        <v>-259.58</v>
+        <v>-310.55</v>
       </c>
       <c r="L57" t="n">
-        <v>293.8</v>
+        <v>351.48</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>-31.97</v>
+        <v>-38.12</v>
       </c>
       <c r="K58" t="n">
-        <v>340.62</v>
+        <v>406.04</v>
       </c>
       <c r="L58" t="n">
-        <v>342.12</v>
+        <v>407.82</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>-12.55</v>
+        <v>-13.13</v>
       </c>
       <c r="K59" t="n">
-        <v>-66.12</v>
+        <v>-69.17</v>
       </c>
       <c r="L59" t="n">
-        <v>67.31</v>
+        <v>70.41</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>11.86</v>
+        <v>12.27</v>
       </c>
       <c r="K60" t="n">
-        <v>-64.27</v>
+        <v>-66.47</v>
       </c>
       <c r="L60" t="n">
-        <v>65.34999999999999</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-138.26</v>
+        <v>-142.85</v>
       </c>
       <c r="K61" t="n">
-        <v>43.88</v>
+        <v>45.34</v>
       </c>
       <c r="L61" t="n">
-        <v>145.06</v>
+        <v>149.88</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>69.06</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>-50.23</v>
+        <v>-53.5</v>
       </c>
       <c r="L62" t="n">
-        <v>85.40000000000001</v>
+        <v>90.94</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-58.32</v>
+        <v>-61.65</v>
       </c>
       <c r="K63" t="n">
-        <v>-101.95</v>
+        <v>-107.77</v>
       </c>
       <c r="L63" t="n">
-        <v>117.46</v>
+        <v>124.16</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-28.95</v>
+        <v>-31.83</v>
       </c>
       <c r="K64" t="n">
-        <v>121.18</v>
+        <v>133.23</v>
       </c>
       <c r="L64" t="n">
-        <v>124.59</v>
+        <v>136.98</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>105.91</v>
+        <v>119.37</v>
       </c>
       <c r="K65" t="n">
-        <v>67.70999999999999</v>
+        <v>76.31</v>
       </c>
       <c r="L65" t="n">
-        <v>125.71</v>
+        <v>141.68</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-16.31</v>
+        <v>-18.59</v>
       </c>
       <c r="K66" t="n">
-        <v>168.62</v>
+        <v>192.13</v>
       </c>
       <c r="L66" t="n">
-        <v>169.41</v>
+        <v>193.03</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>-23.85</v>
+        <v>-27.29</v>
       </c>
       <c r="K67" t="n">
-        <v>-94.37</v>
+        <v>-108.01</v>
       </c>
       <c r="L67" t="n">
-        <v>97.33</v>
+        <v>111.4</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>-48.72</v>
+        <v>-58.1</v>
       </c>
       <c r="K68" t="n">
-        <v>167.13</v>
+        <v>199.34</v>
       </c>
       <c r="L68" t="n">
-        <v>174.09</v>
+        <v>207.63</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>-48.91</v>
+        <v>-58.03</v>
       </c>
       <c r="K69" t="n">
-        <v>-142.21</v>
+        <v>-168.72</v>
       </c>
       <c r="L69" t="n">
-        <v>150.39</v>
+        <v>178.42</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>5.03</v>
+        <v>5.78</v>
       </c>
       <c r="K70" t="n">
-        <v>248.26</v>
+        <v>285.4</v>
       </c>
       <c r="L70" t="n">
-        <v>248.31</v>
+        <v>285.46</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>-250.26</v>
+        <v>-299.93</v>
       </c>
       <c r="K71" t="n">
-        <v>55.17</v>
+        <v>66.12</v>
       </c>
       <c r="L71" t="n">
-        <v>256.27</v>
+        <v>307.13</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>17.55</v>
+        <v>20.82</v>
       </c>
       <c r="K72" t="n">
-        <v>239.14</v>
+        <v>283.74</v>
       </c>
       <c r="L72" t="n">
-        <v>239.78</v>
+        <v>284.5</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-156.72</v>
+        <v>-181.63</v>
       </c>
       <c r="K73" t="n">
-        <v>156.15</v>
+        <v>180.96</v>
       </c>
       <c r="L73" t="n">
-        <v>221.23</v>
+        <v>256.39</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-57.42</v>
+        <v>-59.81</v>
       </c>
       <c r="K74" t="n">
-        <v>79.54000000000001</v>
+        <v>82.84</v>
       </c>
       <c r="L74" t="n">
-        <v>98.09999999999999</v>
+        <v>102.17</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>-64.06</v>
+        <v>-68.42</v>
       </c>
       <c r="K75" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="L75" t="n">
-        <v>64.09999999999999</v>
+        <v>68.45999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>18</v>
       </c>
       <c r="J76" t="n">
-        <v>-42.68</v>
+        <v>-45.78</v>
       </c>
       <c r="K76" t="n">
-        <v>-27.28</v>
+        <v>-29.27</v>
       </c>
       <c r="L76" t="n">
-        <v>50.65</v>
+        <v>54.33</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-59.11</v>
+        <v>-63.13</v>
       </c>
       <c r="K77" t="n">
-        <v>-8.23</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>59.68</v>
+        <v>63.73</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>14.21</v>
+        <v>15.21</v>
       </c>
       <c r="K78" t="n">
-        <v>116.37</v>
+        <v>124.57</v>
       </c>
       <c r="L78" t="n">
-        <v>117.24</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>-1.73</v>
+        <v>-1.87</v>
       </c>
       <c r="K79" t="n">
-        <v>108.21</v>
+        <v>117.11</v>
       </c>
       <c r="L79" t="n">
-        <v>108.22</v>
+        <v>117.13</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>18</v>
       </c>
       <c r="J80" t="n">
-        <v>-132.79</v>
+        <v>-150.97</v>
       </c>
       <c r="K80" t="n">
-        <v>-82.25</v>
+        <v>-93.51000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>156.19</v>
+        <v>177.58</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>49.18</v>
+        <v>56.16</v>
       </c>
       <c r="K81" t="n">
-        <v>163.34</v>
+        <v>186.51</v>
       </c>
       <c r="L81" t="n">
-        <v>170.58</v>
+        <v>194.79</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-61.52</v>
+        <v>-69</v>
       </c>
       <c r="K82" t="n">
-        <v>84.19</v>
+        <v>94.42</v>
       </c>
       <c r="L82" t="n">
-        <v>104.28</v>
+        <v>116.95</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>92.52</v>
+        <v>107.53</v>
       </c>
       <c r="K83" t="n">
-        <v>-103.35</v>
+        <v>-120.13</v>
       </c>
       <c r="L83" t="n">
-        <v>138.71</v>
+        <v>161.23</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>-144.65</v>
+        <v>-171.61</v>
       </c>
       <c r="K84" t="n">
-        <v>37.74</v>
+        <v>44.77</v>
       </c>
       <c r="L84" t="n">
-        <v>149.49</v>
+        <v>177.35</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>-127.34</v>
+        <v>-149.34</v>
       </c>
       <c r="K85" t="n">
-        <v>-98.16</v>
+        <v>-115.13</v>
       </c>
       <c r="L85" t="n">
-        <v>160.78</v>
+        <v>188.56</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-257.68</v>
+        <v>-302.76</v>
       </c>
       <c r="K86" t="n">
-        <v>41.27</v>
+        <v>48.49</v>
       </c>
       <c r="L86" t="n">
-        <v>260.97</v>
+        <v>306.62</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>409.84</v>
+        <v>473.76</v>
       </c>
       <c r="K87" t="n">
-        <v>186.05</v>
+        <v>215.06</v>
       </c>
       <c r="L87" t="n">
-        <v>450.09</v>
+        <v>520.29</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>102.9</v>
+        <v>120.47</v>
       </c>
       <c r="K88" t="n">
-        <v>158.84</v>
+        <v>185.95</v>
       </c>
       <c r="L88" t="n">
-        <v>189.26</v>
+        <v>221.57</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-17.xlsx
+++ b/output/2025-07-17.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>-119.4</v>
+        <v>-80.45999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>-4.09</v>
+        <v>-2.76</v>
       </c>
       <c r="L14" t="n">
-        <v>119.47</v>
+        <v>80.51000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-19.83</v>
+        <v>-14.87</v>
       </c>
       <c r="K15" t="n">
-        <v>-54.56</v>
+        <v>-40.92</v>
       </c>
       <c r="L15" t="n">
-        <v>58.06</v>
+        <v>43.54</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>40.29</v>
+        <v>29.99</v>
       </c>
       <c r="K16" t="n">
-        <v>76.89</v>
+        <v>57.22</v>
       </c>
       <c r="L16" t="n">
-        <v>86.81</v>
+        <v>64.61</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>-14.77</v>
+        <v>-10.66</v>
       </c>
       <c r="K17" t="n">
-        <v>-128.05</v>
+        <v>-92.41</v>
       </c>
       <c r="L17" t="n">
-        <v>128.9</v>
+        <v>93.02</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>32.9</v>
+        <v>22.45</v>
       </c>
       <c r="K18" t="n">
-        <v>99.76000000000001</v>
+        <v>68.09</v>
       </c>
       <c r="L18" t="n">
-        <v>105.05</v>
+        <v>71.69</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>49.73</v>
+        <v>35.99</v>
       </c>
       <c r="K19" t="n">
-        <v>62.36</v>
+        <v>45.14</v>
       </c>
       <c r="L19" t="n">
-        <v>79.76000000000001</v>
+        <v>57.74</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>85.45999999999999</v>
+        <v>64.09</v>
       </c>
       <c r="K20" t="n">
-        <v>-104.66</v>
+        <v>-78.48999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>135.12</v>
+        <v>101.34</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>-5.88</v>
+        <v>-3.94</v>
       </c>
       <c r="K21" t="n">
-        <v>-97.48</v>
+        <v>-65.3</v>
       </c>
       <c r="L21" t="n">
-        <v>97.66</v>
+        <v>65.42</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-99.19</v>
+        <v>-74.39</v>
       </c>
       <c r="K22" t="n">
-        <v>28.48</v>
+        <v>21.36</v>
       </c>
       <c r="L22" t="n">
-        <v>103.2</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-198.94</v>
+        <v>-144.08</v>
       </c>
       <c r="K23" t="n">
-        <v>12.52</v>
+        <v>9.07</v>
       </c>
       <c r="L23" t="n">
-        <v>199.34</v>
+        <v>144.37</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>18</v>
       </c>
       <c r="J24" t="n">
-        <v>181.52</v>
+        <v>136.14</v>
       </c>
       <c r="K24" t="n">
-        <v>13.39</v>
+        <v>10.04</v>
       </c>
       <c r="L24" t="n">
-        <v>182.02</v>
+        <v>136.51</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>88.91</v>
+        <v>62.49</v>
       </c>
       <c r="K25" t="n">
-        <v>171.47</v>
+        <v>120.51</v>
       </c>
       <c r="L25" t="n">
-        <v>193.15</v>
+        <v>135.74</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-31.46</v>
+        <v>-22.71</v>
       </c>
       <c r="K26" t="n">
-        <v>306.55</v>
+        <v>221.26</v>
       </c>
       <c r="L26" t="n">
-        <v>308.16</v>
+        <v>222.42</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>-362.33</v>
+        <v>-271.75</v>
       </c>
       <c r="K27" t="n">
-        <v>-33.05</v>
+        <v>-24.79</v>
       </c>
       <c r="L27" t="n">
-        <v>363.84</v>
+        <v>272.88</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>-111.55</v>
+        <v>-79.95</v>
       </c>
       <c r="K28" t="n">
-        <v>172.35</v>
+        <v>123.54</v>
       </c>
       <c r="L28" t="n">
-        <v>205.3</v>
+        <v>147.15</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-41.92</v>
+        <v>-28.25</v>
       </c>
       <c r="K29" t="n">
-        <v>-32.83</v>
+        <v>-22.13</v>
       </c>
       <c r="L29" t="n">
-        <v>53.25</v>
+        <v>35.88</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-71.78</v>
+        <v>-47.31</v>
       </c>
       <c r="K30" t="n">
-        <v>24.4</v>
+        <v>16.08</v>
       </c>
       <c r="L30" t="n">
-        <v>75.81999999999999</v>
+        <v>49.97</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>-25.27</v>
+        <v>-17.89</v>
       </c>
       <c r="K31" t="n">
-        <v>40.4</v>
+        <v>28.61</v>
       </c>
       <c r="L31" t="n">
-        <v>47.65</v>
+        <v>33.74</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>83.87</v>
+        <v>60.71</v>
       </c>
       <c r="K32" t="n">
-        <v>-99.63</v>
+        <v>-72.12</v>
       </c>
       <c r="L32" t="n">
-        <v>130.23</v>
+        <v>94.27</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>29.08</v>
+        <v>20.92</v>
       </c>
       <c r="K33" t="n">
-        <v>131.74</v>
+        <v>94.77</v>
       </c>
       <c r="L33" t="n">
-        <v>134.91</v>
+        <v>97.05</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-145.27</v>
+        <v>-100.55</v>
       </c>
       <c r="K34" t="n">
-        <v>55.33</v>
+        <v>38.29</v>
       </c>
       <c r="L34" t="n">
-        <v>155.45</v>
+        <v>107.6</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-1.44</v>
+        <v>-1.08</v>
       </c>
       <c r="K35" t="n">
-        <v>196.15</v>
+        <v>147.11</v>
       </c>
       <c r="L35" t="n">
-        <v>196.15</v>
+        <v>147.12</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>118.8</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>25.01</v>
+        <v>18.76</v>
       </c>
       <c r="L36" t="n">
-        <v>121.41</v>
+        <v>91.06</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>-169.26</v>
+        <v>-107.77</v>
       </c>
       <c r="K37" t="n">
-        <v>-38.98</v>
+        <v>-24.82</v>
       </c>
       <c r="L37" t="n">
-        <v>173.69</v>
+        <v>110.59</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>54.86</v>
+        <v>40.83</v>
       </c>
       <c r="K38" t="n">
-        <v>168.61</v>
+        <v>125.48</v>
       </c>
       <c r="L38" t="n">
-        <v>177.31</v>
+        <v>131.96</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>244.56</v>
+        <v>175.04</v>
       </c>
       <c r="K39" t="n">
-        <v>-112.23</v>
+        <v>-80.33</v>
       </c>
       <c r="L39" t="n">
-        <v>269.08</v>
+        <v>192.59</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>-125.19</v>
+        <v>-78.77</v>
       </c>
       <c r="K40" t="n">
-        <v>271.81</v>
+        <v>171.02</v>
       </c>
       <c r="L40" t="n">
-        <v>299.25</v>
+        <v>188.29</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-191.65</v>
+        <v>-141.99</v>
       </c>
       <c r="K41" t="n">
-        <v>303.84</v>
+        <v>225.12</v>
       </c>
       <c r="L41" t="n">
-        <v>359.24</v>
+        <v>266.16</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-260.82</v>
+        <v>-186.09</v>
       </c>
       <c r="K42" t="n">
-        <v>91.12</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>276.27</v>
+        <v>197.11</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>13.75</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>298.45</v>
+        <v>197.76</v>
       </c>
       <c r="L43" t="n">
-        <v>298.77</v>
+        <v>197.96</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-88.31</v>
+        <v>-55.4</v>
       </c>
       <c r="K44" t="n">
-        <v>12.13</v>
+        <v>7.61</v>
       </c>
       <c r="L44" t="n">
-        <v>89.14</v>
+        <v>55.92</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-50.16</v>
+        <v>-32.55</v>
       </c>
       <c r="K45" t="n">
-        <v>-40.65</v>
+        <v>-26.37</v>
       </c>
       <c r="L45" t="n">
-        <v>64.56</v>
+        <v>41.89</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>68.25</v>
+        <v>47.1</v>
       </c>
       <c r="K46" t="n">
-        <v>-35.91</v>
+        <v>-24.78</v>
       </c>
       <c r="L46" t="n">
-        <v>77.12</v>
+        <v>53.22</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-44.41</v>
+        <v>-30.39</v>
       </c>
       <c r="K47" t="n">
-        <v>62.5</v>
+        <v>42.77</v>
       </c>
       <c r="L47" t="n">
-        <v>76.67</v>
+        <v>52.47</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>-48.12</v>
+        <v>-36.09</v>
       </c>
       <c r="K48" t="n">
-        <v>27.93</v>
+        <v>20.95</v>
       </c>
       <c r="L48" t="n">
-        <v>55.64</v>
+        <v>41.73</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>92.25</v>
+        <v>69.19</v>
       </c>
       <c r="K49" t="n">
-        <v>-38.14</v>
+        <v>-28.61</v>
       </c>
       <c r="L49" t="n">
-        <v>99.83</v>
+        <v>74.87</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>18</v>
       </c>
       <c r="J50" t="n">
-        <v>170.52</v>
+        <v>107.65</v>
       </c>
       <c r="K50" t="n">
-        <v>221.61</v>
+        <v>139.9</v>
       </c>
       <c r="L50" t="n">
-        <v>279.62</v>
+        <v>176.52</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>21.87</v>
+        <v>14.47</v>
       </c>
       <c r="K51" t="n">
-        <v>-270.72</v>
+        <v>-179.12</v>
       </c>
       <c r="L51" t="n">
-        <v>271.6</v>
+        <v>179.7</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>-78.53</v>
+        <v>-58.89</v>
       </c>
       <c r="K52" t="n">
-        <v>-20.3</v>
+        <v>-15.22</v>
       </c>
       <c r="L52" t="n">
-        <v>81.11</v>
+        <v>60.83</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>152.26</v>
+        <v>111.63</v>
       </c>
       <c r="K53" t="n">
-        <v>-215.86</v>
+        <v>-158.25</v>
       </c>
       <c r="L53" t="n">
-        <v>264.16</v>
+        <v>193.66</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>50.73</v>
+        <v>38.04</v>
       </c>
       <c r="K54" t="n">
-        <v>-75.34</v>
+        <v>-56.51</v>
       </c>
       <c r="L54" t="n">
-        <v>90.83</v>
+        <v>68.12</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>23.46</v>
+        <v>16.75</v>
       </c>
       <c r="K55" t="n">
-        <v>-172.76</v>
+        <v>-123.36</v>
       </c>
       <c r="L55" t="n">
-        <v>174.35</v>
+        <v>124.5</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>19</v>
       </c>
       <c r="J56" t="n">
-        <v>-438.54</v>
+        <v>-281.92</v>
       </c>
       <c r="K56" t="n">
-        <v>-174.45</v>
+        <v>-112.14</v>
       </c>
       <c r="L56" t="n">
-        <v>471.96</v>
+        <v>303.4</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>164.62</v>
+        <v>123.46</v>
       </c>
       <c r="K57" t="n">
-        <v>-310.55</v>
+        <v>-232.91</v>
       </c>
       <c r="L57" t="n">
-        <v>351.48</v>
+        <v>263.61</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>-38.12</v>
+        <v>-27.58</v>
       </c>
       <c r="K58" t="n">
-        <v>406.04</v>
+        <v>293.75</v>
       </c>
       <c r="L58" t="n">
-        <v>407.82</v>
+        <v>295.05</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>-13.13</v>
+        <v>-8.57</v>
       </c>
       <c r="K59" t="n">
-        <v>-69.17</v>
+        <v>-45.11</v>
       </c>
       <c r="L59" t="n">
-        <v>70.41</v>
+        <v>45.92</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>12.27</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>-66.47</v>
+        <v>-49.86</v>
       </c>
       <c r="L60" t="n">
-        <v>67.59999999999999</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-142.85</v>
+        <v>-93.65000000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>45.34</v>
+        <v>29.73</v>
       </c>
       <c r="L61" t="n">
-        <v>149.88</v>
+        <v>98.26000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>73.54000000000001</v>
+        <v>50.19</v>
       </c>
       <c r="K62" t="n">
-        <v>-53.5</v>
+        <v>-36.51</v>
       </c>
       <c r="L62" t="n">
-        <v>90.94</v>
+        <v>62.07</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-61.65</v>
+        <v>-42.67</v>
       </c>
       <c r="K63" t="n">
-        <v>-107.77</v>
+        <v>-74.59999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>124.16</v>
+        <v>85.94</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-31.83</v>
+        <v>-22.97</v>
       </c>
       <c r="K64" t="n">
-        <v>133.23</v>
+        <v>96.14</v>
       </c>
       <c r="L64" t="n">
-        <v>136.98</v>
+        <v>98.84999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>119.37</v>
+        <v>79.70999999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>76.31</v>
+        <v>50.96</v>
       </c>
       <c r="L65" t="n">
-        <v>141.68</v>
+        <v>94.61</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-18.59</v>
+        <v>-13.94</v>
       </c>
       <c r="K66" t="n">
-        <v>192.13</v>
+        <v>144.1</v>
       </c>
       <c r="L66" t="n">
-        <v>193.03</v>
+        <v>144.77</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>-27.29</v>
+        <v>-19.88</v>
       </c>
       <c r="K67" t="n">
-        <v>-108.01</v>
+        <v>-78.66</v>
       </c>
       <c r="L67" t="n">
-        <v>111.4</v>
+        <v>81.13</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>-58.1</v>
+        <v>-43.35</v>
       </c>
       <c r="K68" t="n">
-        <v>199.34</v>
+        <v>148.73</v>
       </c>
       <c r="L68" t="n">
-        <v>207.63</v>
+        <v>154.92</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>-58.03</v>
+        <v>-41.15</v>
       </c>
       <c r="K69" t="n">
-        <v>-168.72</v>
+        <v>-119.65</v>
       </c>
       <c r="L69" t="n">
-        <v>178.42</v>
+        <v>126.53</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>5.78</v>
+        <v>3.74</v>
       </c>
       <c r="K70" t="n">
-        <v>285.4</v>
+        <v>184.67</v>
       </c>
       <c r="L70" t="n">
-        <v>285.46</v>
+        <v>184.71</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>-299.93</v>
+        <v>-196.71</v>
       </c>
       <c r="K71" t="n">
-        <v>66.12</v>
+        <v>43.36</v>
       </c>
       <c r="L71" t="n">
-        <v>307.13</v>
+        <v>201.43</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>20.82</v>
+        <v>14.75</v>
       </c>
       <c r="K72" t="n">
-        <v>283.74</v>
+        <v>201.06</v>
       </c>
       <c r="L72" t="n">
-        <v>284.5</v>
+        <v>201.6</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-181.63</v>
+        <v>-120.85</v>
       </c>
       <c r="K73" t="n">
-        <v>180.96</v>
+        <v>120.41</v>
       </c>
       <c r="L73" t="n">
-        <v>256.39</v>
+        <v>170.59</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-59.81</v>
+        <v>-39.42</v>
       </c>
       <c r="K74" t="n">
-        <v>82.84</v>
+        <v>54.6</v>
       </c>
       <c r="L74" t="n">
-        <v>102.17</v>
+        <v>67.34</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>-68.42</v>
+        <v>-42.16</v>
       </c>
       <c r="K75" t="n">
-        <v>2.42</v>
+        <v>1.49</v>
       </c>
       <c r="L75" t="n">
-        <v>68.45999999999999</v>
+        <v>42.19</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>18</v>
       </c>
       <c r="J76" t="n">
-        <v>-45.78</v>
+        <v>-34.33</v>
       </c>
       <c r="K76" t="n">
-        <v>-29.27</v>
+        <v>-21.95</v>
       </c>
       <c r="L76" t="n">
-        <v>54.33</v>
+        <v>40.75</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-63.13</v>
+        <v>-41.18</v>
       </c>
       <c r="K77" t="n">
-        <v>-8.789999999999999</v>
+        <v>-5.73</v>
       </c>
       <c r="L77" t="n">
-        <v>63.73</v>
+        <v>41.58</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>15.21</v>
+        <v>11.15</v>
       </c>
       <c r="K78" t="n">
-        <v>124.57</v>
+        <v>91.31999999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>125.5</v>
+        <v>92</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>-1.87</v>
+        <v>-1.25</v>
       </c>
       <c r="K79" t="n">
-        <v>117.11</v>
+        <v>78.20999999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>117.13</v>
+        <v>78.22</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>18</v>
       </c>
       <c r="J80" t="n">
-        <v>-150.97</v>
+        <v>-103.74</v>
       </c>
       <c r="K80" t="n">
-        <v>-93.51000000000001</v>
+        <v>-64.26000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>177.58</v>
+        <v>122.03</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>56.16</v>
+        <v>37.98</v>
       </c>
       <c r="K81" t="n">
-        <v>186.51</v>
+        <v>126.13</v>
       </c>
       <c r="L81" t="n">
-        <v>194.79</v>
+        <v>131.72</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-69</v>
+        <v>-48.21</v>
       </c>
       <c r="K82" t="n">
-        <v>94.42</v>
+        <v>65.97</v>
       </c>
       <c r="L82" t="n">
-        <v>116.95</v>
+        <v>81.7</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>107.53</v>
+        <v>73.63</v>
       </c>
       <c r="K83" t="n">
-        <v>-120.13</v>
+        <v>-82.26000000000001</v>
       </c>
       <c r="L83" t="n">
-        <v>161.23</v>
+        <v>110.4</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>-171.61</v>
+        <v>-116.54</v>
       </c>
       <c r="K84" t="n">
-        <v>44.77</v>
+        <v>30.4</v>
       </c>
       <c r="L84" t="n">
-        <v>177.35</v>
+        <v>120.44</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>-149.34</v>
+        <v>-105.19</v>
       </c>
       <c r="K85" t="n">
-        <v>-115.13</v>
+        <v>-81.09</v>
       </c>
       <c r="L85" t="n">
-        <v>188.56</v>
+        <v>132.82</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-302.76</v>
+        <v>-183.9</v>
       </c>
       <c r="K86" t="n">
-        <v>48.49</v>
+        <v>29.45</v>
       </c>
       <c r="L86" t="n">
-        <v>306.62</v>
+        <v>186.24</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>473.76</v>
+        <v>298.7</v>
       </c>
       <c r="K87" t="n">
-        <v>215.06</v>
+        <v>135.59</v>
       </c>
       <c r="L87" t="n">
-        <v>520.29</v>
+        <v>328.03</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>120.47</v>
+        <v>42.97</v>
       </c>
       <c r="K88" t="n">
-        <v>185.95</v>
+        <v>66.33</v>
       </c>
       <c r="L88" t="n">
-        <v>221.57</v>
+        <v>79.03</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-17.xlsx
+++ b/output/2025-07-17.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>-80.45999999999999</v>
+        <v>-77.48</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.76</v>
+        <v>-2.65</v>
       </c>
       <c r="L14" t="n">
-        <v>80.51000000000001</v>
+        <v>77.53</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-14.87</v>
+        <v>-15.12</v>
       </c>
       <c r="K15" t="n">
-        <v>-40.92</v>
+        <v>-41.6</v>
       </c>
       <c r="L15" t="n">
-        <v>43.54</v>
+        <v>44.26</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>29.99</v>
+        <v>29.26</v>
       </c>
       <c r="K16" t="n">
-        <v>57.22</v>
+        <v>55.84</v>
       </c>
       <c r="L16" t="n">
-        <v>64.61</v>
+        <v>63.04</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>-10.66</v>
+        <v>-10.45</v>
       </c>
       <c r="K17" t="n">
-        <v>-92.41</v>
+        <v>-90.61</v>
       </c>
       <c r="L17" t="n">
-        <v>93.02</v>
+        <v>91.20999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>22.45</v>
+        <v>22.7</v>
       </c>
       <c r="K18" t="n">
-        <v>68.09</v>
+        <v>68.84</v>
       </c>
       <c r="L18" t="n">
-        <v>71.69</v>
+        <v>72.48999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>35.99</v>
+        <v>37.26</v>
       </c>
       <c r="K19" t="n">
-        <v>45.14</v>
+        <v>46.73</v>
       </c>
       <c r="L19" t="n">
-        <v>57.74</v>
+        <v>59.76</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>64.09</v>
+        <v>63.92</v>
       </c>
       <c r="K20" t="n">
-        <v>-78.48999999999999</v>
+        <v>-78.28</v>
       </c>
       <c r="L20" t="n">
-        <v>101.34</v>
+        <v>101.07</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.94</v>
+        <v>-4.28</v>
       </c>
       <c r="K21" t="n">
-        <v>-65.3</v>
+        <v>-71.06</v>
       </c>
       <c r="L21" t="n">
-        <v>65.42</v>
+        <v>71.19</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-74.39</v>
+        <v>-76.67</v>
       </c>
       <c r="K22" t="n">
-        <v>21.36</v>
+        <v>22.01</v>
       </c>
       <c r="L22" t="n">
-        <v>77.40000000000001</v>
+        <v>79.76000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-144.08</v>
+        <v>-142.86</v>
       </c>
       <c r="K23" t="n">
-        <v>9.07</v>
+        <v>8.99</v>
       </c>
       <c r="L23" t="n">
-        <v>144.37</v>
+        <v>143.14</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>18</v>
       </c>
       <c r="J24" t="n">
-        <v>136.14</v>
+        <v>136.46</v>
       </c>
       <c r="K24" t="n">
-        <v>10.04</v>
+        <v>10.07</v>
       </c>
       <c r="L24" t="n">
-        <v>136.51</v>
+        <v>136.83</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>62.49</v>
+        <v>62.86</v>
       </c>
       <c r="K25" t="n">
-        <v>120.51</v>
+        <v>121.23</v>
       </c>
       <c r="L25" t="n">
-        <v>135.74</v>
+        <v>136.56</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-22.71</v>
+        <v>-22.34</v>
       </c>
       <c r="K26" t="n">
-        <v>221.26</v>
+        <v>217.71</v>
       </c>
       <c r="L26" t="n">
-        <v>222.42</v>
+        <v>218.85</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>-271.75</v>
+        <v>-263.42</v>
       </c>
       <c r="K27" t="n">
-        <v>-24.79</v>
+        <v>-24.03</v>
       </c>
       <c r="L27" t="n">
-        <v>272.88</v>
+        <v>264.51</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>-79.95</v>
+        <v>-83.95999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>123.54</v>
+        <v>129.73</v>
       </c>
       <c r="L28" t="n">
-        <v>147.15</v>
+        <v>154.53</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-28.25</v>
+        <v>-30.49</v>
       </c>
       <c r="K29" t="n">
-        <v>-22.13</v>
+        <v>-23.88</v>
       </c>
       <c r="L29" t="n">
-        <v>35.88</v>
+        <v>38.72</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-47.31</v>
+        <v>-48.12</v>
       </c>
       <c r="K30" t="n">
-        <v>16.08</v>
+        <v>16.36</v>
       </c>
       <c r="L30" t="n">
-        <v>49.97</v>
+        <v>50.83</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>-17.89</v>
+        <v>-19.21</v>
       </c>
       <c r="K31" t="n">
-        <v>28.61</v>
+        <v>30.73</v>
       </c>
       <c r="L31" t="n">
-        <v>33.74</v>
+        <v>36.24</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>60.71</v>
+        <v>59.26</v>
       </c>
       <c r="K32" t="n">
-        <v>-72.12</v>
+        <v>-70.39</v>
       </c>
       <c r="L32" t="n">
-        <v>94.27</v>
+        <v>92.01000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>20.92</v>
+        <v>20.28</v>
       </c>
       <c r="K33" t="n">
-        <v>94.77</v>
+        <v>91.87</v>
       </c>
       <c r="L33" t="n">
-        <v>97.05</v>
+        <v>94.08</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-100.55</v>
+        <v>-96.7</v>
       </c>
       <c r="K34" t="n">
-        <v>38.29</v>
+        <v>36.83</v>
       </c>
       <c r="L34" t="n">
-        <v>107.6</v>
+        <v>103.48</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-1.08</v>
+        <v>-0.89</v>
       </c>
       <c r="K35" t="n">
-        <v>147.11</v>
+        <v>120.64</v>
       </c>
       <c r="L35" t="n">
-        <v>147.12</v>
+        <v>120.64</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>89.09999999999999</v>
+        <v>91.13</v>
       </c>
       <c r="K36" t="n">
-        <v>18.76</v>
+        <v>19.19</v>
       </c>
       <c r="L36" t="n">
-        <v>91.06</v>
+        <v>93.13</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>-107.77</v>
+        <v>-107.04</v>
       </c>
       <c r="K37" t="n">
-        <v>-24.82</v>
+        <v>-24.65</v>
       </c>
       <c r="L37" t="n">
-        <v>110.59</v>
+        <v>109.84</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>40.83</v>
+        <v>41.05</v>
       </c>
       <c r="K38" t="n">
-        <v>125.48</v>
+        <v>126.15</v>
       </c>
       <c r="L38" t="n">
-        <v>131.96</v>
+        <v>132.66</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>175.04</v>
+        <v>169.08</v>
       </c>
       <c r="K39" t="n">
-        <v>-80.33</v>
+        <v>-77.59</v>
       </c>
       <c r="L39" t="n">
-        <v>192.59</v>
+        <v>186.03</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>-78.77</v>
+        <v>-77.18000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>171.02</v>
+        <v>167.57</v>
       </c>
       <c r="L40" t="n">
-        <v>188.29</v>
+        <v>184.49</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-141.99</v>
+        <v>-137.9</v>
       </c>
       <c r="K41" t="n">
-        <v>225.12</v>
+        <v>218.63</v>
       </c>
       <c r="L41" t="n">
-        <v>266.16</v>
+        <v>258.49</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-186.09</v>
+        <v>-188.68</v>
       </c>
       <c r="K42" t="n">
-        <v>65.01000000000001</v>
+        <v>65.92</v>
       </c>
       <c r="L42" t="n">
-        <v>197.11</v>
+        <v>199.87</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>9.109999999999999</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>197.76</v>
+        <v>198.51</v>
       </c>
       <c r="L43" t="n">
-        <v>197.96</v>
+        <v>198.72</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-55.4</v>
+        <v>-56.19</v>
       </c>
       <c r="K44" t="n">
-        <v>7.61</v>
+        <v>7.72</v>
       </c>
       <c r="L44" t="n">
-        <v>55.92</v>
+        <v>56.72</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-32.55</v>
+        <v>-33.96</v>
       </c>
       <c r="K45" t="n">
-        <v>-26.37</v>
+        <v>-27.52</v>
       </c>
       <c r="L45" t="n">
-        <v>41.89</v>
+        <v>43.71</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
       <c r="K46" t="n">
-        <v>-24.78</v>
+        <v>-24.73</v>
       </c>
       <c r="L46" t="n">
-        <v>53.22</v>
+        <v>53.11</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-30.39</v>
+        <v>-32.15</v>
       </c>
       <c r="K47" t="n">
-        <v>42.77</v>
+        <v>45.25</v>
       </c>
       <c r="L47" t="n">
-        <v>52.47</v>
+        <v>55.51</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>-36.09</v>
+        <v>-38.95</v>
       </c>
       <c r="K48" t="n">
-        <v>20.95</v>
+        <v>22.61</v>
       </c>
       <c r="L48" t="n">
-        <v>41.73</v>
+        <v>45.04</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>69.19</v>
+        <v>67.84</v>
       </c>
       <c r="K49" t="n">
-        <v>-28.61</v>
+        <v>-28.05</v>
       </c>
       <c r="L49" t="n">
-        <v>74.87</v>
+        <v>73.41</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>18</v>
       </c>
       <c r="J50" t="n">
-        <v>107.65</v>
+        <v>102.97</v>
       </c>
       <c r="K50" t="n">
-        <v>139.9</v>
+        <v>133.82</v>
       </c>
       <c r="L50" t="n">
-        <v>176.52</v>
+        <v>168.85</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>14.47</v>
+        <v>13.79</v>
       </c>
       <c r="K51" t="n">
-        <v>-179.12</v>
+        <v>-170.75</v>
       </c>
       <c r="L51" t="n">
-        <v>179.7</v>
+        <v>171.3</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>-58.89</v>
+        <v>-63.2</v>
       </c>
       <c r="K52" t="n">
-        <v>-15.22</v>
+        <v>-16.34</v>
       </c>
       <c r="L52" t="n">
-        <v>60.83</v>
+        <v>65.28</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>111.63</v>
+        <v>107.6</v>
       </c>
       <c r="K53" t="n">
-        <v>-158.25</v>
+        <v>-152.54</v>
       </c>
       <c r="L53" t="n">
-        <v>193.66</v>
+        <v>186.67</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>38.04</v>
+        <v>37.89</v>
       </c>
       <c r="K54" t="n">
-        <v>-56.51</v>
+        <v>-56.27</v>
       </c>
       <c r="L54" t="n">
-        <v>68.12</v>
+        <v>67.84</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>16.75</v>
+        <v>16.85</v>
       </c>
       <c r="K55" t="n">
-        <v>-123.36</v>
+        <v>-124.06</v>
       </c>
       <c r="L55" t="n">
-        <v>124.5</v>
+        <v>125.19</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>19</v>
       </c>
       <c r="J56" t="n">
-        <v>-281.92</v>
+        <v>-271.86</v>
       </c>
       <c r="K56" t="n">
-        <v>-112.14</v>
+        <v>-108.14</v>
       </c>
       <c r="L56" t="n">
-        <v>303.4</v>
+        <v>292.58</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>123.46</v>
+        <v>120.14</v>
       </c>
       <c r="K57" t="n">
-        <v>-232.91</v>
+        <v>-226.65</v>
       </c>
       <c r="L57" t="n">
-        <v>263.61</v>
+        <v>256.52</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>-27.58</v>
+        <v>-26.55</v>
       </c>
       <c r="K58" t="n">
-        <v>293.75</v>
+        <v>282.81</v>
       </c>
       <c r="L58" t="n">
-        <v>295.05</v>
+        <v>284.05</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>-8.57</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="K59" t="n">
-        <v>-45.11</v>
+        <v>-46.75</v>
       </c>
       <c r="L59" t="n">
-        <v>45.92</v>
+        <v>47.58</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>9.199999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="K60" t="n">
-        <v>-49.86</v>
+        <v>-49.7</v>
       </c>
       <c r="L60" t="n">
-        <v>50.7</v>
+        <v>50.54</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-93.65000000000001</v>
+        <v>-88.7</v>
       </c>
       <c r="K61" t="n">
-        <v>29.73</v>
+        <v>28.15</v>
       </c>
       <c r="L61" t="n">
-        <v>98.26000000000001</v>
+        <v>93.06</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>50.19</v>
+        <v>51.24</v>
       </c>
       <c r="K62" t="n">
-        <v>-36.51</v>
+        <v>-37.27</v>
       </c>
       <c r="L62" t="n">
-        <v>62.07</v>
+        <v>63.36</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-42.67</v>
+        <v>-41.8</v>
       </c>
       <c r="K63" t="n">
-        <v>-74.59999999999999</v>
+        <v>-73.08</v>
       </c>
       <c r="L63" t="n">
-        <v>85.94</v>
+        <v>84.19</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-22.97</v>
+        <v>-22.43</v>
       </c>
       <c r="K64" t="n">
-        <v>96.14</v>
+        <v>93.89</v>
       </c>
       <c r="L64" t="n">
-        <v>98.84999999999999</v>
+        <v>96.53</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>79.70999999999999</v>
+        <v>80.94</v>
       </c>
       <c r="K65" t="n">
-        <v>50.96</v>
+        <v>51.75</v>
       </c>
       <c r="L65" t="n">
-        <v>94.61</v>
+        <v>96.06999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-13.94</v>
+        <v>-13.51</v>
       </c>
       <c r="K66" t="n">
-        <v>144.1</v>
+        <v>139.62</v>
       </c>
       <c r="L66" t="n">
-        <v>144.77</v>
+        <v>140.28</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>-19.88</v>
+        <v>-20.79</v>
       </c>
       <c r="K67" t="n">
-        <v>-78.66</v>
+        <v>-82.25</v>
       </c>
       <c r="L67" t="n">
-        <v>81.13</v>
+        <v>84.84</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>-43.35</v>
+        <v>-41.02</v>
       </c>
       <c r="K68" t="n">
-        <v>148.73</v>
+        <v>140.74</v>
       </c>
       <c r="L68" t="n">
-        <v>154.92</v>
+        <v>146.6</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>-41.15</v>
+        <v>-42.14</v>
       </c>
       <c r="K69" t="n">
-        <v>-119.65</v>
+        <v>-122.5</v>
       </c>
       <c r="L69" t="n">
-        <v>126.53</v>
+        <v>129.55</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>3.74</v>
+        <v>3.65</v>
       </c>
       <c r="K70" t="n">
-        <v>184.67</v>
+        <v>180.21</v>
       </c>
       <c r="L70" t="n">
-        <v>184.71</v>
+        <v>180.25</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>-196.71</v>
+        <v>-200.12</v>
       </c>
       <c r="K71" t="n">
-        <v>43.36</v>
+        <v>44.11</v>
       </c>
       <c r="L71" t="n">
-        <v>201.43</v>
+        <v>204.92</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>14.75</v>
+        <v>14.84</v>
       </c>
       <c r="K72" t="n">
-        <v>201.06</v>
+        <v>202.31</v>
       </c>
       <c r="L72" t="n">
-        <v>201.6</v>
+        <v>202.86</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-120.85</v>
+        <v>-123.91</v>
       </c>
       <c r="K73" t="n">
-        <v>120.41</v>
+        <v>123.46</v>
       </c>
       <c r="L73" t="n">
-        <v>170.59</v>
+        <v>174.92</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-39.42</v>
+        <v>-38.6</v>
       </c>
       <c r="K74" t="n">
-        <v>54.6</v>
+        <v>53.47</v>
       </c>
       <c r="L74" t="n">
-        <v>67.34</v>
+        <v>65.95</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>-42.16</v>
+        <v>-45.17</v>
       </c>
       <c r="K75" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="L75" t="n">
-        <v>42.19</v>
+        <v>45.19</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>18</v>
       </c>
       <c r="J76" t="n">
-        <v>-34.33</v>
+        <v>-35.75</v>
       </c>
       <c r="K76" t="n">
-        <v>-21.95</v>
+        <v>-22.85</v>
       </c>
       <c r="L76" t="n">
-        <v>40.75</v>
+        <v>42.43</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-41.18</v>
+        <v>-45.02</v>
       </c>
       <c r="K77" t="n">
-        <v>-5.73</v>
+        <v>-6.27</v>
       </c>
       <c r="L77" t="n">
-        <v>41.58</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>11.15</v>
+        <v>10.84</v>
       </c>
       <c r="K78" t="n">
-        <v>91.31999999999999</v>
+        <v>88.76000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>92</v>
+        <v>89.42</v>
       </c>
     </row>
     <row r="79">
@@ -3373,10 +3373,10 @@
         <v>-1.25</v>
       </c>
       <c r="K79" t="n">
-        <v>78.20999999999999</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>78.22</v>
+        <v>78.16</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>18</v>
       </c>
       <c r="J80" t="n">
-        <v>-103.74</v>
+        <v>-102.75</v>
       </c>
       <c r="K80" t="n">
-        <v>-64.26000000000001</v>
+        <v>-63.64</v>
       </c>
       <c r="L80" t="n">
-        <v>122.03</v>
+        <v>120.86</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>37.98</v>
+        <v>37.22</v>
       </c>
       <c r="K81" t="n">
-        <v>126.13</v>
+        <v>123.63</v>
       </c>
       <c r="L81" t="n">
-        <v>131.72</v>
+        <v>129.11</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-48.21</v>
+        <v>-49.84</v>
       </c>
       <c r="K82" t="n">
-        <v>65.97</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>81.7</v>
+        <v>84.48</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>73.63</v>
+        <v>76.23</v>
       </c>
       <c r="K83" t="n">
-        <v>-82.26000000000001</v>
+        <v>-85.16</v>
       </c>
       <c r="L83" t="n">
-        <v>110.4</v>
+        <v>114.29</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>-116.54</v>
+        <v>-120.6</v>
       </c>
       <c r="K84" t="n">
-        <v>30.4</v>
+        <v>31.46</v>
       </c>
       <c r="L84" t="n">
-        <v>120.44</v>
+        <v>124.64</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>-105.19</v>
+        <v>-105.87</v>
       </c>
       <c r="K85" t="n">
-        <v>-81.09</v>
+        <v>-81.62</v>
       </c>
       <c r="L85" t="n">
-        <v>132.82</v>
+        <v>133.68</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-183.9</v>
+        <v>-188.33</v>
       </c>
       <c r="K86" t="n">
-        <v>29.45</v>
+        <v>30.16</v>
       </c>
       <c r="L86" t="n">
-        <v>186.24</v>
+        <v>190.73</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>298.7</v>
+        <v>284.78</v>
       </c>
       <c r="K87" t="n">
-        <v>135.59</v>
+        <v>129.27</v>
       </c>
       <c r="L87" t="n">
-        <v>328.03</v>
+        <v>312.75</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>42.97</v>
+        <v>43.35</v>
       </c>
       <c r="K88" t="n">
-        <v>66.33</v>
+        <v>66.91</v>
       </c>
       <c r="L88" t="n">
-        <v>79.03</v>
+        <v>79.72</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-17.xlsx
+++ b/output/2025-07-17.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>-77.48</v>
+        <v>-74.06999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.65</v>
+        <v>-2.54</v>
       </c>
       <c r="L14" t="n">
-        <v>77.53</v>
+        <v>74.12</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-15.12</v>
+        <v>-15.4</v>
       </c>
       <c r="K15" t="n">
-        <v>-41.6</v>
+        <v>-42.37</v>
       </c>
       <c r="L15" t="n">
-        <v>44.26</v>
+        <v>45.08</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>29.26</v>
+        <v>28.43</v>
       </c>
       <c r="K16" t="n">
-        <v>55.84</v>
+        <v>54.25</v>
       </c>
       <c r="L16" t="n">
-        <v>63.04</v>
+        <v>61.25</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>-10.45</v>
+        <v>-10.21</v>
       </c>
       <c r="K17" t="n">
-        <v>-90.61</v>
+        <v>-88.56</v>
       </c>
       <c r="L17" t="n">
-        <v>91.20999999999999</v>
+        <v>89.15000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>22.7</v>
+        <v>22.99</v>
       </c>
       <c r="K18" t="n">
-        <v>68.84</v>
+        <v>69.7</v>
       </c>
       <c r="L18" t="n">
-        <v>72.48999999999999</v>
+        <v>73.39</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>37.26</v>
+        <v>38.7</v>
       </c>
       <c r="K19" t="n">
-        <v>46.73</v>
+        <v>48.54</v>
       </c>
       <c r="L19" t="n">
-        <v>59.76</v>
+        <v>62.08</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>63.92</v>
+        <v>63.72</v>
       </c>
       <c r="K20" t="n">
-        <v>-78.28</v>
+        <v>-78.04000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>101.07</v>
+        <v>100.76</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>-4.28</v>
+        <v>-4.68</v>
       </c>
       <c r="K21" t="n">
-        <v>-71.06</v>
+        <v>-77.64</v>
       </c>
       <c r="L21" t="n">
-        <v>71.19</v>
+        <v>77.78</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-76.67</v>
+        <v>-79.26000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>22.01</v>
+        <v>22.76</v>
       </c>
       <c r="L22" t="n">
-        <v>79.76000000000001</v>
+        <v>82.47</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-142.86</v>
+        <v>-141.46</v>
       </c>
       <c r="K23" t="n">
-        <v>8.99</v>
+        <v>8.91</v>
       </c>
       <c r="L23" t="n">
-        <v>143.14</v>
+        <v>141.74</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>18</v>
       </c>
       <c r="J24" t="n">
-        <v>136.46</v>
+        <v>136.83</v>
       </c>
       <c r="K24" t="n">
-        <v>10.07</v>
+        <v>10.09</v>
       </c>
       <c r="L24" t="n">
-        <v>136.83</v>
+        <v>137.2</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>62.86</v>
+        <v>63.29</v>
       </c>
       <c r="K25" t="n">
-        <v>121.23</v>
+        <v>122.07</v>
       </c>
       <c r="L25" t="n">
-        <v>136.56</v>
+        <v>137.5</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-22.34</v>
+        <v>-21.92</v>
       </c>
       <c r="K26" t="n">
-        <v>217.71</v>
+        <v>213.64</v>
       </c>
       <c r="L26" t="n">
-        <v>218.85</v>
+        <v>214.77</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>-263.42</v>
+        <v>-253.9</v>
       </c>
       <c r="K27" t="n">
-        <v>-24.03</v>
+        <v>-23.16</v>
       </c>
       <c r="L27" t="n">
-        <v>264.51</v>
+        <v>254.95</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>-83.95999999999999</v>
+        <v>-88.54000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>129.73</v>
+        <v>136.81</v>
       </c>
       <c r="L28" t="n">
-        <v>154.53</v>
+        <v>162.96</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-30.49</v>
+        <v>-33.04</v>
       </c>
       <c r="K29" t="n">
-        <v>-23.88</v>
+        <v>-25.88</v>
       </c>
       <c r="L29" t="n">
-        <v>38.72</v>
+        <v>41.97</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-48.12</v>
+        <v>-49.05</v>
       </c>
       <c r="K30" t="n">
-        <v>16.36</v>
+        <v>16.68</v>
       </c>
       <c r="L30" t="n">
-        <v>50.83</v>
+        <v>51.81</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>-19.21</v>
+        <v>-20.73</v>
       </c>
       <c r="K31" t="n">
-        <v>30.73</v>
+        <v>33.15</v>
       </c>
       <c r="L31" t="n">
-        <v>36.24</v>
+        <v>39.09</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>59.26</v>
+        <v>57.6</v>
       </c>
       <c r="K32" t="n">
-        <v>-70.39</v>
+        <v>-68.42</v>
       </c>
       <c r="L32" t="n">
-        <v>92.01000000000001</v>
+        <v>89.44</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>20.28</v>
+        <v>19.55</v>
       </c>
       <c r="K33" t="n">
-        <v>91.87</v>
+        <v>88.54000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>94.08</v>
+        <v>90.67</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-96.7</v>
+        <v>-92.3</v>
       </c>
       <c r="K34" t="n">
-        <v>36.83</v>
+        <v>35.15</v>
       </c>
       <c r="L34" t="n">
-        <v>103.48</v>
+        <v>98.77</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.89</v>
+        <v>-0.87</v>
       </c>
       <c r="K35" t="n">
-        <v>120.64</v>
+        <v>118.41</v>
       </c>
       <c r="L35" t="n">
-        <v>120.64</v>
+        <v>118.41</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>91.13</v>
+        <v>93.45</v>
       </c>
       <c r="K36" t="n">
-        <v>19.19</v>
+        <v>19.68</v>
       </c>
       <c r="L36" t="n">
-        <v>93.13</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>-107.04</v>
+        <v>-106.21</v>
       </c>
       <c r="K37" t="n">
-        <v>-24.65</v>
+        <v>-24.46</v>
       </c>
       <c r="L37" t="n">
-        <v>109.84</v>
+        <v>108.99</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>41.05</v>
+        <v>41.3</v>
       </c>
       <c r="K38" t="n">
-        <v>126.15</v>
+        <v>126.92</v>
       </c>
       <c r="L38" t="n">
-        <v>132.66</v>
+        <v>133.47</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>169.08</v>
+        <v>162.27</v>
       </c>
       <c r="K39" t="n">
-        <v>-77.59</v>
+        <v>-74.47</v>
       </c>
       <c r="L39" t="n">
-        <v>186.03</v>
+        <v>178.54</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>-77.18000000000001</v>
+        <v>-75.36</v>
       </c>
       <c r="K40" t="n">
-        <v>167.57</v>
+        <v>163.63</v>
       </c>
       <c r="L40" t="n">
-        <v>184.49</v>
+        <v>180.15</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-137.9</v>
+        <v>-133.22</v>
       </c>
       <c r="K41" t="n">
-        <v>218.63</v>
+        <v>211.21</v>
       </c>
       <c r="L41" t="n">
-        <v>258.49</v>
+        <v>249.72</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-188.68</v>
+        <v>-191.65</v>
       </c>
       <c r="K42" t="n">
-        <v>65.92</v>
+        <v>66.95</v>
       </c>
       <c r="L42" t="n">
-        <v>199.87</v>
+        <v>203.01</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>9.140000000000001</v>
+        <v>9.18</v>
       </c>
       <c r="K43" t="n">
-        <v>198.51</v>
+        <v>199.37</v>
       </c>
       <c r="L43" t="n">
-        <v>198.72</v>
+        <v>199.58</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-56.19</v>
+        <v>-57.1</v>
       </c>
       <c r="K44" t="n">
-        <v>7.72</v>
+        <v>7.84</v>
       </c>
       <c r="L44" t="n">
-        <v>56.72</v>
+        <v>57.64</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-33.96</v>
+        <v>-35.58</v>
       </c>
       <c r="K45" t="n">
-        <v>-27.52</v>
+        <v>-28.83</v>
       </c>
       <c r="L45" t="n">
-        <v>43.71</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>47</v>
+        <v>46.89</v>
       </c>
       <c r="K46" t="n">
-        <v>-24.73</v>
+        <v>-24.67</v>
       </c>
       <c r="L46" t="n">
-        <v>53.11</v>
+        <v>52.98</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-32.15</v>
+        <v>-34.17</v>
       </c>
       <c r="K47" t="n">
-        <v>45.25</v>
+        <v>48.08</v>
       </c>
       <c r="L47" t="n">
-        <v>55.51</v>
+        <v>58.99</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>-38.95</v>
+        <v>-42.23</v>
       </c>
       <c r="K48" t="n">
-        <v>22.61</v>
+        <v>24.51</v>
       </c>
       <c r="L48" t="n">
-        <v>45.04</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>67.84</v>
+        <v>66.3</v>
       </c>
       <c r="K49" t="n">
-        <v>-28.05</v>
+        <v>-27.41</v>
       </c>
       <c r="L49" t="n">
-        <v>73.41</v>
+        <v>71.75</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>18</v>
       </c>
       <c r="J50" t="n">
-        <v>102.97</v>
+        <v>97.62</v>
       </c>
       <c r="K50" t="n">
-        <v>133.82</v>
+        <v>126.87</v>
       </c>
       <c r="L50" t="n">
-        <v>168.85</v>
+        <v>160.08</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>13.79</v>
+        <v>13.02</v>
       </c>
       <c r="K51" t="n">
-        <v>-170.75</v>
+        <v>-161.17</v>
       </c>
       <c r="L51" t="n">
-        <v>171.3</v>
+        <v>161.7</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>-63.2</v>
+        <v>-68.12</v>
       </c>
       <c r="K52" t="n">
-        <v>-16.34</v>
+        <v>-17.61</v>
       </c>
       <c r="L52" t="n">
-        <v>65.28</v>
+        <v>70.36</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>107.6</v>
+        <v>103</v>
       </c>
       <c r="K53" t="n">
-        <v>-152.54</v>
+        <v>-146.01</v>
       </c>
       <c r="L53" t="n">
-        <v>186.67</v>
+        <v>178.68</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>37.89</v>
+        <v>41.68</v>
       </c>
       <c r="K54" t="n">
-        <v>-56.27</v>
+        <v>-61.91</v>
       </c>
       <c r="L54" t="n">
-        <v>67.84</v>
+        <v>74.63</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>16.85</v>
+        <v>16.96</v>
       </c>
       <c r="K55" t="n">
-        <v>-124.06</v>
+        <v>-124.85</v>
       </c>
       <c r="L55" t="n">
-        <v>125.19</v>
+        <v>125.99</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>19</v>
       </c>
       <c r="J56" t="n">
-        <v>-271.86</v>
+        <v>-260.37</v>
       </c>
       <c r="K56" t="n">
-        <v>-108.14</v>
+        <v>-103.57</v>
       </c>
       <c r="L56" t="n">
-        <v>292.58</v>
+        <v>280.21</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>120.14</v>
+        <v>116.35</v>
       </c>
       <c r="K57" t="n">
-        <v>-226.65</v>
+        <v>-219.49</v>
       </c>
       <c r="L57" t="n">
-        <v>256.52</v>
+        <v>248.42</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>-26.55</v>
+        <v>-25.37</v>
       </c>
       <c r="K58" t="n">
-        <v>282.81</v>
+        <v>270.3</v>
       </c>
       <c r="L58" t="n">
-        <v>284.05</v>
+        <v>271.49</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>-8.880000000000001</v>
+        <v>-9.23</v>
       </c>
       <c r="K59" t="n">
-        <v>-46.75</v>
+        <v>-48.62</v>
       </c>
       <c r="L59" t="n">
-        <v>47.58</v>
+        <v>49.49</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>9.17</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="K60" t="n">
-        <v>-49.7</v>
+        <v>-49.53</v>
       </c>
       <c r="L60" t="n">
-        <v>50.54</v>
+        <v>50.36</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-88.7</v>
+        <v>-83.03</v>
       </c>
       <c r="K61" t="n">
-        <v>28.15</v>
+        <v>26.35</v>
       </c>
       <c r="L61" t="n">
-        <v>93.06</v>
+        <v>87.11</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>51.24</v>
+        <v>52.44</v>
       </c>
       <c r="K62" t="n">
-        <v>-37.27</v>
+        <v>-38.14</v>
       </c>
       <c r="L62" t="n">
-        <v>63.36</v>
+        <v>64.84</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-41.8</v>
+        <v>-40.81</v>
       </c>
       <c r="K63" t="n">
-        <v>-73.08</v>
+        <v>-71.34</v>
       </c>
       <c r="L63" t="n">
-        <v>84.19</v>
+        <v>82.19</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-22.43</v>
+        <v>-21.81</v>
       </c>
       <c r="K64" t="n">
-        <v>93.89</v>
+        <v>91.31</v>
       </c>
       <c r="L64" t="n">
-        <v>96.53</v>
+        <v>93.88</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>80.94</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>51.75</v>
+        <v>52.65</v>
       </c>
       <c r="L65" t="n">
-        <v>96.06999999999999</v>
+        <v>97.73999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-13.51</v>
+        <v>-13.01</v>
       </c>
       <c r="K66" t="n">
-        <v>139.62</v>
+        <v>134.51</v>
       </c>
       <c r="L66" t="n">
-        <v>140.28</v>
+        <v>135.14</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>-20.79</v>
+        <v>-21.82</v>
       </c>
       <c r="K67" t="n">
-        <v>-82.25</v>
+        <v>-86.36</v>
       </c>
       <c r="L67" t="n">
-        <v>84.84</v>
+        <v>89.06999999999999</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>-41.02</v>
+        <v>-41.66</v>
       </c>
       <c r="K68" t="n">
-        <v>140.74</v>
+        <v>142.94</v>
       </c>
       <c r="L68" t="n">
-        <v>146.6</v>
+        <v>148.89</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>-42.14</v>
+        <v>-43.26</v>
       </c>
       <c r="K69" t="n">
-        <v>-122.5</v>
+        <v>-125.77</v>
       </c>
       <c r="L69" t="n">
-        <v>129.55</v>
+        <v>133</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K70" t="n">
-        <v>180.21</v>
+        <v>175.11</v>
       </c>
       <c r="L70" t="n">
-        <v>180.25</v>
+        <v>175.14</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>-200.12</v>
+        <v>-204.01</v>
       </c>
       <c r="K71" t="n">
-        <v>44.11</v>
+        <v>44.97</v>
       </c>
       <c r="L71" t="n">
-        <v>204.92</v>
+        <v>208.91</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>14.84</v>
+        <v>14.95</v>
       </c>
       <c r="K72" t="n">
-        <v>202.31</v>
+        <v>203.74</v>
       </c>
       <c r="L72" t="n">
-        <v>202.86</v>
+        <v>204.29</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-123.91</v>
+        <v>-127.41</v>
       </c>
       <c r="K73" t="n">
-        <v>123.46</v>
+        <v>126.94</v>
       </c>
       <c r="L73" t="n">
-        <v>174.92</v>
+        <v>179.86</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-38.6</v>
+        <v>-37.67</v>
       </c>
       <c r="K74" t="n">
-        <v>53.47</v>
+        <v>52.18</v>
       </c>
       <c r="L74" t="n">
-        <v>65.95</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>-45.17</v>
+        <v>-48.6</v>
       </c>
       <c r="K75" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="L75" t="n">
-        <v>45.19</v>
+        <v>48.63</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>18</v>
       </c>
       <c r="J76" t="n">
-        <v>-35.75</v>
+        <v>-37.37</v>
       </c>
       <c r="K76" t="n">
-        <v>-22.85</v>
+        <v>-23.89</v>
       </c>
       <c r="L76" t="n">
-        <v>42.43</v>
+        <v>44.35</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-45.02</v>
+        <v>-49.41</v>
       </c>
       <c r="K77" t="n">
-        <v>-6.27</v>
+        <v>-6.88</v>
       </c>
       <c r="L77" t="n">
-        <v>45.45</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>10.84</v>
+        <v>10.48</v>
       </c>
       <c r="K78" t="n">
-        <v>88.76000000000001</v>
+        <v>85.84</v>
       </c>
       <c r="L78" t="n">
-        <v>89.42</v>
+        <v>86.48</v>
       </c>
     </row>
     <row r="79">
@@ -3373,10 +3373,10 @@
         <v>-1.25</v>
       </c>
       <c r="K79" t="n">
-        <v>78.15000000000001</v>
+        <v>78.09</v>
       </c>
       <c r="L79" t="n">
-        <v>78.16</v>
+        <v>78.09999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>18</v>
       </c>
       <c r="J80" t="n">
-        <v>-102.75</v>
+        <v>-101.61</v>
       </c>
       <c r="K80" t="n">
-        <v>-63.64</v>
+        <v>-62.94</v>
       </c>
       <c r="L80" t="n">
-        <v>120.86</v>
+        <v>119.53</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>37.22</v>
+        <v>36.37</v>
       </c>
       <c r="K81" t="n">
-        <v>123.63</v>
+        <v>120.78</v>
       </c>
       <c r="L81" t="n">
-        <v>129.11</v>
+        <v>126.14</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-49.84</v>
+        <v>-51.72</v>
       </c>
       <c r="K82" t="n">
-        <v>68.20999999999999</v>
+        <v>70.77</v>
       </c>
       <c r="L82" t="n">
-        <v>84.48</v>
+        <v>87.65000000000001</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>76.23</v>
+        <v>79.2</v>
       </c>
       <c r="K83" t="n">
-        <v>-85.16</v>
+        <v>-88.48</v>
       </c>
       <c r="L83" t="n">
-        <v>114.29</v>
+        <v>118.74</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>-120.6</v>
+        <v>-125.25</v>
       </c>
       <c r="K84" t="n">
-        <v>31.46</v>
+        <v>32.67</v>
       </c>
       <c r="L84" t="n">
-        <v>124.64</v>
+        <v>129.44</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>-105.87</v>
+        <v>-106.66</v>
       </c>
       <c r="K85" t="n">
-        <v>-81.62</v>
+        <v>-82.22</v>
       </c>
       <c r="L85" t="n">
-        <v>133.68</v>
+        <v>134.67</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-188.33</v>
+        <v>-193.38</v>
       </c>
       <c r="K86" t="n">
-        <v>30.16</v>
+        <v>30.97</v>
       </c>
       <c r="L86" t="n">
-        <v>190.73</v>
+        <v>195.85</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>284.78</v>
+        <v>268.87</v>
       </c>
       <c r="K87" t="n">
-        <v>129.27</v>
+        <v>122.05</v>
       </c>
       <c r="L87" t="n">
-        <v>312.75</v>
+        <v>295.27</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>43.35</v>
+        <v>47.37</v>
       </c>
       <c r="K88" t="n">
-        <v>66.91</v>
+        <v>73.11</v>
       </c>
       <c r="L88" t="n">
-        <v>79.72</v>
+        <v>87.12</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-17.xlsx
+++ b/output/2025-07-17.xlsx
@@ -628,25 +628,25 @@
         <v>2.17</v>
       </c>
       <c r="F14" t="n">
-        <v>8.93</v>
+        <v>2.95</v>
       </c>
       <c r="G14" t="n">
-        <v>59.8</v>
+        <v>73.8</v>
       </c>
       <c r="H14" t="n">
-        <v>80.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="I14" t="n">
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>-74.06999999999999</v>
+        <v>-71.91</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.54</v>
+        <v>-2.49</v>
       </c>
       <c r="L14" t="n">
-        <v>74.12</v>
+        <v>71.95</v>
       </c>
     </row>
     <row r="15">
@@ -670,25 +670,25 @@
         <v>1.67</v>
       </c>
       <c r="F15" t="n">
-        <v>8.109999999999999</v>
+        <v>4.67</v>
       </c>
       <c r="G15" t="n">
-        <v>67.40000000000001</v>
+        <v>57.2</v>
       </c>
       <c r="H15" t="n">
-        <v>89.09999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="I15" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J15" t="n">
-        <v>-15.4</v>
+        <v>-18.27</v>
       </c>
       <c r="K15" t="n">
-        <v>-42.37</v>
+        <v>-50.9</v>
       </c>
       <c r="L15" t="n">
-        <v>45.08</v>
+        <v>54.08</v>
       </c>
     </row>
     <row r="16">
@@ -712,25 +712,25 @@
         <v>1.87</v>
       </c>
       <c r="F16" t="n">
-        <v>8.970000000000001</v>
+        <v>7.12</v>
       </c>
       <c r="G16" t="n">
-        <v>71.09999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>88.8</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J16" t="n">
-        <v>28.43</v>
+        <v>36.6</v>
       </c>
       <c r="K16" t="n">
-        <v>54.25</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>61.25</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="17">
@@ -754,25 +754,25 @@
         <v>1.97</v>
       </c>
       <c r="F17" t="n">
-        <v>9.84</v>
+        <v>3.93</v>
       </c>
       <c r="G17" t="n">
-        <v>65.90000000000001</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>91.2</v>
+        <v>85</v>
       </c>
       <c r="I17" t="n">
         <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>-10.21</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>-88.56</v>
+        <v>-91.22</v>
       </c>
       <c r="L17" t="n">
-        <v>89.15000000000001</v>
+        <v>91.66</v>
       </c>
     </row>
     <row r="18">
@@ -796,25 +796,25 @@
         <v>2.16</v>
       </c>
       <c r="F18" t="n">
-        <v>8.16</v>
+        <v>4.95</v>
       </c>
       <c r="G18" t="n">
-        <v>88.3</v>
+        <v>58.3</v>
       </c>
       <c r="H18" t="n">
-        <v>83.40000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="I18" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>22.99</v>
+        <v>24.93</v>
       </c>
       <c r="K18" t="n">
-        <v>69.7</v>
+        <v>73.41</v>
       </c>
       <c r="L18" t="n">
-        <v>73.39</v>
+        <v>77.52</v>
       </c>
     </row>
     <row r="19">
@@ -838,25 +838,25 @@
         <v>1.96</v>
       </c>
       <c r="F19" t="n">
-        <v>8.550000000000001</v>
+        <v>10.07</v>
       </c>
       <c r="G19" t="n">
-        <v>68.09999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="H19" t="n">
-        <v>93.5</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>38.7</v>
+        <v>53.79</v>
       </c>
       <c r="K19" t="n">
-        <v>48.54</v>
+        <v>65.59</v>
       </c>
       <c r="L19" t="n">
-        <v>62.08</v>
+        <v>84.83</v>
       </c>
     </row>
     <row r="20">
@@ -880,25 +880,25 @@
         <v>1.79</v>
       </c>
       <c r="F20" t="n">
-        <v>8.94</v>
+        <v>4.11</v>
       </c>
       <c r="G20" t="n">
-        <v>75.09999999999999</v>
+        <v>74</v>
       </c>
       <c r="H20" t="n">
-        <v>84.2</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>63.72</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>-78.04000000000001</v>
+        <v>-83.67</v>
       </c>
       <c r="L20" t="n">
-        <v>100.76</v>
+        <v>112.36</v>
       </c>
     </row>
     <row r="21">
@@ -922,25 +922,25 @@
         <v>2.18</v>
       </c>
       <c r="F21" t="n">
-        <v>8.369999999999999</v>
+        <v>10.23</v>
       </c>
       <c r="G21" t="n">
-        <v>66.8</v>
+        <v>62.5</v>
       </c>
       <c r="H21" t="n">
-        <v>88.7</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>-4.68</v>
+        <v>16.38</v>
       </c>
       <c r="K21" t="n">
-        <v>-77.64</v>
+        <v>-96.87</v>
       </c>
       <c r="L21" t="n">
-        <v>77.78</v>
+        <v>98.23999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -964,25 +964,25 @@
         <v>1.66</v>
       </c>
       <c r="F22" t="n">
-        <v>8.880000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="G22" t="n">
-        <v>79.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>92.59999999999999</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-79.26000000000001</v>
+        <v>-112.05</v>
       </c>
       <c r="K22" t="n">
-        <v>22.76</v>
+        <v>38.28</v>
       </c>
       <c r="L22" t="n">
-        <v>82.47</v>
+        <v>118.41</v>
       </c>
     </row>
     <row r="23">
@@ -1006,25 +1006,25 @@
         <v>1.99</v>
       </c>
       <c r="F23" t="n">
-        <v>8.44</v>
+        <v>3.16</v>
       </c>
       <c r="G23" t="n">
-        <v>86</v>
+        <v>63.9</v>
       </c>
       <c r="H23" t="n">
-        <v>96.09999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I23" t="n">
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-141.46</v>
+        <v>-136.53</v>
       </c>
       <c r="K23" t="n">
-        <v>8.91</v>
+        <v>18.38</v>
       </c>
       <c r="L23" t="n">
-        <v>141.74</v>
+        <v>137.76</v>
       </c>
     </row>
     <row r="24">
@@ -1048,25 +1048,25 @@
         <v>1.38</v>
       </c>
       <c r="F24" t="n">
-        <v>9.57</v>
+        <v>4.07</v>
       </c>
       <c r="G24" t="n">
-        <v>82.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>86.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="I24" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>136.83</v>
+        <v>151.11</v>
       </c>
       <c r="K24" t="n">
-        <v>10.09</v>
+        <v>10.62</v>
       </c>
       <c r="L24" t="n">
-        <v>137.2</v>
+        <v>151.48</v>
       </c>
     </row>
     <row r="25">
@@ -1090,25 +1090,25 @@
         <v>2.12</v>
       </c>
       <c r="F25" t="n">
-        <v>9.19</v>
+        <v>5.21</v>
       </c>
       <c r="G25" t="n">
-        <v>78.59999999999999</v>
+        <v>79</v>
       </c>
       <c r="H25" t="n">
-        <v>93.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>63.29</v>
+        <v>88.33</v>
       </c>
       <c r="K25" t="n">
-        <v>122.07</v>
+        <v>138.21</v>
       </c>
       <c r="L25" t="n">
-        <v>137.5</v>
+        <v>164.03</v>
       </c>
     </row>
     <row r="26">
@@ -1132,25 +1132,25 @@
         <v>2.01</v>
       </c>
       <c r="F26" t="n">
-        <v>8.960000000000001</v>
+        <v>4.37</v>
       </c>
       <c r="G26" t="n">
-        <v>61.6</v>
+        <v>74.3</v>
       </c>
       <c r="H26" t="n">
-        <v>83.2</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-21.92</v>
+        <v>6.54</v>
       </c>
       <c r="K26" t="n">
-        <v>213.64</v>
+        <v>237.15</v>
       </c>
       <c r="L26" t="n">
-        <v>214.77</v>
+        <v>237.24</v>
       </c>
     </row>
     <row r="27">
@@ -1174,25 +1174,25 @@
         <v>1.66</v>
       </c>
       <c r="F27" t="n">
-        <v>8.83</v>
+        <v>10.23</v>
       </c>
       <c r="G27" t="n">
-        <v>73.59999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="H27" t="n">
-        <v>87.40000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>-253.9</v>
+        <v>-363.35</v>
       </c>
       <c r="K27" t="n">
-        <v>-23.16</v>
+        <v>-24.88</v>
       </c>
       <c r="L27" t="n">
-        <v>254.95</v>
+        <v>364.2</v>
       </c>
     </row>
     <row r="28">
@@ -1216,25 +1216,25 @@
         <v>2.04</v>
       </c>
       <c r="F28" t="n">
-        <v>9.08</v>
+        <v>8.65</v>
       </c>
       <c r="G28" t="n">
-        <v>79.40000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="H28" t="n">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="I28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-88.54000000000001</v>
+        <v>-49.04</v>
       </c>
       <c r="K28" t="n">
-        <v>136.81</v>
+        <v>210.77</v>
       </c>
       <c r="L28" t="n">
-        <v>162.96</v>
+        <v>216.4</v>
       </c>
     </row>
     <row r="29">
@@ -1258,25 +1258,25 @@
         <v>2.17</v>
       </c>
       <c r="F29" t="n">
-        <v>9.199999999999999</v>
+        <v>10.23</v>
       </c>
       <c r="G29" t="n">
-        <v>63.5</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>89.8</v>
+        <v>83.8</v>
       </c>
       <c r="I29" t="n">
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-33.04</v>
+        <v>-44.35</v>
       </c>
       <c r="K29" t="n">
-        <v>-25.88</v>
+        <v>-36.55</v>
       </c>
       <c r="L29" t="n">
-        <v>41.97</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="30">
@@ -1300,25 +1300,25 @@
         <v>2.25</v>
       </c>
       <c r="F30" t="n">
-        <v>8.08</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>71.40000000000001</v>
+        <v>56.7</v>
       </c>
       <c r="H30" t="n">
-        <v>88</v>
+        <v>87.7</v>
       </c>
       <c r="I30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>-49.05</v>
+        <v>-58.92</v>
       </c>
       <c r="K30" t="n">
-        <v>16.68</v>
+        <v>20.89</v>
       </c>
       <c r="L30" t="n">
-        <v>51.81</v>
+        <v>62.51</v>
       </c>
     </row>
     <row r="31">
@@ -1342,25 +1342,25 @@
         <v>2.01</v>
       </c>
       <c r="F31" t="n">
-        <v>9.34</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>52.8</v>
+        <v>82</v>
       </c>
       <c r="H31" t="n">
-        <v>88.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>-20.73</v>
+        <v>-26.27</v>
       </c>
       <c r="K31" t="n">
-        <v>33.15</v>
+        <v>44.07</v>
       </c>
       <c r="L31" t="n">
-        <v>39.09</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="32">
@@ -1384,25 +1384,25 @@
         <v>1.96</v>
       </c>
       <c r="F32" t="n">
-        <v>9.279999999999999</v>
+        <v>10.23</v>
       </c>
       <c r="G32" t="n">
-        <v>79.09999999999999</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>97.3</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>57.6</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>-68.42</v>
+        <v>-89.20999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>89.44</v>
+        <v>117.78</v>
       </c>
     </row>
     <row r="33">
@@ -1426,25 +1426,25 @@
         <v>1.98</v>
       </c>
       <c r="F33" t="n">
-        <v>8.98</v>
+        <v>6.13</v>
       </c>
       <c r="G33" t="n">
-        <v>75.5</v>
+        <v>74.8</v>
       </c>
       <c r="H33" t="n">
-        <v>92.2</v>
+        <v>89.8</v>
       </c>
       <c r="I33" t="n">
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>19.55</v>
+        <v>23.24</v>
       </c>
       <c r="K33" t="n">
-        <v>88.54000000000001</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>90.67</v>
+        <v>102.66</v>
       </c>
     </row>
     <row r="34">
@@ -1468,25 +1468,25 @@
         <v>2.11</v>
       </c>
       <c r="F34" t="n">
-        <v>8.85</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>63.9</v>
+        <v>72</v>
       </c>
       <c r="H34" t="n">
-        <v>91.40000000000001</v>
+        <v>84</v>
       </c>
       <c r="I34" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>-92.3</v>
+        <v>-111.54</v>
       </c>
       <c r="K34" t="n">
-        <v>35.15</v>
+        <v>43.29</v>
       </c>
       <c r="L34" t="n">
-        <v>98.77</v>
+        <v>119.64</v>
       </c>
     </row>
     <row r="35">
@@ -1510,25 +1510,25 @@
         <v>1.8</v>
       </c>
       <c r="F35" t="n">
-        <v>9.67</v>
+        <v>5.14</v>
       </c>
       <c r="G35" t="n">
-        <v>70.90000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="H35" t="n">
-        <v>96.8</v>
+        <v>87.5</v>
       </c>
       <c r="I35" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.87</v>
+        <v>4.95</v>
       </c>
       <c r="K35" t="n">
-        <v>118.41</v>
+        <v>135.64</v>
       </c>
       <c r="L35" t="n">
-        <v>118.41</v>
+        <v>135.73</v>
       </c>
     </row>
     <row r="36">
@@ -1552,25 +1552,25 @@
         <v>1.81</v>
       </c>
       <c r="F36" t="n">
-        <v>8.92</v>
+        <v>8.34</v>
       </c>
       <c r="G36" t="n">
-        <v>76.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>90.8</v>
+        <v>90.2</v>
       </c>
       <c r="I36" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>93.45</v>
+        <v>117.58</v>
       </c>
       <c r="K36" t="n">
-        <v>19.68</v>
+        <v>25.73</v>
       </c>
       <c r="L36" t="n">
-        <v>95.5</v>
+        <v>120.36</v>
       </c>
     </row>
     <row r="37">
@@ -1594,25 +1594,25 @@
         <v>2.35</v>
       </c>
       <c r="F37" t="n">
-        <v>9.34</v>
+        <v>10.23</v>
       </c>
       <c r="G37" t="n">
-        <v>70.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="H37" t="n">
-        <v>93.09999999999999</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>-106.21</v>
+        <v>-144.16</v>
       </c>
       <c r="K37" t="n">
-        <v>-24.46</v>
+        <v>-35.43</v>
       </c>
       <c r="L37" t="n">
-        <v>108.99</v>
+        <v>148.45</v>
       </c>
     </row>
     <row r="38">
@@ -1636,25 +1636,25 @@
         <v>1.88</v>
       </c>
       <c r="F38" t="n">
-        <v>9.31</v>
+        <v>6.65</v>
       </c>
       <c r="G38" t="n">
-        <v>74.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="H38" t="n">
-        <v>87.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>41.3</v>
+        <v>64.45</v>
       </c>
       <c r="K38" t="n">
-        <v>126.92</v>
+        <v>147.84</v>
       </c>
       <c r="L38" t="n">
-        <v>133.47</v>
+        <v>161.28</v>
       </c>
     </row>
     <row r="39">
@@ -1678,25 +1678,25 @@
         <v>2.04</v>
       </c>
       <c r="F39" t="n">
-        <v>8.82</v>
+        <v>5.11</v>
       </c>
       <c r="G39" t="n">
-        <v>79.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H39" t="n">
-        <v>87.8</v>
+        <v>91.8</v>
       </c>
       <c r="I39" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>162.27</v>
+        <v>172.08</v>
       </c>
       <c r="K39" t="n">
-        <v>-74.47</v>
+        <v>-69.48999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>178.54</v>
+        <v>185.58</v>
       </c>
     </row>
     <row r="40">
@@ -1720,25 +1720,25 @@
         <v>2.69</v>
       </c>
       <c r="F40" t="n">
-        <v>8.81</v>
+        <v>10.23</v>
       </c>
       <c r="G40" t="n">
-        <v>72.8</v>
+        <v>71.2</v>
       </c>
       <c r="H40" t="n">
-        <v>96</v>
+        <v>88.5</v>
       </c>
       <c r="I40" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>-75.36</v>
+        <v>-69.98</v>
       </c>
       <c r="K40" t="n">
-        <v>163.63</v>
+        <v>208.44</v>
       </c>
       <c r="L40" t="n">
-        <v>180.15</v>
+        <v>219.87</v>
       </c>
     </row>
     <row r="41">
@@ -1762,25 +1762,25 @@
         <v>1.9</v>
       </c>
       <c r="F41" t="n">
-        <v>8.59</v>
+        <v>4.1</v>
       </c>
       <c r="G41" t="n">
-        <v>67.5</v>
+        <v>67</v>
       </c>
       <c r="H41" t="n">
-        <v>85.7</v>
+        <v>85.8</v>
       </c>
       <c r="I41" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J41" t="n">
-        <v>-133.22</v>
+        <v>-121.96</v>
       </c>
       <c r="K41" t="n">
-        <v>211.21</v>
+        <v>245</v>
       </c>
       <c r="L41" t="n">
-        <v>249.72</v>
+        <v>273.68</v>
       </c>
     </row>
     <row r="42">
@@ -1804,25 +1804,25 @@
         <v>2.06</v>
       </c>
       <c r="F42" t="n">
-        <v>9.26</v>
+        <v>10.17</v>
       </c>
       <c r="G42" t="n">
-        <v>89.3</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>92</v>
+        <v>96.7</v>
       </c>
       <c r="I42" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J42" t="n">
-        <v>-191.65</v>
+        <v>-229.42</v>
       </c>
       <c r="K42" t="n">
-        <v>66.95</v>
+        <v>117.01</v>
       </c>
       <c r="L42" t="n">
-        <v>203.01</v>
+        <v>257.54</v>
       </c>
     </row>
     <row r="43">
@@ -1846,25 +1846,25 @@
         <v>2.4</v>
       </c>
       <c r="F43" t="n">
-        <v>8.960000000000001</v>
+        <v>9.58</v>
       </c>
       <c r="G43" t="n">
-        <v>58.1</v>
+        <v>74.3</v>
       </c>
       <c r="H43" t="n">
-        <v>89.5</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J43" t="n">
-        <v>9.18</v>
+        <v>63.45</v>
       </c>
       <c r="K43" t="n">
-        <v>199.37</v>
+        <v>254.69</v>
       </c>
       <c r="L43" t="n">
-        <v>199.58</v>
+        <v>262.47</v>
       </c>
     </row>
     <row r="44">
@@ -1888,25 +1888,25 @@
         <v>2.45</v>
       </c>
       <c r="F44" t="n">
-        <v>8.09</v>
+        <v>10.23</v>
       </c>
       <c r="G44" t="n">
-        <v>73.40000000000001</v>
+        <v>56.9</v>
       </c>
       <c r="H44" t="n">
-        <v>90.40000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>-57.1</v>
+        <v>-70</v>
       </c>
       <c r="K44" t="n">
-        <v>7.84</v>
+        <v>10.54</v>
       </c>
       <c r="L44" t="n">
-        <v>57.64</v>
+        <v>70.79000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1930,25 +1930,25 @@
         <v>2.31</v>
       </c>
       <c r="F45" t="n">
-        <v>8.029999999999999</v>
+        <v>6.93</v>
       </c>
       <c r="G45" t="n">
-        <v>92.59999999999999</v>
+        <v>55.7</v>
       </c>
       <c r="H45" t="n">
-        <v>89.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>-35.58</v>
+        <v>-43.6</v>
       </c>
       <c r="K45" t="n">
-        <v>-28.83</v>
+        <v>-34.37</v>
       </c>
       <c r="L45" t="n">
-        <v>45.8</v>
+        <v>55.52</v>
       </c>
     </row>
     <row r="46">
@@ -1972,25 +1972,25 @@
         <v>2.09</v>
       </c>
       <c r="F46" t="n">
-        <v>8.039999999999999</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="G46" t="n">
-        <v>71.2</v>
+        <v>55.8</v>
       </c>
       <c r="H46" t="n">
-        <v>91</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>46.89</v>
+        <v>62.84</v>
       </c>
       <c r="K46" t="n">
-        <v>-24.67</v>
+        <v>-32.29</v>
       </c>
       <c r="L46" t="n">
-        <v>52.98</v>
+        <v>70.65000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2014,25 +2014,25 @@
         <v>2.15</v>
       </c>
       <c r="F47" t="n">
-        <v>9.210000000000001</v>
+        <v>10.23</v>
       </c>
       <c r="G47" t="n">
-        <v>76.09999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="H47" t="n">
-        <v>94</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>-34.17</v>
+        <v>-41.14</v>
       </c>
       <c r="K47" t="n">
-        <v>48.08</v>
+        <v>63.81</v>
       </c>
       <c r="L47" t="n">
-        <v>58.99</v>
+        <v>75.92</v>
       </c>
     </row>
     <row r="48">
@@ -2056,25 +2056,25 @@
         <v>1.53</v>
       </c>
       <c r="F48" t="n">
-        <v>8.75</v>
+        <v>7.28</v>
       </c>
       <c r="G48" t="n">
-        <v>78.3</v>
+        <v>70</v>
       </c>
       <c r="H48" t="n">
-        <v>90.59999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="I48" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>-42.23</v>
+        <v>-58.01</v>
       </c>
       <c r="K48" t="n">
-        <v>24.51</v>
+        <v>37.2</v>
       </c>
       <c r="L48" t="n">
-        <v>48.83</v>
+        <v>68.91</v>
       </c>
     </row>
     <row r="49">
@@ -2098,25 +2098,25 @@
         <v>1.48</v>
       </c>
       <c r="F49" t="n">
-        <v>8.35</v>
+        <v>5.96</v>
       </c>
       <c r="G49" t="n">
-        <v>72.09999999999999</v>
+        <v>62</v>
       </c>
       <c r="H49" t="n">
-        <v>89.59999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>66.3</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>-27.41</v>
+        <v>-37.01</v>
       </c>
       <c r="L49" t="n">
-        <v>71.75</v>
+        <v>99.26000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -2140,25 +2140,25 @@
         <v>2.38</v>
       </c>
       <c r="F50" t="n">
-        <v>8.789999999999999</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>69.59999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="H50" t="n">
-        <v>88.5</v>
+        <v>86.8</v>
       </c>
       <c r="I50" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>97.62</v>
+        <v>109.08</v>
       </c>
       <c r="K50" t="n">
-        <v>126.87</v>
+        <v>136.2</v>
       </c>
       <c r="L50" t="n">
-        <v>160.08</v>
+        <v>174.5</v>
       </c>
     </row>
     <row r="51">
@@ -2182,25 +2182,25 @@
         <v>2.22</v>
       </c>
       <c r="F51" t="n">
-        <v>8.31</v>
+        <v>5.63</v>
       </c>
       <c r="G51" t="n">
-        <v>84.7</v>
+        <v>61.4</v>
       </c>
       <c r="H51" t="n">
-        <v>83</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>13.02</v>
+        <v>16.61</v>
       </c>
       <c r="K51" t="n">
-        <v>-161.17</v>
+        <v>-153.08</v>
       </c>
       <c r="L51" t="n">
-        <v>161.7</v>
+        <v>153.98</v>
       </c>
     </row>
     <row r="52">
@@ -2224,25 +2224,25 @@
         <v>1.8</v>
       </c>
       <c r="F52" t="n">
-        <v>9.31</v>
+        <v>5.57</v>
       </c>
       <c r="G52" t="n">
-        <v>75.2</v>
+        <v>81.3</v>
       </c>
       <c r="H52" t="n">
-        <v>85.90000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J52" t="n">
-        <v>-68.12</v>
+        <v>-86.43000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>-17.61</v>
+        <v>-25.24</v>
       </c>
       <c r="L52" t="n">
-        <v>70.36</v>
+        <v>90.04000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -2266,25 +2266,25 @@
         <v>1.94</v>
       </c>
       <c r="F53" t="n">
-        <v>8.949999999999999</v>
+        <v>8.85</v>
       </c>
       <c r="G53" t="n">
-        <v>78.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="H53" t="n">
-        <v>77.7</v>
+        <v>91.2</v>
       </c>
       <c r="I53" t="n">
         <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>103</v>
+        <v>145.02</v>
       </c>
       <c r="K53" t="n">
-        <v>-146.01</v>
+        <v>-182.68</v>
       </c>
       <c r="L53" t="n">
-        <v>178.68</v>
+        <v>233.24</v>
       </c>
     </row>
     <row r="54">
@@ -2308,25 +2308,25 @@
         <v>1.81</v>
       </c>
       <c r="F54" t="n">
-        <v>9.24</v>
+        <v>2.11</v>
       </c>
       <c r="G54" t="n">
-        <v>71.40000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="H54" t="n">
-        <v>79.3</v>
+        <v>87.8</v>
       </c>
       <c r="I54" t="n">
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>41.68</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>-61.91</v>
+        <v>-55.31</v>
       </c>
       <c r="L54" t="n">
-        <v>74.63</v>
+        <v>91.86</v>
       </c>
     </row>
     <row r="55">
@@ -2350,25 +2350,25 @@
         <v>2.05</v>
       </c>
       <c r="F55" t="n">
-        <v>8.6</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>84.8</v>
+        <v>67.2</v>
       </c>
       <c r="H55" t="n">
-        <v>82.40000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="I55" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>16.96</v>
+        <v>42.94</v>
       </c>
       <c r="K55" t="n">
-        <v>-124.85</v>
+        <v>-165.79</v>
       </c>
       <c r="L55" t="n">
-        <v>125.99</v>
+        <v>171.27</v>
       </c>
     </row>
     <row r="56">
@@ -2392,25 +2392,25 @@
         <v>2.55</v>
       </c>
       <c r="F56" t="n">
-        <v>8.98</v>
+        <v>6.43</v>
       </c>
       <c r="G56" t="n">
-        <v>72.5</v>
+        <v>74.8</v>
       </c>
       <c r="H56" t="n">
-        <v>82.3</v>
+        <v>88.3</v>
       </c>
       <c r="I56" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>-260.37</v>
+        <v>-243.29</v>
       </c>
       <c r="K56" t="n">
-        <v>-103.57</v>
+        <v>-101.95</v>
       </c>
       <c r="L56" t="n">
-        <v>280.21</v>
+        <v>263.79</v>
       </c>
     </row>
     <row r="57">
@@ -2434,25 +2434,25 @@
         <v>1.81</v>
       </c>
       <c r="F57" t="n">
-        <v>9.35</v>
+        <v>4.09</v>
       </c>
       <c r="G57" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H57" t="n">
-        <v>88.09999999999999</v>
+        <v>85</v>
       </c>
       <c r="I57" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>116.35</v>
+        <v>139.57</v>
       </c>
       <c r="K57" t="n">
-        <v>-219.49</v>
+        <v>-216.07</v>
       </c>
       <c r="L57" t="n">
-        <v>248.42</v>
+        <v>257.23</v>
       </c>
     </row>
     <row r="58">
@@ -2476,25 +2476,25 @@
         <v>2</v>
       </c>
       <c r="F58" t="n">
-        <v>8.699999999999999</v>
+        <v>9.15</v>
       </c>
       <c r="G58" t="n">
-        <v>67.90000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>90.40000000000001</v>
+        <v>86</v>
       </c>
       <c r="I58" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>-25.37</v>
+        <v>-2.21</v>
       </c>
       <c r="K58" t="n">
-        <v>270.3</v>
+        <v>341.11</v>
       </c>
       <c r="L58" t="n">
-        <v>271.49</v>
+        <v>341.11</v>
       </c>
     </row>
     <row r="59">
@@ -2518,25 +2518,25 @@
         <v>2.29</v>
       </c>
       <c r="F59" t="n">
-        <v>9.35</v>
+        <v>6.22</v>
       </c>
       <c r="G59" t="n">
-        <v>71.40000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H59" t="n">
-        <v>83.7</v>
+        <v>87.7</v>
       </c>
       <c r="I59" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>-9.23</v>
+        <v>-10.03</v>
       </c>
       <c r="K59" t="n">
-        <v>-48.62</v>
+        <v>-58.42</v>
       </c>
       <c r="L59" t="n">
-        <v>49.49</v>
+        <v>59.28</v>
       </c>
     </row>
     <row r="60">
@@ -2560,25 +2560,25 @@
         <v>1.71</v>
       </c>
       <c r="F60" t="n">
-        <v>8.960000000000001</v>
+        <v>6.32</v>
       </c>
       <c r="G60" t="n">
-        <v>76.7</v>
+        <v>74.3</v>
       </c>
       <c r="H60" t="n">
-        <v>87.59999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>9.140000000000001</v>
+        <v>11.81</v>
       </c>
       <c r="K60" t="n">
-        <v>-49.53</v>
+        <v>-61.57</v>
       </c>
       <c r="L60" t="n">
-        <v>50.36</v>
+        <v>62.69</v>
       </c>
     </row>
     <row r="61">
@@ -2602,25 +2602,25 @@
         <v>2.27</v>
       </c>
       <c r="F61" t="n">
-        <v>8.73</v>
+        <v>10.23</v>
       </c>
       <c r="G61" t="n">
-        <v>62.5</v>
+        <v>69.8</v>
       </c>
       <c r="H61" t="n">
-        <v>85.09999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="I61" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>-83.03</v>
+        <v>-113.13</v>
       </c>
       <c r="K61" t="n">
-        <v>26.35</v>
+        <v>36.16</v>
       </c>
       <c r="L61" t="n">
-        <v>87.11</v>
+        <v>118.77</v>
       </c>
     </row>
     <row r="62">
@@ -2644,25 +2644,25 @@
         <v>2.16</v>
       </c>
       <c r="F62" t="n">
-        <v>8.41</v>
+        <v>7.9</v>
       </c>
       <c r="G62" t="n">
-        <v>67.2</v>
+        <v>63.3</v>
       </c>
       <c r="H62" t="n">
-        <v>87.09999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I62" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>52.44</v>
+        <v>67.33</v>
       </c>
       <c r="K62" t="n">
-        <v>-38.14</v>
+        <v>-46.28</v>
       </c>
       <c r="L62" t="n">
-        <v>64.84</v>
+        <v>81.7</v>
       </c>
     </row>
     <row r="63">
@@ -2686,25 +2686,25 @@
         <v>2.11</v>
       </c>
       <c r="F63" t="n">
-        <v>9.49</v>
+        <v>8.73</v>
       </c>
       <c r="G63" t="n">
-        <v>78.5</v>
+        <v>85</v>
       </c>
       <c r="H63" t="n">
-        <v>82.40000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="I63" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>-40.81</v>
+        <v>-50.94</v>
       </c>
       <c r="K63" t="n">
-        <v>-71.34</v>
+        <v>-92.06</v>
       </c>
       <c r="L63" t="n">
-        <v>82.19</v>
+        <v>105.21</v>
       </c>
     </row>
     <row r="64">
@@ -2728,25 +2728,25 @@
         <v>1.97</v>
       </c>
       <c r="F64" t="n">
-        <v>8.640000000000001</v>
+        <v>10.23</v>
       </c>
       <c r="G64" t="n">
-        <v>67</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H64" t="n">
-        <v>94.3</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>-21.81</v>
+        <v>-24.41</v>
       </c>
       <c r="K64" t="n">
-        <v>91.31</v>
+        <v>108.87</v>
       </c>
       <c r="L64" t="n">
-        <v>93.88</v>
+        <v>111.57</v>
       </c>
     </row>
     <row r="65">
@@ -2770,25 +2770,25 @@
         <v>2.19</v>
       </c>
       <c r="F65" t="n">
-        <v>8.859999999999999</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="G65" t="n">
-        <v>71.7</v>
+        <v>72.2</v>
       </c>
       <c r="H65" t="n">
-        <v>91.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>82.34999999999999</v>
+        <v>116.21</v>
       </c>
       <c r="K65" t="n">
-        <v>52.65</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="L65" t="n">
-        <v>97.73999999999999</v>
+        <v>136.26</v>
       </c>
     </row>
     <row r="66">
@@ -2812,25 +2812,25 @@
         <v>1.73</v>
       </c>
       <c r="F66" t="n">
-        <v>9.08</v>
+        <v>5.48</v>
       </c>
       <c r="G66" t="n">
-        <v>68.7</v>
+        <v>76.8</v>
       </c>
       <c r="H66" t="n">
-        <v>86</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-13.01</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="K66" t="n">
-        <v>134.51</v>
+        <v>148.23</v>
       </c>
       <c r="L66" t="n">
-        <v>135.14</v>
+        <v>148.54</v>
       </c>
     </row>
     <row r="67">
@@ -2854,25 +2854,25 @@
         <v>1.93</v>
       </c>
       <c r="F67" t="n">
-        <v>8.65</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="G67" t="n">
-        <v>84.2</v>
+        <v>68</v>
       </c>
       <c r="H67" t="n">
-        <v>89.40000000000001</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-21.82</v>
+        <v>-18.94</v>
       </c>
       <c r="K67" t="n">
-        <v>-86.36</v>
+        <v>-115.29</v>
       </c>
       <c r="L67" t="n">
-        <v>89.06999999999999</v>
+        <v>116.83</v>
       </c>
     </row>
     <row r="68">
@@ -2896,25 +2896,25 @@
         <v>1.87</v>
       </c>
       <c r="F68" t="n">
-        <v>9.119999999999999</v>
+        <v>10.23</v>
       </c>
       <c r="G68" t="n">
-        <v>69.3</v>
+        <v>77.5</v>
       </c>
       <c r="H68" t="n">
-        <v>93.2</v>
+        <v>86.7</v>
       </c>
       <c r="I68" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-41.66</v>
+        <v>-31.88</v>
       </c>
       <c r="K68" t="n">
-        <v>142.94</v>
+        <v>197.43</v>
       </c>
       <c r="L68" t="n">
-        <v>148.89</v>
+        <v>199.98</v>
       </c>
     </row>
     <row r="69">
@@ -2938,25 +2938,25 @@
         <v>2.08</v>
       </c>
       <c r="F69" t="n">
-        <v>8.539999999999999</v>
+        <v>9.18</v>
       </c>
       <c r="G69" t="n">
-        <v>68.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="H69" t="n">
-        <v>88.90000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="I69" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J69" t="n">
-        <v>-43.26</v>
+        <v>-32.68</v>
       </c>
       <c r="K69" t="n">
-        <v>-125.77</v>
+        <v>-156.23</v>
       </c>
       <c r="L69" t="n">
-        <v>133</v>
+        <v>159.61</v>
       </c>
     </row>
     <row r="70">
@@ -2980,25 +2980,25 @@
         <v>2.53</v>
       </c>
       <c r="F70" t="n">
-        <v>8.859999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="G70" t="n">
-        <v>77.3</v>
+        <v>72.2</v>
       </c>
       <c r="H70" t="n">
-        <v>86.7</v>
+        <v>90.7</v>
       </c>
       <c r="I70" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>3.55</v>
+        <v>23.86</v>
       </c>
       <c r="K70" t="n">
-        <v>175.11</v>
+        <v>225.06</v>
       </c>
       <c r="L70" t="n">
-        <v>175.14</v>
+        <v>226.33</v>
       </c>
     </row>
     <row r="71">
@@ -3022,25 +3022,25 @@
         <v>2.45</v>
       </c>
       <c r="F71" t="n">
-        <v>8.77</v>
+        <v>10.23</v>
       </c>
       <c r="G71" t="n">
-        <v>75.2</v>
+        <v>70.5</v>
       </c>
       <c r="H71" t="n">
-        <v>92</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I71" t="n">
         <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>-204.01</v>
+        <v>-230.88</v>
       </c>
       <c r="K71" t="n">
-        <v>44.97</v>
+        <v>96.91</v>
       </c>
       <c r="L71" t="n">
-        <v>208.91</v>
+        <v>250.39</v>
       </c>
     </row>
     <row r="72">
@@ -3064,25 +3064,25 @@
         <v>2.09</v>
       </c>
       <c r="F72" t="n">
-        <v>9.050000000000001</v>
+        <v>10.14</v>
       </c>
       <c r="G72" t="n">
-        <v>86.59999999999999</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="H72" t="n">
-        <v>91.09999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="I72" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>14.95</v>
+        <v>68.16</v>
       </c>
       <c r="K72" t="n">
-        <v>203.74</v>
+        <v>286.66</v>
       </c>
       <c r="L72" t="n">
-        <v>204.29</v>
+        <v>294.65</v>
       </c>
     </row>
     <row r="73">
@@ -3106,25 +3106,25 @@
         <v>2.38</v>
       </c>
       <c r="F73" t="n">
-        <v>8.550000000000001</v>
+        <v>10.23</v>
       </c>
       <c r="G73" t="n">
-        <v>76.2</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="H73" t="n">
-        <v>82.90000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="I73" t="n">
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-127.41</v>
+        <v>-112.58</v>
       </c>
       <c r="K73" t="n">
-        <v>126.94</v>
+        <v>204.7</v>
       </c>
       <c r="L73" t="n">
-        <v>179.86</v>
+        <v>233.61</v>
       </c>
     </row>
     <row r="74">
@@ -3148,25 +3148,25 @@
         <v>2.25</v>
       </c>
       <c r="F74" t="n">
-        <v>7.99</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="G74" t="n">
-        <v>90.7</v>
+        <v>54.9</v>
       </c>
       <c r="H74" t="n">
-        <v>87.40000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="I74" t="n">
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-37.67</v>
+        <v>-45.9</v>
       </c>
       <c r="K74" t="n">
-        <v>52.18</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="L74" t="n">
-        <v>64.36</v>
+        <v>79.43000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -3190,25 +3190,25 @@
         <v>2.53</v>
       </c>
       <c r="F75" t="n">
-        <v>8.66</v>
+        <v>10.23</v>
       </c>
       <c r="G75" t="n">
-        <v>73.09999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="H75" t="n">
-        <v>89.59999999999999</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J75" t="n">
-        <v>-48.6</v>
+        <v>-62.09</v>
       </c>
       <c r="K75" t="n">
-        <v>1.72</v>
+        <v>3.2</v>
       </c>
       <c r="L75" t="n">
-        <v>48.63</v>
+        <v>62.17</v>
       </c>
     </row>
     <row r="76">
@@ -3232,25 +3232,25 @@
         <v>1.76</v>
       </c>
       <c r="F76" t="n">
-        <v>9.369999999999999</v>
+        <v>10.23</v>
       </c>
       <c r="G76" t="n">
-        <v>69.59999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="H76" t="n">
-        <v>96.40000000000001</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-37.37</v>
+        <v>-49.92</v>
       </c>
       <c r="K76" t="n">
-        <v>-23.89</v>
+        <v>-32.61</v>
       </c>
       <c r="L76" t="n">
-        <v>44.35</v>
+        <v>59.62</v>
       </c>
     </row>
     <row r="77">
@@ -3274,25 +3274,25 @@
         <v>2.33</v>
       </c>
       <c r="F77" t="n">
-        <v>8.890000000000001</v>
+        <v>10.23</v>
       </c>
       <c r="G77" t="n">
-        <v>64.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="H77" t="n">
-        <v>86.5</v>
+        <v>84.3</v>
       </c>
       <c r="I77" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>-49.41</v>
+        <v>-69.65000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>-6.88</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>49.88</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="78">
@@ -3316,25 +3316,25 @@
         <v>1.92</v>
       </c>
       <c r="F78" t="n">
-        <v>8.890000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="G78" t="n">
-        <v>68.09999999999999</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="H78" t="n">
-        <v>91.90000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="I78" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>10.48</v>
+        <v>15.97</v>
       </c>
       <c r="K78" t="n">
-        <v>85.84</v>
+        <v>118.79</v>
       </c>
       <c r="L78" t="n">
-        <v>86.48</v>
+        <v>119.85</v>
       </c>
     </row>
     <row r="79">
@@ -3358,25 +3358,25 @@
         <v>2.24</v>
       </c>
       <c r="F79" t="n">
-        <v>8.73</v>
+        <v>6.12</v>
       </c>
       <c r="G79" t="n">
-        <v>86.59999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H79" t="n">
-        <v>83.90000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="I79" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-1.25</v>
+        <v>0.32</v>
       </c>
       <c r="K79" t="n">
-        <v>78.09</v>
+        <v>86.16</v>
       </c>
       <c r="L79" t="n">
-        <v>78.09999999999999</v>
+        <v>86.16</v>
       </c>
     </row>
     <row r="80">
@@ -3400,25 +3400,25 @@
         <v>2.1</v>
       </c>
       <c r="F80" t="n">
-        <v>9.300000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="G80" t="n">
-        <v>69.3</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="H80" t="n">
-        <v>81.2</v>
+        <v>86.7</v>
       </c>
       <c r="I80" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>-101.61</v>
+        <v>-94.01000000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>-62.94</v>
+        <v>-62.12</v>
       </c>
       <c r="L80" t="n">
-        <v>119.53</v>
+        <v>112.68</v>
       </c>
     </row>
     <row r="81">
@@ -3442,25 +3442,25 @@
         <v>2.15</v>
       </c>
       <c r="F81" t="n">
-        <v>8.65</v>
+        <v>9.93</v>
       </c>
       <c r="G81" t="n">
-        <v>73.3</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="H81" t="n">
-        <v>90.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="I81" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>36.37</v>
+        <v>51.93</v>
       </c>
       <c r="K81" t="n">
-        <v>120.78</v>
+        <v>153.27</v>
       </c>
       <c r="L81" t="n">
-        <v>126.14</v>
+        <v>161.83</v>
       </c>
     </row>
     <row r="82">
@@ -3484,25 +3484,25 @@
         <v>2.05</v>
       </c>
       <c r="F82" t="n">
-        <v>8.880000000000001</v>
+        <v>5.84</v>
       </c>
       <c r="G82" t="n">
-        <v>79.8</v>
+        <v>72.8</v>
       </c>
       <c r="H82" t="n">
-        <v>84.09999999999999</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I82" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>-51.72</v>
+        <v>-50.02</v>
       </c>
       <c r="K82" t="n">
-        <v>70.77</v>
+        <v>84.63</v>
       </c>
       <c r="L82" t="n">
-        <v>87.65000000000001</v>
+        <v>98.31</v>
       </c>
     </row>
     <row r="83">
@@ -3526,25 +3526,25 @@
         <v>2.24</v>
       </c>
       <c r="F83" t="n">
-        <v>9.01</v>
+        <v>10.23</v>
       </c>
       <c r="G83" t="n">
-        <v>70.59999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="H83" t="n">
-        <v>88.5</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I83" t="n">
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>79.2</v>
+        <v>126.38</v>
       </c>
       <c r="K83" t="n">
-        <v>-88.48</v>
+        <v>-103.33</v>
       </c>
       <c r="L83" t="n">
-        <v>118.74</v>
+        <v>163.25</v>
       </c>
     </row>
     <row r="84">
@@ -3568,25 +3568,25 @@
         <v>2.28</v>
       </c>
       <c r="F84" t="n">
-        <v>8.859999999999999</v>
+        <v>10.23</v>
       </c>
       <c r="G84" t="n">
-        <v>71.7</v>
+        <v>72.3</v>
       </c>
       <c r="H84" t="n">
-        <v>91.2</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I84" t="n">
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>-125.25</v>
+        <v>-152.05</v>
       </c>
       <c r="K84" t="n">
-        <v>32.67</v>
+        <v>61.13</v>
       </c>
       <c r="L84" t="n">
-        <v>129.44</v>
+        <v>163.87</v>
       </c>
     </row>
     <row r="85">
@@ -3610,25 +3610,25 @@
         <v>2.11</v>
       </c>
       <c r="F85" t="n">
-        <v>9.25</v>
+        <v>10.04</v>
       </c>
       <c r="G85" t="n">
-        <v>67.3</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="H85" t="n">
-        <v>93.8</v>
+        <v>85.7</v>
       </c>
       <c r="I85" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>-106.66</v>
+        <v>-134.06</v>
       </c>
       <c r="K85" t="n">
-        <v>-82.22</v>
+        <v>-121.67</v>
       </c>
       <c r="L85" t="n">
-        <v>134.67</v>
+        <v>181.04</v>
       </c>
     </row>
     <row r="86">
@@ -3652,25 +3652,25 @@
         <v>2.85</v>
       </c>
       <c r="F86" t="n">
-        <v>8.67</v>
+        <v>10.23</v>
       </c>
       <c r="G86" t="n">
-        <v>88.8</v>
+        <v>68.5</v>
       </c>
       <c r="H86" t="n">
-        <v>86.2</v>
+        <v>96.5</v>
       </c>
       <c r="I86" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>-193.38</v>
+        <v>-217.65</v>
       </c>
       <c r="K86" t="n">
-        <v>30.97</v>
+        <v>95.41</v>
       </c>
       <c r="L86" t="n">
-        <v>195.85</v>
+        <v>237.64</v>
       </c>
     </row>
     <row r="87">
@@ -3694,25 +3694,25 @@
         <v>2.65</v>
       </c>
       <c r="F87" t="n">
-        <v>9.199999999999999</v>
+        <v>10.23</v>
       </c>
       <c r="G87" t="n">
-        <v>73.90000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="H87" t="n">
-        <v>86.7</v>
+        <v>89</v>
       </c>
       <c r="I87" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>268.87</v>
+        <v>370.02</v>
       </c>
       <c r="K87" t="n">
-        <v>122.05</v>
+        <v>156.45</v>
       </c>
       <c r="L87" t="n">
-        <v>295.27</v>
+        <v>401.74</v>
       </c>
     </row>
     <row r="88">
@@ -3736,25 +3736,25 @@
         <v>3.82</v>
       </c>
       <c r="F88" t="n">
-        <v>9.359999999999999</v>
+        <v>10.23</v>
       </c>
       <c r="G88" t="n">
-        <v>69.3</v>
+        <v>82.3</v>
       </c>
       <c r="H88" t="n">
-        <v>87.2</v>
+        <v>86.7</v>
       </c>
       <c r="I88" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J88" t="n">
-        <v>47.37</v>
+        <v>199.35</v>
       </c>
       <c r="K88" t="n">
-        <v>73.11</v>
+        <v>86.34</v>
       </c>
       <c r="L88" t="n">
-        <v>87.12</v>
+        <v>217.25</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-17.xlsx
+++ b/output/2025-07-17.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>-71.91</v>
+        <v>-75.98</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.49</v>
+        <v>-2.63</v>
       </c>
       <c r="L14" t="n">
-        <v>71.95</v>
+        <v>76.03</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>19</v>
       </c>
       <c r="J15" t="n">
-        <v>-18.27</v>
+        <v>-19.93</v>
       </c>
       <c r="K15" t="n">
-        <v>-50.9</v>
+        <v>-55.53</v>
       </c>
       <c r="L15" t="n">
-        <v>54.08</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>18</v>
       </c>
       <c r="J16" t="n">
-        <v>36.6</v>
+        <v>40.53</v>
       </c>
       <c r="K16" t="n">
-        <v>69.09999999999999</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>78.2</v>
+        <v>86.58</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>-8.970000000000001</v>
+        <v>-9.93</v>
       </c>
       <c r="K17" t="n">
-        <v>-91.22</v>
+        <v>-101</v>
       </c>
       <c r="L17" t="n">
-        <v>91.66</v>
+        <v>101.48</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>24.93</v>
+        <v>25.89</v>
       </c>
       <c r="K18" t="n">
-        <v>73.41</v>
+        <v>76.23</v>
       </c>
       <c r="L18" t="n">
-        <v>77.52</v>
+        <v>80.51000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>53.79</v>
+        <v>55.86</v>
       </c>
       <c r="K19" t="n">
-        <v>65.59</v>
+        <v>68.12</v>
       </c>
       <c r="L19" t="n">
-        <v>84.83</v>
+        <v>88.09</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>74.98999999999999</v>
+        <v>77.87</v>
       </c>
       <c r="K20" t="n">
-        <v>-83.67</v>
+        <v>-86.89</v>
       </c>
       <c r="L20" t="n">
-        <v>112.36</v>
+        <v>116.68</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>16.38</v>
+        <v>16.7</v>
       </c>
       <c r="K21" t="n">
-        <v>-96.87</v>
+        <v>-98.77</v>
       </c>
       <c r="L21" t="n">
-        <v>98.23999999999999</v>
+        <v>100.17</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-112.05</v>
+        <v>-116.36</v>
       </c>
       <c r="K22" t="n">
-        <v>38.28</v>
+        <v>39.76</v>
       </c>
       <c r="L22" t="n">
-        <v>118.41</v>
+        <v>122.97</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-136.53</v>
+        <v>-139.21</v>
       </c>
       <c r="K23" t="n">
-        <v>18.38</v>
+        <v>18.74</v>
       </c>
       <c r="L23" t="n">
-        <v>137.76</v>
+        <v>140.46</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>151.11</v>
+        <v>156.92</v>
       </c>
       <c r="K24" t="n">
-        <v>10.62</v>
+        <v>11.02</v>
       </c>
       <c r="L24" t="n">
-        <v>151.48</v>
+        <v>157.31</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>88.33</v>
+        <v>97.8</v>
       </c>
       <c r="K25" t="n">
-        <v>138.21</v>
+        <v>153.02</v>
       </c>
       <c r="L25" t="n">
-        <v>164.03</v>
+        <v>181.6</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>6.54</v>
+        <v>6.79</v>
       </c>
       <c r="K26" t="n">
-        <v>237.15</v>
+        <v>246.27</v>
       </c>
       <c r="L26" t="n">
-        <v>237.24</v>
+        <v>246.36</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>-363.35</v>
+        <v>-402.28</v>
       </c>
       <c r="K27" t="n">
-        <v>-24.88</v>
+        <v>-27.55</v>
       </c>
       <c r="L27" t="n">
-        <v>364.2</v>
+        <v>403.22</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-49.04</v>
+        <v>-52.67</v>
       </c>
       <c r="K28" t="n">
-        <v>210.77</v>
+        <v>226.38</v>
       </c>
       <c r="L28" t="n">
-        <v>216.4</v>
+        <v>232.43</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-44.35</v>
+        <v>-48.38</v>
       </c>
       <c r="K29" t="n">
-        <v>-36.55</v>
+        <v>-39.88</v>
       </c>
       <c r="L29" t="n">
-        <v>57.47</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>-58.92</v>
+        <v>-60.07</v>
       </c>
       <c r="K30" t="n">
-        <v>20.89</v>
+        <v>21.3</v>
       </c>
       <c r="L30" t="n">
-        <v>62.51</v>
+        <v>63.73</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>-26.27</v>
+        <v>-28.21</v>
       </c>
       <c r="K31" t="n">
-        <v>44.07</v>
+        <v>47.33</v>
       </c>
       <c r="L31" t="n">
-        <v>51.3</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>76.90000000000001</v>
+        <v>81.25</v>
       </c>
       <c r="K32" t="n">
-        <v>-89.20999999999999</v>
+        <v>-94.26000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>117.78</v>
+        <v>124.45</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>23.24</v>
+        <v>24.13</v>
       </c>
       <c r="K33" t="n">
-        <v>99.98999999999999</v>
+        <v>103.84</v>
       </c>
       <c r="L33" t="n">
-        <v>102.66</v>
+        <v>106.6</v>
       </c>
     </row>
     <row r="34">
@@ -1522,13 +1522,13 @@
         <v>18</v>
       </c>
       <c r="J35" t="n">
-        <v>4.95</v>
+        <v>5.48</v>
       </c>
       <c r="K35" t="n">
-        <v>135.64</v>
+        <v>150.18</v>
       </c>
       <c r="L35" t="n">
-        <v>135.73</v>
+        <v>150.28</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>117.58</v>
+        <v>119.88</v>
       </c>
       <c r="K36" t="n">
-        <v>25.73</v>
+        <v>26.24</v>
       </c>
       <c r="L36" t="n">
-        <v>120.36</v>
+        <v>122.72</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>-144.16</v>
+        <v>-157.26</v>
       </c>
       <c r="K37" t="n">
-        <v>-35.43</v>
+        <v>-38.65</v>
       </c>
       <c r="L37" t="n">
-        <v>148.45</v>
+        <v>161.94</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>64.45</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>147.84</v>
+        <v>156.21</v>
       </c>
       <c r="L38" t="n">
-        <v>161.28</v>
+        <v>170.41</v>
       </c>
     </row>
     <row r="39">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>-69.98</v>
+        <v>-75.17</v>
       </c>
       <c r="K40" t="n">
-        <v>208.44</v>
+        <v>223.88</v>
       </c>
       <c r="L40" t="n">
-        <v>219.87</v>
+        <v>236.16</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>18</v>
       </c>
       <c r="J41" t="n">
-        <v>-121.96</v>
+        <v>-135.03</v>
       </c>
       <c r="K41" t="n">
-        <v>245</v>
+        <v>271.25</v>
       </c>
       <c r="L41" t="n">
-        <v>273.68</v>
+        <v>303</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>19</v>
       </c>
       <c r="J42" t="n">
-        <v>-229.42</v>
+        <v>-250.28</v>
       </c>
       <c r="K42" t="n">
-        <v>117.01</v>
+        <v>127.65</v>
       </c>
       <c r="L42" t="n">
-        <v>257.54</v>
+        <v>280.95</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>21</v>
       </c>
       <c r="J43" t="n">
-        <v>63.45</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>254.69</v>
+        <v>269.1</v>
       </c>
       <c r="L43" t="n">
-        <v>262.47</v>
+        <v>277.33</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>-70</v>
+        <v>-73.95999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>10.54</v>
+        <v>11.13</v>
       </c>
       <c r="L44" t="n">
-        <v>70.79000000000001</v>
+        <v>74.8</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>-43.6</v>
+        <v>-46.07</v>
       </c>
       <c r="K45" t="n">
-        <v>-34.37</v>
+        <v>-36.32</v>
       </c>
       <c r="L45" t="n">
-        <v>55.52</v>
+        <v>58.66</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>62.84</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>-32.29</v>
+        <v>-33.53</v>
       </c>
       <c r="L46" t="n">
-        <v>70.65000000000001</v>
+        <v>73.37</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>-41.14</v>
+        <v>-42.72</v>
       </c>
       <c r="K47" t="n">
-        <v>63.81</v>
+        <v>66.27</v>
       </c>
       <c r="L47" t="n">
-        <v>75.92</v>
+        <v>78.84</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>-58.01</v>
+        <v>-63.28</v>
       </c>
       <c r="K48" t="n">
-        <v>37.2</v>
+        <v>40.58</v>
       </c>
       <c r="L48" t="n">
-        <v>68.91</v>
+        <v>75.17</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>92.09999999999999</v>
+        <v>101.97</v>
       </c>
       <c r="K49" t="n">
-        <v>-37.01</v>
+        <v>-40.97</v>
       </c>
       <c r="L49" t="n">
-        <v>99.26000000000001</v>
+        <v>109.9</v>
       </c>
     </row>
     <row r="50">
@@ -2236,13 +2236,13 @@
         <v>19</v>
       </c>
       <c r="J52" t="n">
-        <v>-86.43000000000001</v>
+        <v>-94.29000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>-25.24</v>
+        <v>-27.53</v>
       </c>
       <c r="L52" t="n">
-        <v>90.04000000000001</v>
+        <v>98.23</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>145.02</v>
+        <v>158.2</v>
       </c>
       <c r="K53" t="n">
-        <v>-182.68</v>
+        <v>-199.28</v>
       </c>
       <c r="L53" t="n">
-        <v>233.24</v>
+        <v>254.44</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>73.34999999999999</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>-55.31</v>
+        <v>-56.39</v>
       </c>
       <c r="L54" t="n">
-        <v>91.86</v>
+        <v>93.67</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>42.94</v>
+        <v>46.13</v>
       </c>
       <c r="K55" t="n">
-        <v>-165.79</v>
+        <v>-178.07</v>
       </c>
       <c r="L55" t="n">
-        <v>171.27</v>
+        <v>183.95</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>-243.29</v>
+        <v>-248.06</v>
       </c>
       <c r="K56" t="n">
-        <v>-101.95</v>
+        <v>-103.95</v>
       </c>
       <c r="L56" t="n">
-        <v>263.79</v>
+        <v>268.96</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>139.57</v>
+        <v>147.47</v>
       </c>
       <c r="K57" t="n">
-        <v>-216.07</v>
+        <v>-228.3</v>
       </c>
       <c r="L57" t="n">
-        <v>257.23</v>
+        <v>271.79</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>-2.21</v>
+        <v>-2.34</v>
       </c>
       <c r="K58" t="n">
-        <v>341.11</v>
+        <v>360.41</v>
       </c>
       <c r="L58" t="n">
-        <v>341.11</v>
+        <v>360.42</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>-10.03</v>
+        <v>-10.95</v>
       </c>
       <c r="K59" t="n">
-        <v>-58.42</v>
+        <v>-63.73</v>
       </c>
       <c r="L59" t="n">
-        <v>59.28</v>
+        <v>64.67</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>11.81</v>
+        <v>12.27</v>
       </c>
       <c r="K60" t="n">
-        <v>-61.57</v>
+        <v>-63.94</v>
       </c>
       <c r="L60" t="n">
-        <v>62.69</v>
+        <v>65.11</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>-113.13</v>
+        <v>-123.41</v>
       </c>
       <c r="K61" t="n">
-        <v>36.16</v>
+        <v>39.45</v>
       </c>
       <c r="L61" t="n">
-        <v>118.77</v>
+        <v>129.56</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>67.33</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>-46.28</v>
+        <v>-47.18</v>
       </c>
       <c r="L62" t="n">
-        <v>81.7</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>-50.94</v>
+        <v>-51.94</v>
       </c>
       <c r="K63" t="n">
-        <v>-92.06</v>
+        <v>-93.86</v>
       </c>
       <c r="L63" t="n">
-        <v>105.21</v>
+        <v>107.28</v>
       </c>
     </row>
     <row r="64">
@@ -2782,13 +2782,13 @@
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>116.21</v>
+        <v>122.78</v>
       </c>
       <c r="K65" t="n">
-        <v>71.15000000000001</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="L65" t="n">
-        <v>136.26</v>
+        <v>143.97</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.529999999999999</v>
+        <v>-10.07</v>
       </c>
       <c r="K66" t="n">
-        <v>148.23</v>
+        <v>156.63</v>
       </c>
       <c r="L66" t="n">
-        <v>148.54</v>
+        <v>156.95</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-18.94</v>
+        <v>-20.35</v>
       </c>
       <c r="K67" t="n">
-        <v>-115.29</v>
+        <v>-123.83</v>
       </c>
       <c r="L67" t="n">
-        <v>116.83</v>
+        <v>125.49</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-31.88</v>
+        <v>-33.68</v>
       </c>
       <c r="K68" t="n">
-        <v>197.43</v>
+        <v>208.6</v>
       </c>
       <c r="L68" t="n">
-        <v>199.98</v>
+        <v>211.3</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>21</v>
       </c>
       <c r="J69" t="n">
-        <v>-32.68</v>
+        <v>-34.53</v>
       </c>
       <c r="K69" t="n">
-        <v>-156.23</v>
+        <v>-165.07</v>
       </c>
       <c r="L69" t="n">
-        <v>159.61</v>
+        <v>168.65</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>23.86</v>
+        <v>25.62</v>
       </c>
       <c r="K70" t="n">
-        <v>225.06</v>
+        <v>241.74</v>
       </c>
       <c r="L70" t="n">
-        <v>226.33</v>
+        <v>243.09</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>-230.88</v>
+        <v>-255.61</v>
       </c>
       <c r="K71" t="n">
-        <v>96.91</v>
+        <v>107.3</v>
       </c>
       <c r="L71" t="n">
-        <v>250.39</v>
+        <v>277.22</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>68.16</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="K72" t="n">
-        <v>286.66</v>
+        <v>312.72</v>
       </c>
       <c r="L72" t="n">
-        <v>294.65</v>
+        <v>321.44</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-112.58</v>
+        <v>-114.79</v>
       </c>
       <c r="K73" t="n">
-        <v>204.7</v>
+        <v>208.71</v>
       </c>
       <c r="L73" t="n">
-        <v>233.61</v>
+        <v>238.19</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-45.9</v>
+        <v>-46.8</v>
       </c>
       <c r="K74" t="n">
-        <v>64.81999999999999</v>
+        <v>66.09</v>
       </c>
       <c r="L74" t="n">
-        <v>79.43000000000001</v>
+        <v>80.98</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>19</v>
       </c>
       <c r="J75" t="n">
-        <v>-62.09</v>
+        <v>-67.73</v>
       </c>
       <c r="K75" t="n">
-        <v>3.2</v>
+        <v>3.49</v>
       </c>
       <c r="L75" t="n">
-        <v>62.17</v>
+        <v>67.81999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-49.92</v>
+        <v>-51.84</v>
       </c>
       <c r="K76" t="n">
-        <v>-32.61</v>
+        <v>-33.86</v>
       </c>
       <c r="L76" t="n">
-        <v>59.62</v>
+        <v>61.92</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>-69.65000000000001</v>
+        <v>-73.59</v>
       </c>
       <c r="K77" t="n">
-        <v>-9.529999999999999</v>
+        <v>-10.07</v>
       </c>
       <c r="L77" t="n">
-        <v>70.3</v>
+        <v>74.28</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>15.97</v>
+        <v>16.87</v>
       </c>
       <c r="K78" t="n">
-        <v>118.79</v>
+        <v>125.51</v>
       </c>
       <c r="L78" t="n">
-        <v>119.85</v>
+        <v>126.64</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="K79" t="n">
-        <v>86.16</v>
+        <v>89.47</v>
       </c>
       <c r="L79" t="n">
-        <v>86.16</v>
+        <v>89.48</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>-94.01000000000001</v>
+        <v>-95.84999999999999</v>
       </c>
       <c r="K80" t="n">
-        <v>-62.12</v>
+        <v>-63.34</v>
       </c>
       <c r="L80" t="n">
-        <v>112.68</v>
+        <v>114.89</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>51.93</v>
+        <v>54.87</v>
       </c>
       <c r="K81" t="n">
-        <v>153.27</v>
+        <v>161.95</v>
       </c>
       <c r="L81" t="n">
-        <v>161.83</v>
+        <v>170.99</v>
       </c>
     </row>
     <row r="82">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>126.38</v>
+        <v>131.24</v>
       </c>
       <c r="K83" t="n">
-        <v>-103.33</v>
+        <v>-107.31</v>
       </c>
       <c r="L83" t="n">
-        <v>163.25</v>
+        <v>169.52</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>-152.05</v>
+        <v>-168.34</v>
       </c>
       <c r="K84" t="n">
-        <v>61.13</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="L84" t="n">
-        <v>163.87</v>
+        <v>181.43</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>-134.06</v>
+        <v>-146.25</v>
       </c>
       <c r="K85" t="n">
-        <v>-121.67</v>
+        <v>-132.73</v>
       </c>
       <c r="L85" t="n">
-        <v>181.04</v>
+        <v>197.5</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>-217.65</v>
+        <v>-240.97</v>
       </c>
       <c r="K86" t="n">
-        <v>95.41</v>
+        <v>105.63</v>
       </c>
       <c r="L86" t="n">
-        <v>237.64</v>
+        <v>263.1</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>370.02</v>
+        <v>397.43</v>
       </c>
       <c r="K87" t="n">
-        <v>156.45</v>
+        <v>168.04</v>
       </c>
       <c r="L87" t="n">
-        <v>401.74</v>
+        <v>431.49</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>19</v>
       </c>
       <c r="J88" t="n">
-        <v>199.35</v>
+        <v>218.47</v>
       </c>
       <c r="K88" t="n">
-        <v>86.34</v>
+        <v>94.62</v>
       </c>
       <c r="L88" t="n">
-        <v>217.25</v>
+        <v>238.08</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-17.xlsx
+++ b/output/2025-07-17.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="F14" t="n">
-        <v>2.95</v>
+        <v>6.58</v>
       </c>
       <c r="G14" t="n">
-        <v>73.8</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>82</v>
+        <v>42.1</v>
       </c>
       <c r="I14" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-75.98</v>
+        <v>35.73</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.63</v>
+        <v>-28.53</v>
       </c>
       <c r="L14" t="n">
-        <v>76.03</v>
+        <v>45.72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:55:56</t>
+          <t>04:55:33</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="F15" t="n">
-        <v>4.67</v>
+        <v>5.16</v>
       </c>
       <c r="G15" t="n">
-        <v>57.2</v>
+        <v>73.5</v>
       </c>
       <c r="H15" t="n">
-        <v>85.8</v>
+        <v>26.6</v>
       </c>
       <c r="I15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-19.93</v>
+        <v>22.77</v>
       </c>
       <c r="K15" t="n">
-        <v>-55.53</v>
+        <v>6.58</v>
       </c>
       <c r="L15" t="n">
-        <v>59</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:58:42</t>
+          <t>04:56:49</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="F16" t="n">
-        <v>7.12</v>
+        <v>2.87</v>
       </c>
       <c r="G16" t="n">
-        <v>74.40000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>87.59999999999999</v>
+        <v>55</v>
       </c>
       <c r="I16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>40.53</v>
+        <v>36.73</v>
       </c>
       <c r="K16" t="n">
-        <v>76.51000000000001</v>
+        <v>2.53</v>
       </c>
       <c r="L16" t="n">
-        <v>86.58</v>
+        <v>36.82</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:03:15</t>
+          <t>05:00:41</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.97</v>
+        <v>2.24</v>
       </c>
       <c r="F17" t="n">
-        <v>3.93</v>
+        <v>6.56</v>
       </c>
       <c r="G17" t="n">
-        <v>91.90000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>85</v>
+        <v>54.4</v>
       </c>
       <c r="I17" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>-9.93</v>
+        <v>-8.77</v>
       </c>
       <c r="K17" t="n">
-        <v>-101</v>
+        <v>52.45</v>
       </c>
       <c r="L17" t="n">
-        <v>101.48</v>
+        <v>53.18</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:04:13</t>
+          <t>05:02:42</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.16</v>
+        <v>1.77</v>
       </c>
       <c r="F18" t="n">
-        <v>4.95</v>
+        <v>9.24</v>
       </c>
       <c r="G18" t="n">
-        <v>58.3</v>
+        <v>71</v>
       </c>
       <c r="H18" t="n">
-        <v>96.2</v>
+        <v>59.6</v>
       </c>
       <c r="I18" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>25.89</v>
+        <v>-29.27</v>
       </c>
       <c r="K18" t="n">
-        <v>76.23</v>
+        <v>26.56</v>
       </c>
       <c r="L18" t="n">
-        <v>80.51000000000001</v>
+        <v>39.53</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:05:18</t>
+          <t>05:04:36</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.96</v>
+        <v>2.8</v>
       </c>
       <c r="F19" t="n">
-        <v>10.07</v>
+        <v>10.23</v>
       </c>
       <c r="G19" t="n">
-        <v>66.2</v>
+        <v>65</v>
       </c>
       <c r="H19" t="n">
-        <v>86.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>55.86</v>
+        <v>10.24</v>
       </c>
       <c r="K19" t="n">
-        <v>68.12</v>
+        <v>-94.97</v>
       </c>
       <c r="L19" t="n">
-        <v>88.09</v>
+        <v>95.52</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:09:06</t>
+          <t>05:09:18</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.79</v>
+        <v>2.27</v>
       </c>
       <c r="F20" t="n">
-        <v>4.11</v>
+        <v>6.71</v>
       </c>
       <c r="G20" t="n">
-        <v>74</v>
+        <v>71.3</v>
       </c>
       <c r="H20" t="n">
-        <v>89.59999999999999</v>
+        <v>52.5</v>
       </c>
       <c r="I20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>77.87</v>
+        <v>107.83</v>
       </c>
       <c r="K20" t="n">
-        <v>-86.89</v>
+        <v>-10.6</v>
       </c>
       <c r="L20" t="n">
-        <v>116.68</v>
+        <v>108.35</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:10:25</t>
+          <t>05:10:44</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.18</v>
+        <v>1.82</v>
       </c>
       <c r="F21" t="n">
-        <v>10.23</v>
+        <v>4.71</v>
       </c>
       <c r="G21" t="n">
-        <v>62.5</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>85.40000000000001</v>
+        <v>40.7</v>
       </c>
       <c r="I21" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>16.7</v>
+        <v>60.8</v>
       </c>
       <c r="K21" t="n">
-        <v>-98.77</v>
+        <v>-63.02</v>
       </c>
       <c r="L21" t="n">
-        <v>100.17</v>
+        <v>87.56999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:12:08</t>
+          <t>05:12:58</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.66</v>
+        <v>2.03</v>
       </c>
       <c r="F22" t="n">
-        <v>8.74</v>
+        <v>2.33</v>
       </c>
       <c r="G22" t="n">
-        <v>72.59999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="H22" t="n">
-        <v>91.90000000000001</v>
+        <v>76</v>
       </c>
       <c r="I22" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J22" t="n">
-        <v>-116.36</v>
+        <v>23.97</v>
       </c>
       <c r="K22" t="n">
-        <v>39.76</v>
+        <v>73.45</v>
       </c>
       <c r="L22" t="n">
-        <v>122.97</v>
+        <v>77.26000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:18:21</t>
+          <t>05:16:27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="F23" t="n">
-        <v>3.16</v>
+        <v>3.61</v>
       </c>
       <c r="G23" t="n">
-        <v>63.9</v>
+        <v>62.1</v>
       </c>
       <c r="H23" t="n">
-        <v>95.09999999999999</v>
+        <v>56.7</v>
       </c>
       <c r="I23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-139.21</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>18.74</v>
+        <v>131.28</v>
       </c>
       <c r="L23" t="n">
-        <v>140.46</v>
+        <v>146.94</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:20:29</t>
+          <t>05:17:54</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="F24" t="n">
-        <v>4.07</v>
+        <v>4.1</v>
       </c>
       <c r="G24" t="n">
-        <v>86.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="H24" t="n">
-        <v>93.2</v>
+        <v>62</v>
       </c>
       <c r="I24" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>156.92</v>
+        <v>-15.83</v>
       </c>
       <c r="K24" t="n">
-        <v>11.02</v>
+        <v>-128.99</v>
       </c>
       <c r="L24" t="n">
-        <v>157.31</v>
+        <v>129.95</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:21:55</t>
+          <t>05:19:58</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="F25" t="n">
-        <v>5.21</v>
+        <v>5.36</v>
       </c>
       <c r="G25" t="n">
-        <v>79</v>
+        <v>78.5</v>
       </c>
       <c r="H25" t="n">
-        <v>91.40000000000001</v>
+        <v>44.1</v>
       </c>
       <c r="I25" t="n">
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>97.8</v>
+        <v>50.91</v>
       </c>
       <c r="K25" t="n">
-        <v>153.02</v>
+        <v>129.92</v>
       </c>
       <c r="L25" t="n">
-        <v>181.6</v>
+        <v>139.54</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:26:33</t>
+          <t>05:24:36</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.01</v>
+        <v>1.31</v>
       </c>
       <c r="F26" t="n">
-        <v>4.37</v>
+        <v>5.84</v>
       </c>
       <c r="G26" t="n">
-        <v>74.3</v>
+        <v>76.3</v>
       </c>
       <c r="H26" t="n">
-        <v>82.90000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>6.79</v>
+        <v>111.64</v>
       </c>
       <c r="K26" t="n">
-        <v>246.27</v>
+        <v>84.2</v>
       </c>
       <c r="L26" t="n">
-        <v>246.36</v>
+        <v>139.83</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:28:16</t>
+          <t>05:26:41</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="F27" t="n">
-        <v>10.23</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>71.7</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>88.90000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-402.28</v>
+        <v>-4.22</v>
       </c>
       <c r="K27" t="n">
-        <v>-27.55</v>
+        <v>139.5</v>
       </c>
       <c r="L27" t="n">
-        <v>403.22</v>
+        <v>139.57</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:29:55</t>
+          <t>05:28:29</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="F28" t="n">
-        <v>8.65</v>
+        <v>7.79</v>
       </c>
       <c r="G28" t="n">
-        <v>76.7</v>
+        <v>79.7</v>
       </c>
       <c r="H28" t="n">
-        <v>91.7</v>
+        <v>50.1</v>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-52.67</v>
+        <v>-178.54</v>
       </c>
       <c r="K28" t="n">
-        <v>226.38</v>
+        <v>50.01</v>
       </c>
       <c r="L28" t="n">
-        <v>232.43</v>
+        <v>185.41</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:37:37</t>
+          <t>05:39:49</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="F29" t="n">
-        <v>10.23</v>
+        <v>9.07</v>
       </c>
       <c r="G29" t="n">
-        <v>79.09999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="H29" t="n">
-        <v>83.8</v>
+        <v>66.7</v>
       </c>
       <c r="I29" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-48.38</v>
+        <v>20.98</v>
       </c>
       <c r="K29" t="n">
-        <v>-39.88</v>
+        <v>21.58</v>
       </c>
       <c r="L29" t="n">
-        <v>62.7</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:39:01</t>
+          <t>05:40:54</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="F30" t="n">
-        <v>8.279999999999999</v>
+        <v>5.73</v>
       </c>
       <c r="G30" t="n">
-        <v>56.7</v>
+        <v>69</v>
       </c>
       <c r="H30" t="n">
-        <v>87.7</v>
+        <v>70</v>
       </c>
       <c r="I30" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>-60.07</v>
+        <v>28.68</v>
       </c>
       <c r="K30" t="n">
-        <v>21.3</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="L30" t="n">
-        <v>63.73</v>
+        <v>29.97</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:40:05</t>
+          <t>05:42:41</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.01</v>
+        <v>1.87</v>
       </c>
       <c r="F31" t="n">
-        <v>8.119999999999999</v>
+        <v>5.37</v>
       </c>
       <c r="G31" t="n">
-        <v>82</v>
+        <v>68.7</v>
       </c>
       <c r="H31" t="n">
-        <v>78.40000000000001</v>
+        <v>57.1</v>
       </c>
       <c r="I31" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J31" t="n">
-        <v>-28.21</v>
+        <v>-23.5</v>
       </c>
       <c r="K31" t="n">
-        <v>47.33</v>
+        <v>-18.34</v>
       </c>
       <c r="L31" t="n">
-        <v>55.1</v>
+        <v>29.81</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:43:30</t>
+          <t>05:47:37</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.96</v>
+        <v>2.24</v>
       </c>
       <c r="F32" t="n">
-        <v>10.23</v>
+        <v>3.4</v>
       </c>
       <c r="G32" t="n">
-        <v>80.59999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>91.59999999999999</v>
+        <v>29.3</v>
       </c>
       <c r="I32" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>81.25</v>
+        <v>58.31</v>
       </c>
       <c r="K32" t="n">
-        <v>-94.26000000000001</v>
+        <v>-3.87</v>
       </c>
       <c r="L32" t="n">
-        <v>124.45</v>
+        <v>58.44</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:45:15</t>
+          <t>05:48:50</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="F33" t="n">
-        <v>6.13</v>
+        <v>7.05</v>
       </c>
       <c r="G33" t="n">
-        <v>74.8</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>89.8</v>
+        <v>76.5</v>
       </c>
       <c r="I33" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>24.13</v>
+        <v>-47.06</v>
       </c>
       <c r="K33" t="n">
-        <v>103.84</v>
+        <v>4.25</v>
       </c>
       <c r="L33" t="n">
-        <v>106.6</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:47:01</t>
+          <t>05:50:30</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="F34" t="n">
-        <v>9.880000000000001</v>
+        <v>6.22</v>
       </c>
       <c r="G34" t="n">
-        <v>72</v>
+        <v>76.8</v>
       </c>
       <c r="H34" t="n">
-        <v>84</v>
+        <v>26.7</v>
       </c>
       <c r="I34" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J34" t="n">
-        <v>-111.54</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>43.29</v>
+        <v>-10.02</v>
       </c>
       <c r="L34" t="n">
-        <v>119.64</v>
+        <v>70.01000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:51:00</t>
+          <t>05:56:26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="F35" t="n">
-        <v>5.14</v>
+        <v>5.13</v>
       </c>
       <c r="G35" t="n">
-        <v>88.5</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>87.5</v>
+        <v>33.8</v>
       </c>
       <c r="I35" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>5.48</v>
+        <v>-2.06</v>
       </c>
       <c r="K35" t="n">
-        <v>150.18</v>
+        <v>-72.79000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>150.28</v>
+        <v>72.81999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:52:51</t>
+          <t>05:58:44</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.81</v>
+        <v>2.18</v>
       </c>
       <c r="F36" t="n">
-        <v>8.34</v>
+        <v>6.43</v>
       </c>
       <c r="G36" t="n">
-        <v>73.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="H36" t="n">
-        <v>90.2</v>
+        <v>84.8</v>
       </c>
       <c r="I36" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>119.88</v>
+        <v>-69.95</v>
       </c>
       <c r="K36" t="n">
-        <v>26.24</v>
+        <v>20.17</v>
       </c>
       <c r="L36" t="n">
-        <v>122.72</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:54:55</t>
+          <t>06:00:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="F37" t="n">
         <v>10.23</v>
       </c>
       <c r="G37" t="n">
-        <v>82</v>
+        <v>71.8</v>
       </c>
       <c r="H37" t="n">
-        <v>87.40000000000001</v>
+        <v>30.3</v>
       </c>
       <c r="I37" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-157.26</v>
+        <v>67.44</v>
       </c>
       <c r="K37" t="n">
-        <v>-38.65</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>161.94</v>
+        <v>68.12</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:00:45</t>
+          <t>06:05:02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="F38" t="n">
-        <v>6.65</v>
+        <v>9.09</v>
       </c>
       <c r="G38" t="n">
-        <v>81.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>89.09999999999999</v>
+        <v>63.7</v>
       </c>
       <c r="I38" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>68.09999999999999</v>
+        <v>123.01</v>
       </c>
       <c r="K38" t="n">
-        <v>156.21</v>
+        <v>-55.44</v>
       </c>
       <c r="L38" t="n">
-        <v>170.41</v>
+        <v>134.92</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:02:23</t>
+          <t>06:06:59</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="F39" t="n">
-        <v>5.11</v>
+        <v>8.1</v>
       </c>
       <c r="G39" t="n">
-        <v>71.59999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="H39" t="n">
-        <v>91.8</v>
+        <v>42.7</v>
       </c>
       <c r="I39" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>172.08</v>
+        <v>20.42</v>
       </c>
       <c r="K39" t="n">
-        <v>-69.48999999999999</v>
+        <v>125.06</v>
       </c>
       <c r="L39" t="n">
-        <v>185.58</v>
+        <v>126.72</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:03:08</t>
+          <t>06:09:41</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.69</v>
+        <v>2.08</v>
       </c>
       <c r="F40" t="n">
-        <v>10.23</v>
+        <v>5.31</v>
       </c>
       <c r="G40" t="n">
-        <v>71.2</v>
+        <v>83.5</v>
       </c>
       <c r="H40" t="n">
-        <v>88.5</v>
+        <v>19.2</v>
       </c>
       <c r="I40" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>-75.17</v>
+        <v>26.15</v>
       </c>
       <c r="K40" t="n">
-        <v>223.88</v>
+        <v>-127.05</v>
       </c>
       <c r="L40" t="n">
-        <v>236.16</v>
+        <v>129.71</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:06:56</t>
+          <t>06:12:49</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="F41" t="n">
-        <v>4.1</v>
+        <v>9.26</v>
       </c>
       <c r="G41" t="n">
-        <v>67</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="H41" t="n">
-        <v>85.8</v>
+        <v>62.4</v>
       </c>
       <c r="I41" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-135.03</v>
+        <v>-73.31999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>271.25</v>
+        <v>160.46</v>
       </c>
       <c r="L41" t="n">
-        <v>303</v>
+        <v>176.42</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:08:16</t>
+          <t>06:14:58</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="F42" t="n">
-        <v>10.17</v>
+        <v>5.46</v>
       </c>
       <c r="G42" t="n">
-        <v>80.40000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="H42" t="n">
-        <v>96.7</v>
+        <v>12.8</v>
       </c>
       <c r="I42" t="n">
         <v>19</v>
       </c>
       <c r="J42" t="n">
-        <v>-250.28</v>
+        <v>-117.07</v>
       </c>
       <c r="K42" t="n">
-        <v>127.65</v>
+        <v>-165.11</v>
       </c>
       <c r="L42" t="n">
-        <v>280.95</v>
+        <v>202.4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:09:27</t>
+          <t>06:16:47</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="F43" t="n">
-        <v>9.58</v>
+        <v>8.73</v>
       </c>
       <c r="G43" t="n">
-        <v>74.3</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="H43" t="n">
-        <v>81.09999999999999</v>
+        <v>35.7</v>
       </c>
       <c r="I43" t="n">
         <v>21</v>
       </c>
       <c r="J43" t="n">
-        <v>67.04000000000001</v>
+        <v>45.58</v>
       </c>
       <c r="K43" t="n">
-        <v>269.1</v>
+        <v>164.25</v>
       </c>
       <c r="L43" t="n">
-        <v>277.33</v>
+        <v>170.45</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:17:12</t>
+          <t>06:26:10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.45</v>
+        <v>1.76</v>
       </c>
       <c r="F44" t="n">
-        <v>10.23</v>
+        <v>7.19</v>
       </c>
       <c r="G44" t="n">
-        <v>56.9</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>88.8</v>
+        <v>60.6</v>
       </c>
       <c r="I44" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>-73.95999999999999</v>
+        <v>-7.54</v>
       </c>
       <c r="K44" t="n">
-        <v>11.13</v>
+        <v>28.72</v>
       </c>
       <c r="L44" t="n">
-        <v>74.8</v>
+        <v>29.69</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:18:38</t>
+          <t>06:27:55</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="F45" t="n">
-        <v>6.93</v>
+        <v>7.85</v>
       </c>
       <c r="G45" t="n">
-        <v>55.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="H45" t="n">
-        <v>98.40000000000001</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>-46.07</v>
+        <v>23.24</v>
       </c>
       <c r="K45" t="n">
-        <v>-36.32</v>
+        <v>33.61</v>
       </c>
       <c r="L45" t="n">
-        <v>58.66</v>
+        <v>40.86</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:20:56</t>
+          <t>06:29:09</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="F46" t="n">
-        <v>9.720000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="G46" t="n">
-        <v>55.8</v>
+        <v>78</v>
       </c>
       <c r="H46" t="n">
-        <v>87.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="I46" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>65.26000000000001</v>
+        <v>-21.9</v>
       </c>
       <c r="K46" t="n">
-        <v>-33.53</v>
+        <v>-31.33</v>
       </c>
       <c r="L46" t="n">
-        <v>73.37</v>
+        <v>38.22</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:25:47</t>
+          <t>06:33:28</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.15</v>
+        <v>2.64</v>
       </c>
       <c r="F47" t="n">
-        <v>10.23</v>
+        <v>9.83</v>
       </c>
       <c r="G47" t="n">
-        <v>79.3</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="H47" t="n">
-        <v>90.09999999999999</v>
+        <v>50</v>
       </c>
       <c r="I47" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>-42.72</v>
+        <v>33.28</v>
       </c>
       <c r="K47" t="n">
-        <v>66.27</v>
+        <v>55.68</v>
       </c>
       <c r="L47" t="n">
-        <v>78.84</v>
+        <v>64.86</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:28:11</t>
+          <t>06:34:57</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.53</v>
+        <v>1.96</v>
       </c>
       <c r="F48" t="n">
-        <v>7.28</v>
+        <v>6.87</v>
       </c>
       <c r="G48" t="n">
-        <v>70</v>
+        <v>77.5</v>
       </c>
       <c r="H48" t="n">
-        <v>91.2</v>
+        <v>47.5</v>
       </c>
       <c r="I48" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-63.28</v>
+        <v>-3.87</v>
       </c>
       <c r="K48" t="n">
-        <v>40.58</v>
+        <v>-64.72</v>
       </c>
       <c r="L48" t="n">
-        <v>75.17</v>
+        <v>64.84</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:29:49</t>
+          <t>06:36:39</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.48</v>
+        <v>1.93</v>
       </c>
       <c r="F49" t="n">
-        <v>5.96</v>
+        <v>8.6</v>
       </c>
       <c r="G49" t="n">
-        <v>62</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>88.09999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="I49" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>101.97</v>
+        <v>67.44</v>
       </c>
       <c r="K49" t="n">
-        <v>-40.97</v>
+        <v>-89.14</v>
       </c>
       <c r="L49" t="n">
-        <v>109.9</v>
+        <v>111.78</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:35:47</t>
+          <t>06:40:03</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="F50" t="n">
-        <v>9.449999999999999</v>
+        <v>10.23</v>
       </c>
       <c r="G50" t="n">
-        <v>70.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="H50" t="n">
-        <v>86.8</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>109.08</v>
+        <v>98.97</v>
       </c>
       <c r="K50" t="n">
-        <v>136.2</v>
+        <v>-133.07</v>
       </c>
       <c r="L50" t="n">
-        <v>174.5</v>
+        <v>165.84</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:37:10</t>
+          <t>06:42:46</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="F51" t="n">
-        <v>5.63</v>
+        <v>10.23</v>
       </c>
       <c r="G51" t="n">
-        <v>61.4</v>
+        <v>61.9</v>
       </c>
       <c r="H51" t="n">
-        <v>94.40000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="I51" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>16.61</v>
+        <v>31.14</v>
       </c>
       <c r="K51" t="n">
-        <v>-153.08</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>153.98</v>
+        <v>84.15000000000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:38:38</t>
+          <t>06:43:58</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>1.8</v>
+        <v>2.44</v>
       </c>
       <c r="F52" t="n">
-        <v>5.57</v>
+        <v>8.93</v>
       </c>
       <c r="G52" t="n">
-        <v>81.3</v>
+        <v>77.5</v>
       </c>
       <c r="H52" t="n">
-        <v>89.59999999999999</v>
+        <v>41.5</v>
       </c>
       <c r="I52" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>-94.29000000000001</v>
+        <v>49.48</v>
       </c>
       <c r="K52" t="n">
-        <v>-27.53</v>
+        <v>84.54000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>98.23</v>
+        <v>97.95999999999999</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:43:33</t>
+          <t>06:49:23</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.94</v>
+        <v>2.27</v>
       </c>
       <c r="F53" t="n">
-        <v>8.85</v>
+        <v>10.23</v>
       </c>
       <c r="G53" t="n">
-        <v>74.09999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="H53" t="n">
-        <v>91.2</v>
+        <v>27</v>
       </c>
       <c r="I53" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>158.2</v>
+        <v>-83.3</v>
       </c>
       <c r="K53" t="n">
-        <v>-199.28</v>
+        <v>105.9</v>
       </c>
       <c r="L53" t="n">
-        <v>254.44</v>
+        <v>134.74</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:45:30</t>
+          <t>06:51:38</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="F54" t="n">
-        <v>2.11</v>
+        <v>6.16</v>
       </c>
       <c r="G54" t="n">
-        <v>79.90000000000001</v>
+        <v>77</v>
       </c>
       <c r="H54" t="n">
-        <v>87.8</v>
+        <v>64.2</v>
       </c>
       <c r="I54" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>74.79000000000001</v>
+        <v>-16.46</v>
       </c>
       <c r="K54" t="n">
-        <v>-56.39</v>
+        <v>-113.95</v>
       </c>
       <c r="L54" t="n">
-        <v>93.67</v>
+        <v>115.13</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:47:38</t>
+          <t>06:53:24</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.05</v>
+        <v>2.26</v>
       </c>
       <c r="F55" t="n">
-        <v>8.779999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>67.2</v>
+        <v>61.5</v>
       </c>
       <c r="H55" t="n">
-        <v>94.5</v>
+        <v>58</v>
       </c>
       <c r="I55" t="n">
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>46.13</v>
+        <v>92.84</v>
       </c>
       <c r="K55" t="n">
-        <v>-178.07</v>
+        <v>-117.63</v>
       </c>
       <c r="L55" t="n">
-        <v>183.95</v>
+        <v>149.86</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:50:41</t>
+          <t>06:57:27</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.55</v>
+        <v>2.04</v>
       </c>
       <c r="F56" t="n">
-        <v>6.43</v>
+        <v>9.59</v>
       </c>
       <c r="G56" t="n">
-        <v>74.8</v>
+        <v>63.6</v>
       </c>
       <c r="H56" t="n">
-        <v>88.3</v>
+        <v>57.8</v>
       </c>
       <c r="I56" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>-248.06</v>
+        <v>10.19</v>
       </c>
       <c r="K56" t="n">
-        <v>-103.95</v>
+        <v>-145.19</v>
       </c>
       <c r="L56" t="n">
-        <v>268.96</v>
+        <v>145.55</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:51:46</t>
+          <t>06:58:17</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1.81</v>
+        <v>2.35</v>
       </c>
       <c r="F57" t="n">
-        <v>4.09</v>
+        <v>10.23</v>
       </c>
       <c r="G57" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H57" t="n">
-        <v>85</v>
+        <v>63.6</v>
       </c>
       <c r="I57" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J57" t="n">
-        <v>147.47</v>
+        <v>120.66</v>
       </c>
       <c r="K57" t="n">
-        <v>-228.3</v>
+        <v>119.02</v>
       </c>
       <c r="L57" t="n">
-        <v>271.79</v>
+        <v>169.48</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:53:43</t>
+          <t>06:59:43</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="F58" t="n">
-        <v>9.15</v>
+        <v>7.72</v>
       </c>
       <c r="G58" t="n">
-        <v>69.09999999999999</v>
+        <v>62.7</v>
       </c>
       <c r="H58" t="n">
-        <v>86</v>
+        <v>59.4</v>
       </c>
       <c r="I58" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>-2.34</v>
+        <v>132.26</v>
       </c>
       <c r="K58" t="n">
-        <v>360.41</v>
+        <v>-55.96</v>
       </c>
       <c r="L58" t="n">
-        <v>360.42</v>
+        <v>143.62</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:05:12</t>
+          <t>07:11:30</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="F59" t="n">
-        <v>6.22</v>
+        <v>10.23</v>
       </c>
       <c r="G59" t="n">
-        <v>82.09999999999999</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="H59" t="n">
-        <v>87.7</v>
+        <v>50.8</v>
       </c>
       <c r="I59" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>-10.95</v>
+        <v>0.98</v>
       </c>
       <c r="K59" t="n">
-        <v>-63.73</v>
+        <v>6.21</v>
       </c>
       <c r="L59" t="n">
-        <v>64.67</v>
+        <v>6.28</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:07:05</t>
+          <t>07:12:51</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>1.71</v>
+        <v>2.15</v>
       </c>
       <c r="F60" t="n">
-        <v>6.32</v>
+        <v>7.1</v>
       </c>
       <c r="G60" t="n">
-        <v>74.3</v>
+        <v>55.2</v>
       </c>
       <c r="H60" t="n">
-        <v>90.40000000000001</v>
+        <v>50.9</v>
       </c>
       <c r="I60" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>12.27</v>
+        <v>-17.3</v>
       </c>
       <c r="K60" t="n">
-        <v>-63.94</v>
+        <v>29.7</v>
       </c>
       <c r="L60" t="n">
-        <v>65.11</v>
+        <v>34.37</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:09:29</t>
+          <t>07:14:05</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.27</v>
+        <v>1.52</v>
       </c>
       <c r="F61" t="n">
-        <v>10.23</v>
+        <v>4.37</v>
       </c>
       <c r="G61" t="n">
-        <v>69.8</v>
+        <v>65.2</v>
       </c>
       <c r="H61" t="n">
-        <v>83.3</v>
+        <v>76.3</v>
       </c>
       <c r="I61" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-123.41</v>
+        <v>3.48</v>
       </c>
       <c r="K61" t="n">
-        <v>39.45</v>
+        <v>35.36</v>
       </c>
       <c r="L61" t="n">
-        <v>129.56</v>
+        <v>35.53</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:14:55</t>
+          <t>07:18:26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="F62" t="n">
-        <v>7.9</v>
+        <v>8.09</v>
       </c>
       <c r="G62" t="n">
-        <v>63.3</v>
+        <v>77.8</v>
       </c>
       <c r="H62" t="n">
-        <v>85.59999999999999</v>
+        <v>62.7</v>
       </c>
       <c r="I62" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>68.65000000000001</v>
+        <v>-20.23</v>
       </c>
       <c r="K62" t="n">
-        <v>-47.18</v>
+        <v>61.22</v>
       </c>
       <c r="L62" t="n">
-        <v>83.3</v>
+        <v>64.48</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:16:03</t>
+          <t>07:20:09</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="F63" t="n">
-        <v>8.73</v>
+        <v>4.34</v>
       </c>
       <c r="G63" t="n">
-        <v>85</v>
+        <v>79.5</v>
       </c>
       <c r="H63" t="n">
-        <v>91.3</v>
+        <v>78.5</v>
       </c>
       <c r="I63" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-51.94</v>
+        <v>49.67</v>
       </c>
       <c r="K63" t="n">
-        <v>-93.86</v>
+        <v>-15.94</v>
       </c>
       <c r="L63" t="n">
-        <v>107.28</v>
+        <v>52.17</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:18:04</t>
+          <t>07:21:59</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.97</v>
+        <v>2.5</v>
       </c>
       <c r="F64" t="n">
         <v>10.23</v>
       </c>
       <c r="G64" t="n">
-        <v>67.90000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="H64" t="n">
-        <v>85.59999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>-24.41</v>
+        <v>69.98</v>
       </c>
       <c r="K64" t="n">
-        <v>108.87</v>
+        <v>19.2</v>
       </c>
       <c r="L64" t="n">
-        <v>111.57</v>
+        <v>72.56</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:23:12</t>
+          <t>07:26:29</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.19</v>
+        <v>1.64</v>
       </c>
       <c r="F65" t="n">
-        <v>9.880000000000001</v>
+        <v>6.43</v>
       </c>
       <c r="G65" t="n">
-        <v>72.2</v>
+        <v>64.8</v>
       </c>
       <c r="H65" t="n">
-        <v>87.90000000000001</v>
+        <v>50.9</v>
       </c>
       <c r="I65" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>122.78</v>
+        <v>-73.48999999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>75.18000000000001</v>
+        <v>49.77</v>
       </c>
       <c r="L65" t="n">
-        <v>143.97</v>
+        <v>88.75</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:24:43</t>
+          <t>07:28:39</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="F66" t="n">
-        <v>5.48</v>
+        <v>7.6</v>
       </c>
       <c r="G66" t="n">
-        <v>76.8</v>
+        <v>49.8</v>
       </c>
       <c r="H66" t="n">
-        <v>86.40000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-10.07</v>
+        <v>53.26</v>
       </c>
       <c r="K66" t="n">
-        <v>156.63</v>
+        <v>55.19</v>
       </c>
       <c r="L66" t="n">
-        <v>156.95</v>
+        <v>76.7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:26:51</t>
+          <t>07:30:42</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.93</v>
+        <v>2.11</v>
       </c>
       <c r="F67" t="n">
-        <v>8.949999999999999</v>
+        <v>10.23</v>
       </c>
       <c r="G67" t="n">
-        <v>68</v>
+        <v>69.2</v>
       </c>
       <c r="H67" t="n">
-        <v>94.09999999999999</v>
+        <v>59</v>
       </c>
       <c r="I67" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J67" t="n">
-        <v>-20.35</v>
+        <v>50.6</v>
       </c>
       <c r="K67" t="n">
-        <v>-123.83</v>
+        <v>66.91</v>
       </c>
       <c r="L67" t="n">
-        <v>125.49</v>
+        <v>83.89</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:32:04</t>
+          <t>07:34:45</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1.87</v>
+        <v>2.18</v>
       </c>
       <c r="F68" t="n">
-        <v>10.23</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="G68" t="n">
-        <v>77.5</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="H68" t="n">
-        <v>86.7</v>
+        <v>50.6</v>
       </c>
       <c r="I68" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>-33.68</v>
+        <v>93.06</v>
       </c>
       <c r="K68" t="n">
-        <v>208.6</v>
+        <v>276.32</v>
       </c>
       <c r="L68" t="n">
-        <v>211.3</v>
+        <v>291.57</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:34:06</t>
+          <t>07:35:55</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="F69" t="n">
-        <v>9.18</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G69" t="n">
-        <v>66</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="H69" t="n">
-        <v>86.2</v>
+        <v>84.8</v>
       </c>
       <c r="I69" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>-34.53</v>
+        <v>135.14</v>
       </c>
       <c r="K69" t="n">
-        <v>-165.07</v>
+        <v>-105.3</v>
       </c>
       <c r="L69" t="n">
-        <v>168.65</v>
+        <v>171.32</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:35:27</t>
+          <t>07:36:54</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.53</v>
+        <v>2.72</v>
       </c>
       <c r="F70" t="n">
-        <v>9.23</v>
+        <v>10.23</v>
       </c>
       <c r="G70" t="n">
-        <v>72.2</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H70" t="n">
-        <v>90.7</v>
+        <v>80.5</v>
       </c>
       <c r="I70" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>25.62</v>
+        <v>30.27</v>
       </c>
       <c r="K70" t="n">
-        <v>241.74</v>
+        <v>-112.84</v>
       </c>
       <c r="L70" t="n">
-        <v>243.09</v>
+        <v>116.83</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:41:06</t>
+          <t>07:41:54</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="F71" t="n">
-        <v>10.23</v>
+        <v>6.87</v>
       </c>
       <c r="G71" t="n">
-        <v>70.5</v>
+        <v>82.5</v>
       </c>
       <c r="H71" t="n">
-        <v>89.59999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="I71" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-255.61</v>
+        <v>71.88</v>
       </c>
       <c r="K71" t="n">
-        <v>107.3</v>
+        <v>-147.3</v>
       </c>
       <c r="L71" t="n">
-        <v>277.22</v>
+        <v>163.9</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:43:10</t>
+          <t>07:43:26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.09</v>
+        <v>2.64</v>
       </c>
       <c r="F72" t="n">
-        <v>10.14</v>
+        <v>5.86</v>
       </c>
       <c r="G72" t="n">
-        <v>76.09999999999999</v>
+        <v>71</v>
       </c>
       <c r="H72" t="n">
-        <v>95.3</v>
+        <v>57.1</v>
       </c>
       <c r="I72" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J72" t="n">
-        <v>74.34999999999999</v>
+        <v>-86.73</v>
       </c>
       <c r="K72" t="n">
-        <v>312.72</v>
+        <v>183.84</v>
       </c>
       <c r="L72" t="n">
-        <v>321.44</v>
+        <v>203.27</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:45:09</t>
+          <t>07:45:43</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="F73" t="n">
         <v>10.23</v>
       </c>
       <c r="G73" t="n">
-        <v>66.09999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="H73" t="n">
-        <v>90.2</v>
+        <v>32.6</v>
       </c>
       <c r="I73" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-114.79</v>
+        <v>94.64</v>
       </c>
       <c r="K73" t="n">
-        <v>208.71</v>
+        <v>138.73</v>
       </c>
       <c r="L73" t="n">
-        <v>238.19</v>
+        <v>167.94</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:56:23</t>
+          <t>07:57:24</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.25</v>
+        <v>2.54</v>
       </c>
       <c r="F74" t="n">
-        <v>8.640000000000001</v>
+        <v>7.08</v>
       </c>
       <c r="G74" t="n">
-        <v>54.9</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="H74" t="n">
-        <v>97.40000000000001</v>
+        <v>11.6</v>
       </c>
       <c r="I74" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-46.8</v>
+        <v>-44.73</v>
       </c>
       <c r="K74" t="n">
-        <v>66.09</v>
+        <v>7.62</v>
       </c>
       <c r="L74" t="n">
-        <v>80.98</v>
+        <v>45.37</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:59:06</t>
+          <t>07:57:47</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.53</v>
+        <v>2.15</v>
       </c>
       <c r="F75" t="n">
         <v>10.23</v>
       </c>
       <c r="G75" t="n">
-        <v>68.3</v>
+        <v>63.2</v>
       </c>
       <c r="H75" t="n">
         <v>88.59999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-67.73</v>
+        <v>-20.21</v>
       </c>
       <c r="K75" t="n">
-        <v>3.49</v>
+        <v>33.03</v>
       </c>
       <c r="L75" t="n">
-        <v>67.81999999999999</v>
+        <v>38.72</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:00:02</t>
+          <t>07:59:26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>1.76</v>
+        <v>2.54</v>
       </c>
       <c r="F76" t="n">
         <v>10.23</v>
       </c>
       <c r="G76" t="n">
-        <v>82.5</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="H76" t="n">
-        <v>86.90000000000001</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>-51.84</v>
+        <v>31.84</v>
       </c>
       <c r="K76" t="n">
-        <v>-33.86</v>
+        <v>13.15</v>
       </c>
       <c r="L76" t="n">
-        <v>61.92</v>
+        <v>34.45</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:04:35</t>
+          <t>08:04:32</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="F77" t="n">
         <v>10.23</v>
       </c>
       <c r="G77" t="n">
-        <v>72.90000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="H77" t="n">
-        <v>84.3</v>
+        <v>61</v>
       </c>
       <c r="I77" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>-73.59</v>
+        <v>-3.49</v>
       </c>
       <c r="K77" t="n">
-        <v>-10.07</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="L77" t="n">
-        <v>74.28</v>
+        <v>72.52</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:06:36</t>
+          <t>08:05:08</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="F78" t="n">
-        <v>9.99</v>
+        <v>10.23</v>
       </c>
       <c r="G78" t="n">
-        <v>72.90000000000001</v>
+        <v>63.3</v>
       </c>
       <c r="H78" t="n">
-        <v>86.09999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I78" t="n">
         <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>16.87</v>
+        <v>52.06</v>
       </c>
       <c r="K78" t="n">
-        <v>125.51</v>
+        <v>27.54</v>
       </c>
       <c r="L78" t="n">
-        <v>126.64</v>
+        <v>58.89</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:08:40</t>
+          <t>08:07:33</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.24</v>
+        <v>1.62</v>
       </c>
       <c r="F79" t="n">
-        <v>6.12</v>
+        <v>7.73</v>
       </c>
       <c r="G79" t="n">
-        <v>69.59999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="H79" t="n">
-        <v>95.3</v>
+        <v>57.3</v>
       </c>
       <c r="I79" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>0.33</v>
+        <v>-1.65</v>
       </c>
       <c r="K79" t="n">
-        <v>89.47</v>
+        <v>-45.48</v>
       </c>
       <c r="L79" t="n">
-        <v>89.48</v>
+        <v>45.51</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:14:14</t>
+          <t>08:12:11</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="F80" t="n">
-        <v>4.3</v>
+        <v>10.23</v>
       </c>
       <c r="G80" t="n">
-        <v>81.09999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="H80" t="n">
-        <v>86.7</v>
+        <v>62.2</v>
       </c>
       <c r="I80" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-95.84999999999999</v>
+        <v>-27.08</v>
       </c>
       <c r="K80" t="n">
-        <v>-63.34</v>
+        <v>94.53</v>
       </c>
       <c r="L80" t="n">
-        <v>114.89</v>
+        <v>98.33</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:15:15</t>
+          <t>08:14:33</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="F81" t="n">
-        <v>9.93</v>
+        <v>10.23</v>
       </c>
       <c r="G81" t="n">
-        <v>68.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="H81" t="n">
-        <v>88.7</v>
+        <v>44.9</v>
       </c>
       <c r="I81" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>54.87</v>
+        <v>84.91</v>
       </c>
       <c r="K81" t="n">
-        <v>161.95</v>
+        <v>-14.05</v>
       </c>
       <c r="L81" t="n">
-        <v>170.99</v>
+        <v>86.06</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:16:38</t>
+          <t>08:15:45</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.05</v>
+        <v>2.32</v>
       </c>
       <c r="F82" t="n">
-        <v>5.84</v>
+        <v>10.09</v>
       </c>
       <c r="G82" t="n">
-        <v>72.8</v>
+        <v>70.8</v>
       </c>
       <c r="H82" t="n">
-        <v>91.90000000000001</v>
+        <v>63.2</v>
       </c>
       <c r="I82" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J82" t="n">
-        <v>-50.02</v>
+        <v>101.92</v>
       </c>
       <c r="K82" t="n">
-        <v>84.63</v>
+        <v>13.44</v>
       </c>
       <c r="L82" t="n">
-        <v>98.31</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:20:38</t>
+          <t>08:19:56</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.24</v>
+        <v>2.52</v>
       </c>
       <c r="F83" t="n">
-        <v>10.23</v>
+        <v>8.08</v>
       </c>
       <c r="G83" t="n">
-        <v>75.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="H83" t="n">
-        <v>87.40000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="I83" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J83" t="n">
-        <v>131.24</v>
+        <v>109.44</v>
       </c>
       <c r="K83" t="n">
-        <v>-107.31</v>
+        <v>122.56</v>
       </c>
       <c r="L83" t="n">
-        <v>169.52</v>
+        <v>164.31</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:22:27</t>
+          <t>08:20:59</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.28</v>
+        <v>2.03</v>
       </c>
       <c r="F84" t="n">
-        <v>10.23</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="G84" t="n">
-        <v>72.3</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="H84" t="n">
-        <v>87.90000000000001</v>
+        <v>60.3</v>
       </c>
       <c r="I84" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J84" t="n">
-        <v>-168.34</v>
+        <v>-57.1</v>
       </c>
       <c r="K84" t="n">
-        <v>67.68000000000001</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="L84" t="n">
-        <v>181.43</v>
+        <v>87.14</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:23:52</t>
+          <t>08:22:28</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.11</v>
+        <v>2.92</v>
       </c>
       <c r="F85" t="n">
-        <v>10.04</v>
+        <v>10.23</v>
       </c>
       <c r="G85" t="n">
-        <v>80.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="H85" t="n">
-        <v>85.7</v>
+        <v>42.9</v>
       </c>
       <c r="I85" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-146.25</v>
+        <v>205.76</v>
       </c>
       <c r="K85" t="n">
-        <v>-132.73</v>
+        <v>15.4</v>
       </c>
       <c r="L85" t="n">
-        <v>197.5</v>
+        <v>206.34</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:29:05</t>
+          <t>08:25:59</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.85</v>
+        <v>2.31</v>
       </c>
       <c r="F86" t="n">
         <v>10.23</v>
       </c>
       <c r="G86" t="n">
-        <v>68.5</v>
+        <v>72.2</v>
       </c>
       <c r="H86" t="n">
-        <v>96.5</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>-240.97</v>
+        <v>-12.99</v>
       </c>
       <c r="K86" t="n">
-        <v>105.63</v>
+        <v>149.49</v>
       </c>
       <c r="L86" t="n">
-        <v>263.1</v>
+        <v>150.05</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:31:14</t>
+          <t>08:27:34</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.65</v>
+        <v>2.26</v>
       </c>
       <c r="F87" t="n">
-        <v>10.23</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G87" t="n">
-        <v>79.09999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="H87" t="n">
-        <v>89</v>
+        <v>49.2</v>
       </c>
       <c r="I87" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J87" t="n">
-        <v>397.43</v>
+        <v>-149.63</v>
       </c>
       <c r="K87" t="n">
-        <v>168.04</v>
+        <v>-123.28</v>
       </c>
       <c r="L87" t="n">
-        <v>431.49</v>
+        <v>193.87</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:32:09</t>
+          <t>08:28:55</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.82</v>
+        <v>2.18</v>
       </c>
       <c r="F88" t="n">
-        <v>10.23</v>
+        <v>6.45</v>
       </c>
       <c r="G88" t="n">
-        <v>82.3</v>
+        <v>75.3</v>
       </c>
       <c r="H88" t="n">
-        <v>86.7</v>
+        <v>42.2</v>
       </c>
       <c r="I88" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J88" t="n">
-        <v>218.47</v>
+        <v>89.81999999999999</v>
       </c>
       <c r="K88" t="n">
-        <v>94.62</v>
+        <v>-43.26</v>
       </c>
       <c r="L88" t="n">
-        <v>238.08</v>
+        <v>99.7</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-17.xlsx
+++ b/output/2025-07-17.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="F14" t="n">
-        <v>6.58</v>
+        <v>4.5</v>
       </c>
       <c r="G14" t="n">
-        <v>66.90000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>42.1</v>
+        <v>100</v>
       </c>
       <c r="I14" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>35.73</v>
+        <v>-11.83</v>
       </c>
       <c r="K14" t="n">
-        <v>-28.53</v>
+        <v>26.72</v>
       </c>
       <c r="L14" t="n">
-        <v>45.72</v>
+        <v>29.22</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:55:33</t>
+          <t>04:56:36</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.79</v>
+        <v>3.62</v>
       </c>
       <c r="F15" t="n">
-        <v>5.16</v>
+        <v>10.23</v>
       </c>
       <c r="G15" t="n">
-        <v>73.5</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>26.6</v>
+        <v>56</v>
       </c>
       <c r="I15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J15" t="n">
-        <v>22.77</v>
+        <v>35.53</v>
       </c>
       <c r="K15" t="n">
-        <v>6.58</v>
+        <v>-1.84</v>
       </c>
       <c r="L15" t="n">
-        <v>23.7</v>
+        <v>35.58</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:56:49</t>
+          <t>04:58:46</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.09</v>
+        <v>1.78</v>
       </c>
       <c r="F16" t="n">
-        <v>2.87</v>
+        <v>7.25</v>
       </c>
       <c r="G16" t="n">
-        <v>93.09999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="H16" t="n">
-        <v>55</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>36.73</v>
+        <v>19.73</v>
       </c>
       <c r="K16" t="n">
-        <v>2.53</v>
+        <v>-28.27</v>
       </c>
       <c r="L16" t="n">
-        <v>36.82</v>
+        <v>34.47</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:00:41</t>
+          <t>05:04:53</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.24</v>
+        <v>1.55</v>
       </c>
       <c r="F17" t="n">
-        <v>6.56</v>
+        <v>5.45</v>
       </c>
       <c r="G17" t="n">
-        <v>75.59999999999999</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>54.4</v>
+        <v>30.9</v>
       </c>
       <c r="I17" t="n">
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>-8.77</v>
+        <v>-7.63</v>
       </c>
       <c r="K17" t="n">
-        <v>52.45</v>
+        <v>42.27</v>
       </c>
       <c r="L17" t="n">
-        <v>53.18</v>
+        <v>42.95</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:02:42</t>
+          <t>05:06:15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="F18" t="n">
-        <v>9.24</v>
+        <v>6.8</v>
       </c>
       <c r="G18" t="n">
-        <v>71</v>
+        <v>72.8</v>
       </c>
       <c r="H18" t="n">
-        <v>59.6</v>
+        <v>56.6</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>-29.27</v>
+        <v>50.47</v>
       </c>
       <c r="K18" t="n">
-        <v>26.56</v>
+        <v>16.07</v>
       </c>
       <c r="L18" t="n">
-        <v>39.53</v>
+        <v>52.97</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:04:36</t>
+          <t>05:07:16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.8</v>
+        <v>1.74</v>
       </c>
       <c r="F19" t="n">
-        <v>10.23</v>
+        <v>2.33</v>
       </c>
       <c r="G19" t="n">
-        <v>65</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>100</v>
+        <v>14.3</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>10.24</v>
+        <v>20.4</v>
       </c>
       <c r="K19" t="n">
-        <v>-94.97</v>
+        <v>-47.07</v>
       </c>
       <c r="L19" t="n">
-        <v>95.52</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:09:18</t>
+          <t>05:13:02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="F20" t="n">
-        <v>6.71</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>71.3</v>
+        <v>68.5</v>
       </c>
       <c r="H20" t="n">
-        <v>52.5</v>
+        <v>23.7</v>
       </c>
       <c r="I20" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>107.83</v>
+        <v>2.25</v>
       </c>
       <c r="K20" t="n">
-        <v>-10.6</v>
+        <v>-119.01</v>
       </c>
       <c r="L20" t="n">
-        <v>108.35</v>
+        <v>119.03</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:10:44</t>
+          <t>05:14:31</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="F21" t="n">
-        <v>4.71</v>
+        <v>6.14</v>
       </c>
       <c r="G21" t="n">
-        <v>90.09999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>40.7</v>
+        <v>66.3</v>
       </c>
       <c r="I21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>60.8</v>
+        <v>74.31</v>
       </c>
       <c r="K21" t="n">
-        <v>-63.02</v>
+        <v>-43.04</v>
       </c>
       <c r="L21" t="n">
-        <v>87.56999999999999</v>
+        <v>85.87</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:12:58</t>
+          <t>05:16:04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.03</v>
+        <v>1.82</v>
       </c>
       <c r="F22" t="n">
-        <v>2.33</v>
+        <v>4.52</v>
       </c>
       <c r="G22" t="n">
-        <v>68.8</v>
+        <v>68.7</v>
       </c>
       <c r="H22" t="n">
-        <v>76</v>
+        <v>61.6</v>
       </c>
       <c r="I22" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>23.97</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>73.45</v>
+        <v>-50.84</v>
       </c>
       <c r="L22" t="n">
-        <v>77.26000000000001</v>
+        <v>85.56</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:16:27</t>
+          <t>05:19:15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="F23" t="n">
-        <v>3.61</v>
+        <v>8.65</v>
       </c>
       <c r="G23" t="n">
-        <v>62.1</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>56.7</v>
+        <v>49</v>
       </c>
       <c r="I23" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>66.01000000000001</v>
+        <v>-75.52</v>
       </c>
       <c r="K23" t="n">
-        <v>131.28</v>
+        <v>129.11</v>
       </c>
       <c r="L23" t="n">
-        <v>146.94</v>
+        <v>149.57</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:17:54</t>
+          <t>05:20:19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.48</v>
+        <v>2.03</v>
       </c>
       <c r="F24" t="n">
-        <v>4.1</v>
+        <v>8.94</v>
       </c>
       <c r="G24" t="n">
-        <v>71.5</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>62</v>
+        <v>51.4</v>
       </c>
       <c r="I24" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-15.83</v>
+        <v>-3.5</v>
       </c>
       <c r="K24" t="n">
-        <v>-128.99</v>
+        <v>-96.90000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>129.95</v>
+        <v>96.95999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:19:58</t>
+          <t>05:22:12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.22</v>
+        <v>1.66</v>
       </c>
       <c r="F25" t="n">
-        <v>5.36</v>
+        <v>10.23</v>
       </c>
       <c r="G25" t="n">
-        <v>78.5</v>
+        <v>73.3</v>
       </c>
       <c r="H25" t="n">
-        <v>44.1</v>
+        <v>45.1</v>
       </c>
       <c r="I25" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>50.91</v>
+        <v>40.55</v>
       </c>
       <c r="K25" t="n">
-        <v>129.92</v>
+        <v>-116.66</v>
       </c>
       <c r="L25" t="n">
-        <v>139.54</v>
+        <v>123.51</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:24:36</t>
+          <t>05:28:26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.31</v>
+        <v>2.41</v>
       </c>
       <c r="F26" t="n">
-        <v>5.84</v>
+        <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>76.3</v>
+        <v>72.2</v>
       </c>
       <c r="H26" t="n">
-        <v>86.59999999999999</v>
+        <v>61.8</v>
       </c>
       <c r="I26" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>111.64</v>
+        <v>71.63</v>
       </c>
       <c r="K26" t="n">
-        <v>84.2</v>
+        <v>-174.64</v>
       </c>
       <c r="L26" t="n">
-        <v>139.83</v>
+        <v>188.76</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:26:41</t>
+          <t>05:30:14</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.62</v>
+        <v>1.94</v>
       </c>
       <c r="F27" t="n">
-        <v>9.119999999999999</v>
+        <v>7.56</v>
       </c>
       <c r="G27" t="n">
-        <v>67.90000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="H27" t="n">
-        <v>77.90000000000001</v>
+        <v>62.8</v>
       </c>
       <c r="I27" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>-4.22</v>
+        <v>163.28</v>
       </c>
       <c r="K27" t="n">
-        <v>139.5</v>
+        <v>45.92</v>
       </c>
       <c r="L27" t="n">
-        <v>139.57</v>
+        <v>169.62</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:28:29</t>
+          <t>05:31:55</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="F28" t="n">
-        <v>7.79</v>
+        <v>7.02</v>
       </c>
       <c r="G28" t="n">
-        <v>79.7</v>
+        <v>84.8</v>
       </c>
       <c r="H28" t="n">
-        <v>50.1</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>-178.54</v>
+        <v>172.93</v>
       </c>
       <c r="K28" t="n">
-        <v>50.01</v>
+        <v>91.55</v>
       </c>
       <c r="L28" t="n">
-        <v>185.41</v>
+        <v>195.67</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:39:49</t>
+          <t>05:40:45</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="F29" t="n">
-        <v>9.07</v>
+        <v>10.1</v>
       </c>
       <c r="G29" t="n">
-        <v>64.3</v>
+        <v>68.7</v>
       </c>
       <c r="H29" t="n">
-        <v>66.7</v>
+        <v>61.4</v>
       </c>
       <c r="I29" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>20.98</v>
+        <v>3.62</v>
       </c>
       <c r="K29" t="n">
-        <v>21.58</v>
+        <v>-71.79000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>30.1</v>
+        <v>71.89</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:40:54</t>
+          <t>05:42:39</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.24</v>
+        <v>1.99</v>
       </c>
       <c r="F30" t="n">
-        <v>5.73</v>
+        <v>10.23</v>
       </c>
       <c r="G30" t="n">
-        <v>69</v>
+        <v>63.2</v>
       </c>
       <c r="H30" t="n">
-        <v>70</v>
+        <v>84.8</v>
       </c>
       <c r="I30" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>28.68</v>
+        <v>27.05</v>
       </c>
       <c r="K30" t="n">
-        <v>-8.720000000000001</v>
+        <v>-23.97</v>
       </c>
       <c r="L30" t="n">
-        <v>29.97</v>
+        <v>36.14</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:42:41</t>
+          <t>05:43:51</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="F31" t="n">
-        <v>5.37</v>
+        <v>4.43</v>
       </c>
       <c r="G31" t="n">
-        <v>68.7</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>57.1</v>
+        <v>63</v>
       </c>
       <c r="I31" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>-23.5</v>
+        <v>-36.99</v>
       </c>
       <c r="K31" t="n">
-        <v>-18.34</v>
+        <v>-5.56</v>
       </c>
       <c r="L31" t="n">
-        <v>29.81</v>
+        <v>37.41</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:47:37</t>
+          <t>05:48:24</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.24</v>
+        <v>1.93</v>
       </c>
       <c r="F32" t="n">
-        <v>3.4</v>
+        <v>8.42</v>
       </c>
       <c r="G32" t="n">
-        <v>69.09999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>29.3</v>
+        <v>38.7</v>
       </c>
       <c r="I32" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J32" t="n">
-        <v>58.31</v>
+        <v>55.74</v>
       </c>
       <c r="K32" t="n">
-        <v>-3.87</v>
+        <v>-7.4</v>
       </c>
       <c r="L32" t="n">
-        <v>58.44</v>
+        <v>56.23</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:48:50</t>
+          <t>05:50:07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="F33" t="n">
-        <v>7.05</v>
+        <v>4.85</v>
       </c>
       <c r="G33" t="n">
-        <v>80.09999999999999</v>
+        <v>63.6</v>
       </c>
       <c r="H33" t="n">
-        <v>76.5</v>
+        <v>51.3</v>
       </c>
       <c r="I33" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>-47.06</v>
+        <v>-19.36</v>
       </c>
       <c r="K33" t="n">
-        <v>4.25</v>
+        <v>-61.15</v>
       </c>
       <c r="L33" t="n">
-        <v>47.25</v>
+        <v>64.15000000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:50:30</t>
+          <t>05:52:04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.13</v>
+        <v>1.57</v>
       </c>
       <c r="F34" t="n">
-        <v>6.22</v>
+        <v>8.42</v>
       </c>
       <c r="G34" t="n">
-        <v>76.8</v>
+        <v>66.2</v>
       </c>
       <c r="H34" t="n">
-        <v>26.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I34" t="n">
         <v>16</v>
       </c>
       <c r="J34" t="n">
-        <v>69.29000000000001</v>
+        <v>18.86</v>
       </c>
       <c r="K34" t="n">
-        <v>-10.02</v>
+        <v>42.79</v>
       </c>
       <c r="L34" t="n">
-        <v>70.01000000000001</v>
+        <v>46.76</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:56:26</t>
+          <t>05:57:23</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.77</v>
+        <v>2.11</v>
       </c>
       <c r="F35" t="n">
-        <v>5.13</v>
+        <v>4.69</v>
       </c>
       <c r="G35" t="n">
-        <v>66.09999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="H35" t="n">
-        <v>33.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-2.06</v>
+        <v>156.49</v>
       </c>
       <c r="K35" t="n">
-        <v>-72.79000000000001</v>
+        <v>113.42</v>
       </c>
       <c r="L35" t="n">
-        <v>72.81999999999999</v>
+        <v>193.27</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:58:44</t>
+          <t>05:59:03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="F36" t="n">
-        <v>6.43</v>
+        <v>6.52</v>
       </c>
       <c r="G36" t="n">
-        <v>72.3</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>84.8</v>
+        <v>56.5</v>
       </c>
       <c r="I36" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>-69.95</v>
+        <v>-63.91</v>
       </c>
       <c r="K36" t="n">
-        <v>20.17</v>
+        <v>51.92</v>
       </c>
       <c r="L36" t="n">
-        <v>72.8</v>
+        <v>82.34</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:00:00</t>
+          <t>06:01:20</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="F37" t="n">
         <v>10.23</v>
       </c>
       <c r="G37" t="n">
-        <v>71.8</v>
+        <v>87.3</v>
       </c>
       <c r="H37" t="n">
-        <v>30.3</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>67.44</v>
+        <v>39.98</v>
       </c>
       <c r="K37" t="n">
-        <v>9.529999999999999</v>
+        <v>59.58</v>
       </c>
       <c r="L37" t="n">
-        <v>68.12</v>
+        <v>71.75</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:05:02</t>
+          <t>06:06:15</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="F38" t="n">
-        <v>9.09</v>
+        <v>7.83</v>
       </c>
       <c r="G38" t="n">
-        <v>69.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>63.7</v>
+        <v>46.5</v>
       </c>
       <c r="I38" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J38" t="n">
-        <v>123.01</v>
+        <v>-3.51</v>
       </c>
       <c r="K38" t="n">
-        <v>-55.44</v>
+        <v>-146.97</v>
       </c>
       <c r="L38" t="n">
-        <v>134.92</v>
+        <v>147.02</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:06:59</t>
+          <t>06:07:47</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.18</v>
+        <v>2.44</v>
       </c>
       <c r="F39" t="n">
-        <v>8.1</v>
+        <v>10.23</v>
       </c>
       <c r="G39" t="n">
-        <v>67.7</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>42.7</v>
+        <v>76</v>
       </c>
       <c r="I39" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J39" t="n">
-        <v>20.42</v>
+        <v>53.3</v>
       </c>
       <c r="K39" t="n">
-        <v>125.06</v>
+        <v>-54.25</v>
       </c>
       <c r="L39" t="n">
-        <v>126.72</v>
+        <v>76.05</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:09:41</t>
+          <t>06:09:43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="F40" t="n">
-        <v>5.31</v>
+        <v>5.64</v>
       </c>
       <c r="G40" t="n">
-        <v>83.5</v>
+        <v>69.7</v>
       </c>
       <c r="H40" t="n">
-        <v>19.2</v>
+        <v>84.8</v>
       </c>
       <c r="I40" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>26.15</v>
+        <v>45.05</v>
       </c>
       <c r="K40" t="n">
-        <v>-127.05</v>
+        <v>-122.92</v>
       </c>
       <c r="L40" t="n">
-        <v>129.71</v>
+        <v>130.91</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:12:49</t>
+          <t>06:12:52</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.98</v>
+        <v>2.49</v>
       </c>
       <c r="F41" t="n">
-        <v>9.26</v>
+        <v>9.74</v>
       </c>
       <c r="G41" t="n">
-        <v>73.59999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="H41" t="n">
-        <v>62.4</v>
+        <v>55.5</v>
       </c>
       <c r="I41" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-73.31999999999999</v>
+        <v>-141.28</v>
       </c>
       <c r="K41" t="n">
-        <v>160.46</v>
+        <v>92.48999999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>176.42</v>
+        <v>168.86</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:14:58</t>
+          <t>06:14:33</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.98</v>
+        <v>2.41</v>
       </c>
       <c r="F42" t="n">
-        <v>5.46</v>
+        <v>9.6</v>
       </c>
       <c r="G42" t="n">
-        <v>68.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>12.8</v>
+        <v>35.8</v>
       </c>
       <c r="I42" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-117.07</v>
+        <v>-124.27</v>
       </c>
       <c r="K42" t="n">
-        <v>-165.11</v>
+        <v>-172.25</v>
       </c>
       <c r="L42" t="n">
-        <v>202.4</v>
+        <v>212.4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:16:47</t>
+          <t>06:16:55</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.38</v>
+        <v>2.03</v>
       </c>
       <c r="F43" t="n">
-        <v>8.73</v>
+        <v>6.1</v>
       </c>
       <c r="G43" t="n">
-        <v>75.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="H43" t="n">
-        <v>35.7</v>
+        <v>62.9</v>
       </c>
       <c r="I43" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J43" t="n">
-        <v>45.58</v>
+        <v>-125.92</v>
       </c>
       <c r="K43" t="n">
-        <v>164.25</v>
+        <v>-133.82</v>
       </c>
       <c r="L43" t="n">
-        <v>170.45</v>
+        <v>183.75</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:26:10</t>
+          <t>06:26:28</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.76</v>
+        <v>2.21</v>
       </c>
       <c r="F44" t="n">
-        <v>7.19</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="G44" t="n">
-        <v>82.59999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="H44" t="n">
-        <v>60.6</v>
+        <v>42.6</v>
       </c>
       <c r="I44" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>-7.54</v>
+        <v>15.96</v>
       </c>
       <c r="K44" t="n">
-        <v>28.72</v>
+        <v>-36.26</v>
       </c>
       <c r="L44" t="n">
-        <v>29.69</v>
+        <v>39.61</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:27:55</t>
+          <t>06:28:22</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.21</v>
+        <v>1.92</v>
       </c>
       <c r="F45" t="n">
-        <v>7.85</v>
+        <v>5.41</v>
       </c>
       <c r="G45" t="n">
-        <v>80.40000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="H45" t="n">
-        <v>89.90000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="I45" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>23.24</v>
+        <v>-30.67</v>
       </c>
       <c r="K45" t="n">
-        <v>33.61</v>
+        <v>-9.27</v>
       </c>
       <c r="L45" t="n">
-        <v>40.86</v>
+        <v>32.04</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:29:09</t>
+          <t>06:30:33</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="F46" t="n">
-        <v>3.3</v>
+        <v>7.98</v>
       </c>
       <c r="G46" t="n">
-        <v>78</v>
+        <v>72.8</v>
       </c>
       <c r="H46" t="n">
-        <v>91.7</v>
+        <v>20.9</v>
       </c>
       <c r="I46" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>-21.9</v>
+        <v>-2.06</v>
       </c>
       <c r="K46" t="n">
-        <v>-31.33</v>
+        <v>38.59</v>
       </c>
       <c r="L46" t="n">
-        <v>38.22</v>
+        <v>38.65</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:33:28</t>
+          <t>06:36:28</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.64</v>
+        <v>2.87</v>
       </c>
       <c r="F47" t="n">
-        <v>9.83</v>
+        <v>7.91</v>
       </c>
       <c r="G47" t="n">
-        <v>80.90000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>50</v>
+        <v>38.7</v>
       </c>
       <c r="I47" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J47" t="n">
-        <v>33.28</v>
+        <v>-54.83</v>
       </c>
       <c r="K47" t="n">
-        <v>55.68</v>
+        <v>-5.22</v>
       </c>
       <c r="L47" t="n">
-        <v>64.86</v>
+        <v>55.08</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:34:57</t>
+          <t>06:38:30</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.96</v>
+        <v>2.24</v>
       </c>
       <c r="F48" t="n">
-        <v>6.87</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>77.5</v>
+        <v>70.2</v>
       </c>
       <c r="H48" t="n">
-        <v>47.5</v>
+        <v>43.9</v>
       </c>
       <c r="I48" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-3.87</v>
+        <v>44.27</v>
       </c>
       <c r="K48" t="n">
-        <v>-64.72</v>
+        <v>-28.58</v>
       </c>
       <c r="L48" t="n">
-        <v>64.84</v>
+        <v>52.69</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:36:39</t>
+          <t>06:40:21</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="F49" t="n">
-        <v>8.6</v>
+        <v>10.23</v>
       </c>
       <c r="G49" t="n">
-        <v>69.90000000000001</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>81.5</v>
+        <v>83.5</v>
       </c>
       <c r="I49" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J49" t="n">
-        <v>67.44</v>
+        <v>-9.74</v>
       </c>
       <c r="K49" t="n">
-        <v>-89.14</v>
+        <v>77.03</v>
       </c>
       <c r="L49" t="n">
-        <v>111.78</v>
+        <v>77.64</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:40:03</t>
+          <t>06:44:54</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.52</v>
+        <v>2.41</v>
       </c>
       <c r="F50" t="n">
         <v>10.23</v>
       </c>
       <c r="G50" t="n">
-        <v>77.90000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="H50" t="n">
-        <v>70.09999999999999</v>
+        <v>39.5</v>
       </c>
       <c r="I50" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>98.97</v>
+        <v>50.37</v>
       </c>
       <c r="K50" t="n">
-        <v>-133.07</v>
+        <v>-40.35</v>
       </c>
       <c r="L50" t="n">
-        <v>165.84</v>
+        <v>64.54000000000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:42:46</t>
+          <t>06:46:06</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="F51" t="n">
-        <v>10.23</v>
+        <v>8</v>
       </c>
       <c r="G51" t="n">
-        <v>61.9</v>
+        <v>71</v>
       </c>
       <c r="H51" t="n">
-        <v>44.8</v>
+        <v>83</v>
       </c>
       <c r="I51" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>31.14</v>
+        <v>11.97</v>
       </c>
       <c r="K51" t="n">
-        <v>78.18000000000001</v>
+        <v>70.03</v>
       </c>
       <c r="L51" t="n">
-        <v>84.15000000000001</v>
+        <v>71.05</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:43:58</t>
+          <t>06:47:30</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.44</v>
+        <v>2.21</v>
       </c>
       <c r="F52" t="n">
-        <v>8.93</v>
+        <v>10.23</v>
       </c>
       <c r="G52" t="n">
-        <v>77.5</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="H52" t="n">
-        <v>41.5</v>
+        <v>35</v>
       </c>
       <c r="I52" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>49.48</v>
+        <v>-22.06</v>
       </c>
       <c r="K52" t="n">
-        <v>84.54000000000001</v>
+        <v>97.63</v>
       </c>
       <c r="L52" t="n">
-        <v>97.95999999999999</v>
+        <v>100.09</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:49:23</t>
+          <t>06:53:50</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.27</v>
+        <v>1.85</v>
       </c>
       <c r="F53" t="n">
-        <v>10.23</v>
+        <v>6.1</v>
       </c>
       <c r="G53" t="n">
-        <v>74.8</v>
+        <v>86.2</v>
       </c>
       <c r="H53" t="n">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="I53" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>-83.3</v>
+        <v>-85.34999999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>105.9</v>
+        <v>35.55</v>
       </c>
       <c r="L53" t="n">
-        <v>134.74</v>
+        <v>92.45999999999999</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:51:38</t>
+          <t>06:56:38</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="F54" t="n">
-        <v>6.16</v>
+        <v>10.23</v>
       </c>
       <c r="G54" t="n">
-        <v>77</v>
+        <v>62.2</v>
       </c>
       <c r="H54" t="n">
-        <v>64.2</v>
+        <v>59.8</v>
       </c>
       <c r="I54" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>-16.46</v>
+        <v>-104.92</v>
       </c>
       <c r="K54" t="n">
-        <v>-113.95</v>
+        <v>40.44</v>
       </c>
       <c r="L54" t="n">
-        <v>115.13</v>
+        <v>112.45</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:53:24</t>
+          <t>06:58:12</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.26</v>
+        <v>2.53</v>
       </c>
       <c r="F55" t="n">
-        <v>8.699999999999999</v>
+        <v>10.23</v>
       </c>
       <c r="G55" t="n">
-        <v>61.5</v>
+        <v>79.2</v>
       </c>
       <c r="H55" t="n">
-        <v>58</v>
+        <v>48.6</v>
       </c>
       <c r="I55" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>92.84</v>
+        <v>94.62</v>
       </c>
       <c r="K55" t="n">
-        <v>-117.63</v>
+        <v>-149.48</v>
       </c>
       <c r="L55" t="n">
-        <v>149.86</v>
+        <v>176.91</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:57:27</t>
+          <t>07:03:37</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="F56" t="n">
-        <v>9.59</v>
+        <v>6.32</v>
       </c>
       <c r="G56" t="n">
-        <v>63.6</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="H56" t="n">
-        <v>57.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>10.19</v>
+        <v>-102.63</v>
       </c>
       <c r="K56" t="n">
-        <v>-145.19</v>
+        <v>-127.82</v>
       </c>
       <c r="L56" t="n">
-        <v>145.55</v>
+        <v>163.92</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:58:17</t>
+          <t>07:05:48</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.35</v>
+        <v>2.06</v>
       </c>
       <c r="F57" t="n">
-        <v>10.23</v>
+        <v>9.18</v>
       </c>
       <c r="G57" t="n">
-        <v>75</v>
+        <v>61.9</v>
       </c>
       <c r="H57" t="n">
-        <v>63.6</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>120.66</v>
+        <v>-172.65</v>
       </c>
       <c r="K57" t="n">
-        <v>119.02</v>
+        <v>-43.03</v>
       </c>
       <c r="L57" t="n">
-        <v>169.48</v>
+        <v>177.93</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:59:43</t>
+          <t>07:07:53</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1.93</v>
+        <v>2.31</v>
       </c>
       <c r="F58" t="n">
-        <v>7.72</v>
+        <v>10.1</v>
       </c>
       <c r="G58" t="n">
-        <v>62.7</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>59.4</v>
+        <v>65.7</v>
       </c>
       <c r="I58" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>132.26</v>
+        <v>5.83</v>
       </c>
       <c r="K58" t="n">
-        <v>-55.96</v>
+        <v>-71.03</v>
       </c>
       <c r="L58" t="n">
-        <v>143.62</v>
+        <v>71.27</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:11:30</t>
+          <t>07:19:35</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.31</v>
+        <v>2.46</v>
       </c>
       <c r="F59" t="n">
         <v>10.23</v>
       </c>
       <c r="G59" t="n">
-        <v>87.59999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="H59" t="n">
-        <v>50.8</v>
+        <v>62.6</v>
       </c>
       <c r="I59" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>0.98</v>
+        <v>-42.85</v>
       </c>
       <c r="K59" t="n">
-        <v>6.21</v>
+        <v>-1.86</v>
       </c>
       <c r="L59" t="n">
-        <v>6.28</v>
+        <v>42.89</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:12:51</t>
+          <t>07:20:33</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="F60" t="n">
-        <v>7.1</v>
+        <v>7.37</v>
       </c>
       <c r="G60" t="n">
-        <v>55.2</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="H60" t="n">
-        <v>50.9</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-17.3</v>
+        <v>-1.13</v>
       </c>
       <c r="K60" t="n">
-        <v>29.7</v>
+        <v>36.25</v>
       </c>
       <c r="L60" t="n">
-        <v>34.37</v>
+        <v>36.27</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:14:05</t>
+          <t>07:23:17</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>1.52</v>
+        <v>2.38</v>
       </c>
       <c r="F61" t="n">
-        <v>4.37</v>
+        <v>6.42</v>
       </c>
       <c r="G61" t="n">
-        <v>65.2</v>
+        <v>70.3</v>
       </c>
       <c r="H61" t="n">
-        <v>76.3</v>
+        <v>35.9</v>
       </c>
       <c r="I61" t="n">
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>3.48</v>
+        <v>-34.14</v>
       </c>
       <c r="K61" t="n">
-        <v>35.36</v>
+        <v>12.21</v>
       </c>
       <c r="L61" t="n">
-        <v>35.53</v>
+        <v>36.26</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:18:26</t>
+          <t>07:28:58</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.44</v>
+        <v>2.21</v>
       </c>
       <c r="F62" t="n">
-        <v>8.09</v>
+        <v>5.72</v>
       </c>
       <c r="G62" t="n">
-        <v>77.8</v>
+        <v>68</v>
       </c>
       <c r="H62" t="n">
-        <v>62.7</v>
+        <v>53.9</v>
       </c>
       <c r="I62" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-20.23</v>
+        <v>70.31</v>
       </c>
       <c r="K62" t="n">
-        <v>61.22</v>
+        <v>21.3</v>
       </c>
       <c r="L62" t="n">
-        <v>64.48</v>
+        <v>73.47</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:20:09</t>
+          <t>07:30:25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="F63" t="n">
-        <v>4.34</v>
+        <v>3.52</v>
       </c>
       <c r="G63" t="n">
-        <v>79.5</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="H63" t="n">
-        <v>78.5</v>
+        <v>60.3</v>
       </c>
       <c r="I63" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J63" t="n">
-        <v>49.67</v>
+        <v>25.58</v>
       </c>
       <c r="K63" t="n">
-        <v>-15.94</v>
+        <v>39.46</v>
       </c>
       <c r="L63" t="n">
-        <v>52.17</v>
+        <v>47.02</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:21:59</t>
+          <t>07:31:31</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="F64" t="n">
-        <v>10.23</v>
+        <v>9.33</v>
       </c>
       <c r="G64" t="n">
-        <v>77.7</v>
+        <v>69.5</v>
       </c>
       <c r="H64" t="n">
-        <v>65.40000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>69.98</v>
+        <v>57.18</v>
       </c>
       <c r="K64" t="n">
-        <v>19.2</v>
+        <v>-26.84</v>
       </c>
       <c r="L64" t="n">
-        <v>72.56</v>
+        <v>63.17</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:26:29</t>
+          <t>07:36:20</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="F65" t="n">
-        <v>6.43</v>
+        <v>6.87</v>
       </c>
       <c r="G65" t="n">
-        <v>64.8</v>
+        <v>70.8</v>
       </c>
       <c r="H65" t="n">
-        <v>50.9</v>
+        <v>92.7</v>
       </c>
       <c r="I65" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>-73.48999999999999</v>
+        <v>-65.69</v>
       </c>
       <c r="K65" t="n">
-        <v>49.77</v>
+        <v>7.5</v>
       </c>
       <c r="L65" t="n">
-        <v>88.75</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:28:39</t>
+          <t>07:38:12</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="F66" t="n">
-        <v>7.6</v>
+        <v>5.61</v>
       </c>
       <c r="G66" t="n">
-        <v>49.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H66" t="n">
-        <v>78.40000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="I66" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>53.26</v>
+        <v>-85.17</v>
       </c>
       <c r="K66" t="n">
-        <v>55.19</v>
+        <v>18.26</v>
       </c>
       <c r="L66" t="n">
-        <v>76.7</v>
+        <v>87.11</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:30:42</t>
+          <t>07:39:53</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.11</v>
+        <v>3.95</v>
       </c>
       <c r="F67" t="n">
         <v>10.23</v>
       </c>
       <c r="G67" t="n">
-        <v>69.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="H67" t="n">
-        <v>59</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="I67" t="n">
         <v>21</v>
       </c>
       <c r="J67" t="n">
-        <v>50.6</v>
+        <v>106.63</v>
       </c>
       <c r="K67" t="n">
-        <v>66.91</v>
+        <v>-129.43</v>
       </c>
       <c r="L67" t="n">
-        <v>83.89</v>
+        <v>167.7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:34:45</t>
+          <t>07:45:17</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="F68" t="n">
-        <v>9.039999999999999</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="G68" t="n">
-        <v>66.59999999999999</v>
+        <v>60.7</v>
       </c>
       <c r="H68" t="n">
-        <v>50.6</v>
+        <v>40</v>
       </c>
       <c r="I68" t="n">
         <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>93.06</v>
+        <v>-38.06</v>
       </c>
       <c r="K68" t="n">
-        <v>276.32</v>
+        <v>132.14</v>
       </c>
       <c r="L68" t="n">
-        <v>291.57</v>
+        <v>137.51</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:35:55</t>
+          <t>07:47:21</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="F69" t="n">
-        <v>8.140000000000001</v>
+        <v>10.18</v>
       </c>
       <c r="G69" t="n">
-        <v>84.09999999999999</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H69" t="n">
-        <v>84.8</v>
+        <v>40.8</v>
       </c>
       <c r="I69" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J69" t="n">
-        <v>135.14</v>
+        <v>153.39</v>
       </c>
       <c r="K69" t="n">
-        <v>-105.3</v>
+        <v>-44.16</v>
       </c>
       <c r="L69" t="n">
-        <v>171.32</v>
+        <v>159.62</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:36:54</t>
+          <t>07:49:55</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.72</v>
+        <v>1.79</v>
       </c>
       <c r="F70" t="n">
-        <v>10.23</v>
+        <v>5.79</v>
       </c>
       <c r="G70" t="n">
-        <v>81.40000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="H70" t="n">
-        <v>80.5</v>
+        <v>70.8</v>
       </c>
       <c r="I70" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>30.27</v>
+        <v>26.49</v>
       </c>
       <c r="K70" t="n">
-        <v>-112.84</v>
+        <v>159.19</v>
       </c>
       <c r="L70" t="n">
-        <v>116.83</v>
+        <v>161.38</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:41:54</t>
+          <t>07:54:31</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="F71" t="n">
-        <v>6.87</v>
+        <v>10.23</v>
       </c>
       <c r="G71" t="n">
-        <v>82.5</v>
+        <v>76.5</v>
       </c>
       <c r="H71" t="n">
-        <v>69.7</v>
+        <v>54.6</v>
       </c>
       <c r="I71" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>71.88</v>
+        <v>-170.54</v>
       </c>
       <c r="K71" t="n">
-        <v>-147.3</v>
+        <v>-1.12</v>
       </c>
       <c r="L71" t="n">
-        <v>163.9</v>
+        <v>170.55</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:43:26</t>
+          <t>07:55:35</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.64</v>
+        <v>2.16</v>
       </c>
       <c r="F72" t="n">
-        <v>5.86</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="G72" t="n">
-        <v>71</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="H72" t="n">
-        <v>57.1</v>
+        <v>79</v>
       </c>
       <c r="I72" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-86.73</v>
+        <v>78.77</v>
       </c>
       <c r="K72" t="n">
-        <v>183.84</v>
+        <v>151.41</v>
       </c>
       <c r="L72" t="n">
-        <v>203.27</v>
+        <v>170.67</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:45:43</t>
+          <t>07:56:50</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.27</v>
+        <v>2.12</v>
       </c>
       <c r="F73" t="n">
-        <v>10.23</v>
+        <v>5.51</v>
       </c>
       <c r="G73" t="n">
-        <v>69.8</v>
+        <v>66.8</v>
       </c>
       <c r="H73" t="n">
-        <v>32.6</v>
+        <v>14.8</v>
       </c>
       <c r="I73" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>94.64</v>
+        <v>-159.72</v>
       </c>
       <c r="K73" t="n">
-        <v>138.73</v>
+        <v>-111.09</v>
       </c>
       <c r="L73" t="n">
-        <v>167.94</v>
+        <v>194.55</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:57:24</t>
+          <t>08:09:00</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="F74" t="n">
-        <v>7.08</v>
+        <v>8.58</v>
       </c>
       <c r="G74" t="n">
-        <v>70.90000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="H74" t="n">
-        <v>11.6</v>
+        <v>58.2</v>
       </c>
       <c r="I74" t="n">
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-44.73</v>
+        <v>-24.72</v>
       </c>
       <c r="K74" t="n">
-        <v>7.62</v>
+        <v>24.37</v>
       </c>
       <c r="L74" t="n">
-        <v>45.37</v>
+        <v>34.71</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:57:47</t>
+          <t>08:10:37</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.15</v>
+        <v>2.65</v>
       </c>
       <c r="F75" t="n">
         <v>10.23</v>
       </c>
       <c r="G75" t="n">
-        <v>63.2</v>
+        <v>72.3</v>
       </c>
       <c r="H75" t="n">
-        <v>88.59999999999999</v>
+        <v>99.2</v>
       </c>
       <c r="I75" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-20.21</v>
+        <v>48.2</v>
       </c>
       <c r="K75" t="n">
-        <v>33.03</v>
+        <v>-4.16</v>
       </c>
       <c r="L75" t="n">
-        <v>38.72</v>
+        <v>48.38</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:59:26</t>
+          <t>08:12:32</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="F76" t="n">
         <v>10.23</v>
       </c>
       <c r="G76" t="n">
-        <v>64.59999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="H76" t="n">
-        <v>99.40000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="I76" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>31.84</v>
+        <v>40.44</v>
       </c>
       <c r="K76" t="n">
-        <v>13.15</v>
+        <v>-11.6</v>
       </c>
       <c r="L76" t="n">
-        <v>34.45</v>
+        <v>42.07</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:04:32</t>
+          <t>08:15:55</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="F77" t="n">
-        <v>10.23</v>
+        <v>7.18</v>
       </c>
       <c r="G77" t="n">
-        <v>88.2</v>
+        <v>84.8</v>
       </c>
       <c r="H77" t="n">
-        <v>61</v>
+        <v>68.5</v>
       </c>
       <c r="I77" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J77" t="n">
-        <v>-3.49</v>
+        <v>61.24</v>
       </c>
       <c r="K77" t="n">
-        <v>72.43000000000001</v>
+        <v>-76.87</v>
       </c>
       <c r="L77" t="n">
-        <v>72.52</v>
+        <v>98.28</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:05:08</t>
+          <t>08:17:49</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.02</v>
+        <v>2.19</v>
       </c>
       <c r="F78" t="n">
-        <v>10.23</v>
+        <v>3.94</v>
       </c>
       <c r="G78" t="n">
-        <v>63.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H78" t="n">
-        <v>72.09999999999999</v>
+        <v>34.1</v>
       </c>
       <c r="I78" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>52.06</v>
+        <v>-71.61</v>
       </c>
       <c r="K78" t="n">
-        <v>27.54</v>
+        <v>29.97</v>
       </c>
       <c r="L78" t="n">
-        <v>58.89</v>
+        <v>77.62</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:07:33</t>
+          <t>08:19:08</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="F79" t="n">
-        <v>7.73</v>
+        <v>4.95</v>
       </c>
       <c r="G79" t="n">
-        <v>65.3</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H79" t="n">
-        <v>57.3</v>
+        <v>90.2</v>
       </c>
       <c r="I79" t="n">
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>-1.65</v>
+        <v>-38.93</v>
       </c>
       <c r="K79" t="n">
-        <v>-45.48</v>
+        <v>31.78</v>
       </c>
       <c r="L79" t="n">
-        <v>45.51</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:12:11</t>
+          <t>08:23:52</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1.72</v>
+        <v>2.44</v>
       </c>
       <c r="F80" t="n">
         <v>10.23</v>
       </c>
       <c r="G80" t="n">
-        <v>67.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="H80" t="n">
-        <v>62.2</v>
+        <v>51.6</v>
       </c>
       <c r="I80" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>-27.08</v>
+        <v>-46.96</v>
       </c>
       <c r="K80" t="n">
-        <v>94.53</v>
+        <v>-51.42</v>
       </c>
       <c r="L80" t="n">
-        <v>98.33</v>
+        <v>69.64</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:14:33</t>
+          <t>08:25:50</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="F81" t="n">
-        <v>10.23</v>
+        <v>8.25</v>
       </c>
       <c r="G81" t="n">
-        <v>71.7</v>
+        <v>58.8</v>
       </c>
       <c r="H81" t="n">
-        <v>44.9</v>
+        <v>77.5</v>
       </c>
       <c r="I81" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>84.91</v>
+        <v>-85.56999999999999</v>
       </c>
       <c r="K81" t="n">
-        <v>-14.05</v>
+        <v>-74.58</v>
       </c>
       <c r="L81" t="n">
-        <v>86.06</v>
+        <v>113.51</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:15:45</t>
+          <t>08:27:39</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.32</v>
+        <v>1.94</v>
       </c>
       <c r="F82" t="n">
-        <v>10.09</v>
+        <v>6.74</v>
       </c>
       <c r="G82" t="n">
-        <v>70.8</v>
+        <v>81.8</v>
       </c>
       <c r="H82" t="n">
-        <v>63.2</v>
+        <v>46.4</v>
       </c>
       <c r="I82" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>101.92</v>
+        <v>21.52</v>
       </c>
       <c r="K82" t="n">
-        <v>13.44</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="L82" t="n">
-        <v>102.8</v>
+        <v>76.14</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:19:56</t>
+          <t>08:32:57</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.52</v>
+        <v>2.29</v>
       </c>
       <c r="F83" t="n">
-        <v>8.08</v>
+        <v>10.04</v>
       </c>
       <c r="G83" t="n">
-        <v>70.90000000000001</v>
+        <v>60.8</v>
       </c>
       <c r="H83" t="n">
-        <v>61.4</v>
+        <v>54.4</v>
       </c>
       <c r="I83" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>109.44</v>
+        <v>160.8</v>
       </c>
       <c r="K83" t="n">
-        <v>122.56</v>
+        <v>-41.02</v>
       </c>
       <c r="L83" t="n">
-        <v>164.31</v>
+        <v>165.95</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:20:59</t>
+          <t>08:34:11</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.03</v>
+        <v>2.46</v>
       </c>
       <c r="F84" t="n">
-        <v>8.539999999999999</v>
+        <v>10.23</v>
       </c>
       <c r="G84" t="n">
-        <v>66.59999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="H84" t="n">
-        <v>60.3</v>
+        <v>21.9</v>
       </c>
       <c r="I84" t="n">
         <v>17</v>
       </c>
       <c r="J84" t="n">
-        <v>-57.1</v>
+        <v>10.59</v>
       </c>
       <c r="K84" t="n">
-        <v>65.81999999999999</v>
+        <v>-119.61</v>
       </c>
       <c r="L84" t="n">
-        <v>87.14</v>
+        <v>120.08</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:22:28</t>
+          <t>08:35:25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.92</v>
+        <v>2.41</v>
       </c>
       <c r="F85" t="n">
         <v>10.23</v>
       </c>
       <c r="G85" t="n">
-        <v>88.2</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="H85" t="n">
-        <v>42.9</v>
+        <v>52</v>
       </c>
       <c r="I85" t="n">
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>205.76</v>
+        <v>38</v>
       </c>
       <c r="K85" t="n">
-        <v>15.4</v>
+        <v>-159.74</v>
       </c>
       <c r="L85" t="n">
-        <v>206.34</v>
+        <v>164.2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:25:59</t>
+          <t>08:40:55</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="F86" t="n">
         <v>10.23</v>
       </c>
       <c r="G86" t="n">
-        <v>72.2</v>
+        <v>80</v>
       </c>
       <c r="H86" t="n">
-        <v>67.40000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="I86" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-12.99</v>
+        <v>-169.23</v>
       </c>
       <c r="K86" t="n">
-        <v>149.49</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="L86" t="n">
-        <v>150.05</v>
+        <v>195.11</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:27:34</t>
+          <t>08:42:53</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.26</v>
+        <v>2.33</v>
       </c>
       <c r="F87" t="n">
-        <v>8.199999999999999</v>
+        <v>10.23</v>
       </c>
       <c r="G87" t="n">
-        <v>76.59999999999999</v>
+        <v>60.1</v>
       </c>
       <c r="H87" t="n">
-        <v>49.2</v>
+        <v>39.5</v>
       </c>
       <c r="I87" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-149.63</v>
+        <v>-216.03</v>
       </c>
       <c r="K87" t="n">
-        <v>-123.28</v>
+        <v>-45.76</v>
       </c>
       <c r="L87" t="n">
-        <v>193.87</v>
+        <v>220.82</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:28:55</t>
+          <t>08:44:53</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="F88" t="n">
-        <v>6.45</v>
+        <v>7.77</v>
       </c>
       <c r="G88" t="n">
-        <v>75.3</v>
+        <v>69.8</v>
       </c>
       <c r="H88" t="n">
-        <v>42.2</v>
+        <v>57.6</v>
       </c>
       <c r="I88" t="n">
         <v>17</v>
       </c>
       <c r="J88" t="n">
-        <v>89.81999999999999</v>
+        <v>-3.71</v>
       </c>
       <c r="K88" t="n">
-        <v>-43.26</v>
+        <v>154.35</v>
       </c>
       <c r="L88" t="n">
-        <v>99.7</v>
+        <v>154.39</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-17.xlsx
+++ b/output/2025-07-17.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>-74.06999999999999</v>
+        <v>-73.79000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.54</v>
+        <v>-2.53</v>
       </c>
       <c r="L14" t="n">
-        <v>74.12</v>
+        <v>73.83</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-15.4</v>
+        <v>-17.08</v>
       </c>
       <c r="K15" t="n">
-        <v>-42.37</v>
+        <v>-46.99</v>
       </c>
       <c r="L15" t="n">
-        <v>45.08</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>28.43</v>
+        <v>29.79</v>
       </c>
       <c r="K16" t="n">
-        <v>54.25</v>
+        <v>56.84</v>
       </c>
       <c r="L16" t="n">
-        <v>61.25</v>
+        <v>64.17</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>-10.21</v>
+        <v>-11.02</v>
       </c>
       <c r="K17" t="n">
-        <v>-88.56</v>
+        <v>-95.58</v>
       </c>
       <c r="L17" t="n">
-        <v>89.15000000000001</v>
+        <v>96.22</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>22.99</v>
+        <v>25.85</v>
       </c>
       <c r="K18" t="n">
-        <v>69.7</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>73.39</v>
+        <v>82.55</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>38.7</v>
+        <v>44.88</v>
       </c>
       <c r="K19" t="n">
-        <v>48.54</v>
+        <v>56.29</v>
       </c>
       <c r="L19" t="n">
-        <v>62.08</v>
+        <v>71.98999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>63.72</v>
+        <v>72.34</v>
       </c>
       <c r="K20" t="n">
-        <v>-78.04000000000001</v>
+        <v>-88.59999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>100.76</v>
+        <v>114.38</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>-4.68</v>
+        <v>-6.04</v>
       </c>
       <c r="K21" t="n">
-        <v>-77.64</v>
+        <v>-100.12</v>
       </c>
       <c r="L21" t="n">
-        <v>77.78</v>
+        <v>100.31</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-79.26000000000001</v>
+        <v>-94.37</v>
       </c>
       <c r="K22" t="n">
-        <v>22.76</v>
+        <v>27.09</v>
       </c>
       <c r="L22" t="n">
-        <v>82.47</v>
+        <v>98.18000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-141.46</v>
+        <v>-166.53</v>
       </c>
       <c r="K23" t="n">
-        <v>8.91</v>
+        <v>10.48</v>
       </c>
       <c r="L23" t="n">
-        <v>141.74</v>
+        <v>166.86</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>18</v>
       </c>
       <c r="J24" t="n">
-        <v>136.83</v>
+        <v>165.33</v>
       </c>
       <c r="K24" t="n">
-        <v>10.09</v>
+        <v>12.19</v>
       </c>
       <c r="L24" t="n">
-        <v>137.2</v>
+        <v>165.77</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>63.29</v>
+        <v>75.87</v>
       </c>
       <c r="K25" t="n">
-        <v>122.07</v>
+        <v>146.32</v>
       </c>
       <c r="L25" t="n">
-        <v>137.5</v>
+        <v>164.82</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-21.92</v>
+        <v>-26.29</v>
       </c>
       <c r="K26" t="n">
-        <v>213.64</v>
+        <v>256.2</v>
       </c>
       <c r="L26" t="n">
-        <v>214.77</v>
+        <v>257.54</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>-253.9</v>
+        <v>-298.92</v>
       </c>
       <c r="K27" t="n">
-        <v>-23.16</v>
+        <v>-27.26</v>
       </c>
       <c r="L27" t="n">
-        <v>254.95</v>
+        <v>300.16</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>-88.54000000000001</v>
+        <v>-117.35</v>
       </c>
       <c r="K28" t="n">
-        <v>136.81</v>
+        <v>181.32</v>
       </c>
       <c r="L28" t="n">
-        <v>162.96</v>
+        <v>215.98</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-33.04</v>
+        <v>-38.83</v>
       </c>
       <c r="K29" t="n">
-        <v>-25.88</v>
+        <v>-30.41</v>
       </c>
       <c r="L29" t="n">
-        <v>41.97</v>
+        <v>49.32</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-49.05</v>
+        <v>-53.7</v>
       </c>
       <c r="K30" t="n">
-        <v>16.68</v>
+        <v>18.25</v>
       </c>
       <c r="L30" t="n">
-        <v>51.81</v>
+        <v>56.72</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>-20.73</v>
+        <v>-24.03</v>
       </c>
       <c r="K31" t="n">
-        <v>33.15</v>
+        <v>38.43</v>
       </c>
       <c r="L31" t="n">
-        <v>39.09</v>
+        <v>45.33</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>57.6</v>
+        <v>61.87</v>
       </c>
       <c r="K32" t="n">
-        <v>-68.42</v>
+        <v>-73.48999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>89.44</v>
+        <v>96.06</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>19.55</v>
+        <v>20.6</v>
       </c>
       <c r="K33" t="n">
-        <v>88.54000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="L33" t="n">
-        <v>90.67</v>
+        <v>95.54000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-92.3</v>
+        <v>-96.33</v>
       </c>
       <c r="K34" t="n">
-        <v>35.15</v>
+        <v>36.69</v>
       </c>
       <c r="L34" t="n">
-        <v>98.77</v>
+        <v>103.08</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.87</v>
+        <v>-0.99</v>
       </c>
       <c r="K35" t="n">
-        <v>118.41</v>
+        <v>134.25</v>
       </c>
       <c r="L35" t="n">
-        <v>118.41</v>
+        <v>134.26</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>93.45</v>
+        <v>111.41</v>
       </c>
       <c r="K36" t="n">
-        <v>19.68</v>
+        <v>23.46</v>
       </c>
       <c r="L36" t="n">
-        <v>95.5</v>
+        <v>113.85</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>-106.21</v>
+        <v>-122.49</v>
       </c>
       <c r="K37" t="n">
-        <v>-24.46</v>
+        <v>-28.21</v>
       </c>
       <c r="L37" t="n">
-        <v>108.99</v>
+        <v>125.7</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>41.3</v>
+        <v>50.11</v>
       </c>
       <c r="K38" t="n">
-        <v>126.92</v>
+        <v>154</v>
       </c>
       <c r="L38" t="n">
-        <v>133.47</v>
+        <v>161.94</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>162.27</v>
+        <v>181.23</v>
       </c>
       <c r="K39" t="n">
-        <v>-74.47</v>
+        <v>-83.17</v>
       </c>
       <c r="L39" t="n">
-        <v>178.54</v>
+        <v>199.41</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>-75.36</v>
+        <v>-88.95999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>163.63</v>
+        <v>193.14</v>
       </c>
       <c r="L40" t="n">
-        <v>180.15</v>
+        <v>212.64</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-133.22</v>
+        <v>-157.47</v>
       </c>
       <c r="K41" t="n">
-        <v>211.21</v>
+        <v>249.65</v>
       </c>
       <c r="L41" t="n">
-        <v>249.72</v>
+        <v>295.16</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-191.65</v>
+        <v>-245.02</v>
       </c>
       <c r="K42" t="n">
-        <v>66.95</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>203.01</v>
+        <v>259.54</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>9.18</v>
+        <v>11.52</v>
       </c>
       <c r="K43" t="n">
-        <v>199.37</v>
+        <v>250.04</v>
       </c>
       <c r="L43" t="n">
-        <v>199.58</v>
+        <v>250.3</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-57.1</v>
+        <v>-63.5</v>
       </c>
       <c r="K44" t="n">
-        <v>7.84</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="L44" t="n">
-        <v>57.64</v>
+        <v>64.09</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-35.58</v>
+        <v>-40.42</v>
       </c>
       <c r="K45" t="n">
-        <v>-28.83</v>
+        <v>-32.76</v>
       </c>
       <c r="L45" t="n">
-        <v>45.8</v>
+        <v>52.03</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>46.89</v>
+        <v>49.52</v>
       </c>
       <c r="K46" t="n">
-        <v>-24.67</v>
+        <v>-26.05</v>
       </c>
       <c r="L46" t="n">
-        <v>52.98</v>
+        <v>55.96</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-34.17</v>
+        <v>-41.07</v>
       </c>
       <c r="K47" t="n">
-        <v>48.08</v>
+        <v>57.81</v>
       </c>
       <c r="L47" t="n">
-        <v>58.99</v>
+        <v>70.91</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>-42.23</v>
+        <v>-50.44</v>
       </c>
       <c r="K48" t="n">
-        <v>24.51</v>
+        <v>29.28</v>
       </c>
       <c r="L48" t="n">
-        <v>48.83</v>
+        <v>58.32</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>66.3</v>
+        <v>69.39</v>
       </c>
       <c r="K49" t="n">
-        <v>-27.41</v>
+        <v>-28.69</v>
       </c>
       <c r="L49" t="n">
-        <v>71.75</v>
+        <v>75.09</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>18</v>
       </c>
       <c r="J50" t="n">
-        <v>97.62</v>
+        <v>106.6</v>
       </c>
       <c r="K50" t="n">
-        <v>126.87</v>
+        <v>138.54</v>
       </c>
       <c r="L50" t="n">
-        <v>160.08</v>
+        <v>174.81</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>13.02</v>
+        <v>14</v>
       </c>
       <c r="K51" t="n">
-        <v>-161.17</v>
+        <v>-173.37</v>
       </c>
       <c r="L51" t="n">
-        <v>161.7</v>
+        <v>173.93</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>-68.12</v>
+        <v>-84.81999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>-17.61</v>
+        <v>-21.93</v>
       </c>
       <c r="L52" t="n">
-        <v>70.36</v>
+        <v>87.61</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>103</v>
+        <v>115.2</v>
       </c>
       <c r="K53" t="n">
-        <v>-146.01</v>
+        <v>-163.32</v>
       </c>
       <c r="L53" t="n">
-        <v>178.68</v>
+        <v>199.86</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>41.68</v>
+        <v>55.3</v>
       </c>
       <c r="K54" t="n">
-        <v>-61.91</v>
+        <v>-82.14</v>
       </c>
       <c r="L54" t="n">
-        <v>74.63</v>
+        <v>99.02</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>16.96</v>
+        <v>19.95</v>
       </c>
       <c r="K55" t="n">
-        <v>-124.85</v>
+        <v>-146.92</v>
       </c>
       <c r="L55" t="n">
-        <v>125.99</v>
+        <v>148.27</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>19</v>
       </c>
       <c r="J56" t="n">
-        <v>-260.37</v>
+        <v>-307.5</v>
       </c>
       <c r="K56" t="n">
-        <v>-103.57</v>
+        <v>-122.32</v>
       </c>
       <c r="L56" t="n">
-        <v>280.21</v>
+        <v>330.93</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>116.35</v>
+        <v>138.56</v>
       </c>
       <c r="K57" t="n">
-        <v>-219.49</v>
+        <v>-261.4</v>
       </c>
       <c r="L57" t="n">
-        <v>248.42</v>
+        <v>295.85</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>-25.37</v>
+        <v>-29.8</v>
       </c>
       <c r="K58" t="n">
-        <v>270.3</v>
+        <v>317.49</v>
       </c>
       <c r="L58" t="n">
-        <v>271.49</v>
+        <v>318.88</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>-9.23</v>
+        <v>-10.34</v>
       </c>
       <c r="K59" t="n">
-        <v>-48.62</v>
+        <v>-54.48</v>
       </c>
       <c r="L59" t="n">
-        <v>49.49</v>
+        <v>55.45</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>9.140000000000001</v>
+        <v>9.84</v>
       </c>
       <c r="K60" t="n">
-        <v>-49.53</v>
+        <v>-53.34</v>
       </c>
       <c r="L60" t="n">
-        <v>50.36</v>
+        <v>54.24</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-83.03</v>
+        <v>-80.76000000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>26.35</v>
+        <v>25.63</v>
       </c>
       <c r="L61" t="n">
-        <v>87.11</v>
+        <v>84.73</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>52.44</v>
+        <v>59.44</v>
       </c>
       <c r="K62" t="n">
-        <v>-38.14</v>
+        <v>-43.23</v>
       </c>
       <c r="L62" t="n">
-        <v>64.84</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-40.81</v>
+        <v>-43.33</v>
       </c>
       <c r="K63" t="n">
-        <v>-71.34</v>
+        <v>-75.73999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>82.19</v>
+        <v>87.26000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-21.81</v>
+        <v>-23.46</v>
       </c>
       <c r="K64" t="n">
-        <v>91.31</v>
+        <v>98.22</v>
       </c>
       <c r="L64" t="n">
-        <v>93.88</v>
+        <v>100.99</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>82.34999999999999</v>
+        <v>97.67</v>
       </c>
       <c r="K65" t="n">
-        <v>52.65</v>
+        <v>62.44</v>
       </c>
       <c r="L65" t="n">
-        <v>97.73999999999999</v>
+        <v>115.93</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-13.01</v>
+        <v>-14.23</v>
       </c>
       <c r="K66" t="n">
-        <v>134.51</v>
+        <v>147.1</v>
       </c>
       <c r="L66" t="n">
-        <v>135.14</v>
+        <v>147.79</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>-21.82</v>
+        <v>-26.8</v>
       </c>
       <c r="K67" t="n">
-        <v>-86.36</v>
+        <v>-106.04</v>
       </c>
       <c r="L67" t="n">
-        <v>89.06999999999999</v>
+        <v>109.38</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>-41.66</v>
+        <v>-51.6</v>
       </c>
       <c r="K68" t="n">
-        <v>142.94</v>
+        <v>177.01</v>
       </c>
       <c r="L68" t="n">
-        <v>148.89</v>
+        <v>184.38</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>-43.26</v>
+        <v>-53.03</v>
       </c>
       <c r="K69" t="n">
-        <v>-125.77</v>
+        <v>-154.17</v>
       </c>
       <c r="L69" t="n">
-        <v>133</v>
+        <v>163.03</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>3.55</v>
+        <v>4.08</v>
       </c>
       <c r="K70" t="n">
-        <v>175.11</v>
+        <v>201.51</v>
       </c>
       <c r="L70" t="n">
-        <v>175.14</v>
+        <v>201.56</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>-204.01</v>
+        <v>-263.74</v>
       </c>
       <c r="K71" t="n">
-        <v>44.97</v>
+        <v>58.14</v>
       </c>
       <c r="L71" t="n">
-        <v>208.91</v>
+        <v>270.08</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>14.95</v>
+        <v>18.81</v>
       </c>
       <c r="K72" t="n">
-        <v>203.74</v>
+        <v>256.38</v>
       </c>
       <c r="L72" t="n">
-        <v>204.29</v>
+        <v>257.07</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-127.41</v>
+        <v>-163.2</v>
       </c>
       <c r="K73" t="n">
-        <v>126.94</v>
+        <v>162.6</v>
       </c>
       <c r="L73" t="n">
-        <v>179.86</v>
+        <v>230.37</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-37.67</v>
+        <v>-38.94</v>
       </c>
       <c r="K74" t="n">
-        <v>52.18</v>
+        <v>53.94</v>
       </c>
       <c r="L74" t="n">
-        <v>64.36</v>
+        <v>66.53</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>-48.6</v>
+        <v>-57.95</v>
       </c>
       <c r="K75" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="L75" t="n">
-        <v>48.63</v>
+        <v>57.99</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>18</v>
       </c>
       <c r="J76" t="n">
-        <v>-37.37</v>
+        <v>-43.44</v>
       </c>
       <c r="K76" t="n">
-        <v>-23.89</v>
+        <v>-27.77</v>
       </c>
       <c r="L76" t="n">
-        <v>44.35</v>
+        <v>51.56</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-49.41</v>
+        <v>-60.71</v>
       </c>
       <c r="K77" t="n">
-        <v>-6.88</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>49.88</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>10.48</v>
+        <v>11.04</v>
       </c>
       <c r="K78" t="n">
-        <v>85.84</v>
+        <v>90.41</v>
       </c>
       <c r="L78" t="n">
-        <v>86.48</v>
+        <v>91.08</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>-1.25</v>
+        <v>-1.38</v>
       </c>
       <c r="K79" t="n">
-        <v>78.09</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>78.09999999999999</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>18</v>
       </c>
       <c r="J80" t="n">
-        <v>-101.61</v>
+        <v>-115.91</v>
       </c>
       <c r="K80" t="n">
-        <v>-62.94</v>
+        <v>-71.79000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>119.53</v>
+        <v>136.35</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>36.37</v>
+        <v>41.16</v>
       </c>
       <c r="K81" t="n">
-        <v>120.78</v>
+        <v>136.69</v>
       </c>
       <c r="L81" t="n">
-        <v>126.14</v>
+        <v>142.75</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-51.72</v>
+        <v>-62.24</v>
       </c>
       <c r="K82" t="n">
-        <v>70.77</v>
+        <v>85.17</v>
       </c>
       <c r="L82" t="n">
-        <v>87.65000000000001</v>
+        <v>105.49</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>79.2</v>
+        <v>98.34</v>
       </c>
       <c r="K83" t="n">
-        <v>-88.48</v>
+        <v>-109.86</v>
       </c>
       <c r="L83" t="n">
-        <v>118.74</v>
+        <v>147.44</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>-125.25</v>
+        <v>-157.2</v>
       </c>
       <c r="K84" t="n">
-        <v>32.67</v>
+        <v>41.01</v>
       </c>
       <c r="L84" t="n">
-        <v>129.44</v>
+        <v>162.46</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>-106.66</v>
+        <v>-127.73</v>
       </c>
       <c r="K85" t="n">
-        <v>-82.22</v>
+        <v>-98.45999999999999</v>
       </c>
       <c r="L85" t="n">
-        <v>134.67</v>
+        <v>161.27</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-193.38</v>
+        <v>-251.51</v>
       </c>
       <c r="K86" t="n">
-        <v>30.97</v>
+        <v>40.28</v>
       </c>
       <c r="L86" t="n">
-        <v>195.85</v>
+        <v>254.71</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>268.87</v>
+        <v>310.38</v>
       </c>
       <c r="K87" t="n">
-        <v>122.05</v>
+        <v>140.9</v>
       </c>
       <c r="L87" t="n">
-        <v>295.27</v>
+        <v>340.87</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>47.37</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="K88" t="n">
-        <v>73.11</v>
+        <v>103.96</v>
       </c>
       <c r="L88" t="n">
-        <v>87.12</v>
+        <v>123.87</v>
       </c>
     </row>
   </sheetData>
